--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,6 +508,2794 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>איתן לויטס</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>info@medico.co.il</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CLINIC_OR_ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%AA%D7%9F-%D7%9C%D7%95%D7%99%D7%98%D7%A1/</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ם לדרג את ד"ר איתן לויטס במדיקו? על מנת לייצר דירוג אמין ואיכותי של גולשים אשר שהו במרפאת ד"ר איתן לויטס רק מי שביקר במרפאה יוכל לבקש קישור ממזכירות המרפאה למילוי חוות דעת והפרטים יתפרסמו באתר הבריאות מדיקו רק לאחר אישור ובכפוף לאימות הפרטים ותקנון האתר. מיד: שיפור מראה הפנים בהתאמה אישית אסתטיקה ואגינלית לפני ואחרי לידה אסתטיקה וגינאלית בהרדמה מקומית להתייעצות עם ד"ר איתן לויטס השאירו פרטים אישור תקנון אתר הנני מאשר את תקנון אתר יש לאשר את תקנון האתר אני מאשר העברת הנתונים לצדדים שלישיים או לחל</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>"איתן לויטס" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>[{"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"איתן לויטס\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/148548/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%AA%D7%9F-%D7%9C%D7%95%D7%99%D7%98%D7%A1/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%90%D7%A1%D7%AA%D7%98%D7%99%D7%AA/", "https://www.medico.co.il/doctors/specialization/%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%90%D7%A1%D7%AA%D7%98%D7%99%D7%AA/city/%D7%91%D7%90%D7%A8-%D7%A9%D7%91%D7%A2/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/"]</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>איתן פאר</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>info@medico.co.il</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CLINIC_OR_ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%AA%D7%9F-%D7%A4%D7%90%D7%A8/</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ה, בית החולים רמב"ם. איזור: חיפה והצפון קופות חולים: מכבי חברות ביטוח: פרטי 5.0/5 1 גולשים דירגו מעוניינים לדרג את ד"ר איתן פאר במדיקו? על מנת לייצר דירוג אמין ואיכותי של גולשים אשר שהו במרפאת ד"ר איתן פאר רק מי שביקר במרפאה יוכל לבקש קישור ממזכירות המרפאה למילוי חוות דעת והפרטים יתפרסמו באתר הבריאות מדיקו רק לאחר אישור ובכפוף לאימות הפרטים ותקנון האתר. להתייעצות עם ד"ר איתן פאר השאירו פרטים אישור תקנון אתר הנני מאשר את תקנון אתר יש לאשר את תקנון האתר אני מאשר העברת הנתונים לצדדים שלישיים או לחל</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>"איתן פאר" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%AA%D7%9F-%D7%A4%D7%90%D7%A8/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%A8%D7%9E%D7%AA-%D7%99%D7%A9%D7%99/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/"]</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>איליה בורד</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>galil@ima.org.il</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://www.ima.org.il/DocHealth/</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>[email protected]</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>"איליה בורד" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>cloudflare</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5703D069-0C8C-4562-AB4F-D2BDBF0DD5D9", "evidence": "[email protected]", "matched_query": "\"איליה בורד\" יילוד גינקולוג", "extraction_method": "cloudflare"}, {"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"איליה בורד\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/144354/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://docsrated.com/doctors/איליה-בורד", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5703D069-0C8C-4562-AB4F-D2BDBF0DD5D9", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#32665547445d46725b5f531c5d40551c5b5e", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>איליה קליינר</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>galil@ima.org.il</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://www.ima.org.il/DocHealth/</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>[email protected]</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>"איליה קליינר" מרפאה פרטית</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>cloudflare</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=567d39f0-ac4e-4c1f-bc0b-9e2d7df0fe55", "evidence": "[email protected]", "matched_query": "\"איליה קליינר\" מרפאה פרטית", "extraction_method": "cloudflare"}]</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.doctorita.co.il/experts/96599", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=567d39f0-ac4e-4c1f-bc0b-9e2d7df0fe55", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#5d093a282b32291d34303c73322f3a733431", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>אילנה ויזל</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>galil@ima.org.il</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://www.ima.org.il/DocHealth/</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>[email protected]</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>"אילנה ויזל" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>cloudflare</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/DoctorsIndex/DoctorProfile.aspx?uDoc=355a292b-1d43-4a5d-90f0-4c32b6488b44", "evidence": "[email protected]", "matched_query": "\"אילנה ויזל\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אילנה-ויזל", "https://www.ima.org.il/DoctorsIndex/DoctorProfile.aspx?uDoc=355a292b-1d43-4a5d-90f0-4c32b6488b44", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#194d7e6c6f766d5970747837766b7e377075", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>אימן חסדיה</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>galil@ima.org.il</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://www.ima.org.il/DocHealth/</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>[email protected]</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>"אימן חסדיה" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>cloudflare</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=bf476bbc-7f22-4f46-87a5-1c620fc9d9bb", "evidence": "[email protected]", "matched_query": "\"אימן חסדיה\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=bf476bbc-7f22-4f46-87a5-1c620fc9d9bb", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#64300311120b10240d09054a0b16034a0d08", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>איתי גולדרט</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>galil@ima.org.il</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://www.ima.org.il/DocHealth/</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>[email protected]</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>"איתי גולדרט" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>cloudflare</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=7945a770-a22a-4e4c-928a-e2b01634ace5", "evidence": "[email protected]", "matched_query": "\"איתי גולדרט\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/איתי-גולדרט", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=7945a770-a22a-4e4c-928a-e2b01634ace5", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#b0e4d7c5c6dfc4f0d9ddd19edfc2d79ed9dc", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>אליאס קסטל</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>galil@ima.org.il</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://www.ima.org.il/DocHealth/</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>[email protected]</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>"אליאס קסטל" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>cloudflare</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=cd209e51-71a4-4071-b665-445363fad75c", "evidence": "[email protected]", "matched_query": "\"אליאס קסטל\" יילוד גינקולוג", "extraction_method": "cloudflare"}, {"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אליאס קסטל\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/93793/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.dr-castel.co.il/", "https://www.dr-castel.co.il/contact", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=cd209e51-71a4-4071-b665-445363fad75c", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#dd89baa8abb2a99db4b0bcf3b2afbaf3b4b1", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>אליהו גוטרמן</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>galil@ima.org.il</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://www.ima.org.il/DocHealth/</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>[email protected]</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>"אליהו גוטרמן" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>cloudflare</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=62015b19-7b3b-418d-80b5-5d7bfe46ebff", "evidence": "[email protected]", "matched_query": "\"אליהו גוטרמן\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=62015b19-7b3b-418d-80b5-5d7bfe46ebff", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#e7b38092918893a78e8a86c9889580c98e8b", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>אליעזר טל</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>galil@ima.org.il</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://www.ima.org.il/DocHealth/</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>[email protected]</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>"אליעזר טל" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>cloudflare</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3b0b0096-b01b-413b-b98c-644ada1c7cba", "evidence": "[email protected]", "matched_query": "\"אליעזר טל\" יילוד גינקולוג", "extraction_method": "cloudflare"}, {"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אליעזר טל\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אליעזר-טל", "https://www.infomed.co.il/experts/93883/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3b0b0096-b01b-413b-b98c-644ada1c7cba", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#2f7b485a59405b6f46424e01405d48014643", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>אליעזר שלו</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>galil@ima.org.il</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://www.ima.org.il/DocHealth/</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>[email protected]</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>"אליעזר שלו" site:ima.org.il</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>cloudflare</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "evidence": "[email protected]", "matched_query": "\"אליעזר שלו\" site:ima.org.il", "extraction_method": "cloudflare"}]</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://he.hamichlol.org.il/אליעזר_שלו", "https://www.ima.org.il/medicinesite/article.aspx?newspaperarticleid=210", "https://www.hamichlol.org.il/אליעזר_שלו", "https://www.doctors.co.il/forum-18/message-149255/", "https://www.ima.org.il/(S(c4l3jumc5opcdmpgjk4orisw))/MedicineSite/Article.aspx?NewspaperArticleId=210", "https://www.ima.org.il/medicinesite/Article.aspx?NewspaperArticleId=210", "https://isuog.ima.org.il/ViewContent.aspx?CategoryId=14969", "https://gynecology.mednet.co.il/events/", "https://fetalmedicinebarcelona.org/calc/", "https://www.ima.org.il/Main/Default.aspx", "https://isuog.ima.org.il/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://isuog.ima.org.il/About.aspx", "https://isuog.ima.org.il/https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx", "https://www.ima.org.il/Main/Populations/DoctorsReturnFromAbroad.aspx", "https://www.ima.org.il/Main/Populations/IndependentDoctors.aspx", "https://www.ima.org.il/MemorialNew/Default.aspx", "https://www.ima.org.il/Main/TabsPage.aspx?tpId=5"]</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>אייל גולדשמידט</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>"אייל גולדשמידט" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/74822/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%92%D7%95%D7%9C%D7%93%D7%A9%D7%9E%D7%99%D7%93%D7%98/", "https://rmc-med.co.il/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%90%D7%AA%D7%A8/", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/", "https://rmc-med.co.il/about/", "https://rmc-med.co.il/management/", "https://rmc-med.co.il/contact/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%92%D7%95%D7%9C%D7%93%D7%A9%D7%9E%D7%99%D7%93%D7%98/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjcxNDAiLCJ0b2dnbGUiOmZhbHNlfQ%3D%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%92%D7%95%D7%9C%D7%93%D7%A9%D7%9E%D7%99%D7%93%D7%98/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%95%D7%A1%D7%99%D7%9D-%D7%90%D7%91%D7%95-%D7%A0%D7%A1%D7%A8%D7%94/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%97%D7%95%D7%A1%D7%90%D7%9D-%D7%A0%D7%A1%D7%90%D7%A8/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%A8%D7%9F-%D7%9C%D7%99%D7%9F/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%95%D7%9F-%D7%9E%D7%A9%D7%99%D7%97/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%A0%D7%90%D7%93%D7%99-%D7%96%D7%9C%D7%99%D7%A6%D7%A0%D7%A7%D7%95/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%9B%D7%94%D7%9F-%D7%9E%D7%99%D7%9B%D7%90%D7%9C/", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjcxNDAiLCJ0b2dnbGUiOmZhbHNlfQ%3D%3D", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%99%D7%90-%D7%A8%D7%95%D7%91%D7%99%D7%9F/", "https://rmc-med.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%95%D7%94%D7%A0%D7%90-%D7%A0%D7%99%D7%93%D7%90%D7%9C/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%95%D7%A4%D7%90%D7%A0%D7%99-%D7%A2%D7%96%D7%99%D7%96/", "https://rmc-med.co.il/doctors/%D7%A2%D7%91%D7%90%D7%A1%D7%99-%D7%A2%D7%A0%D7%90%D7%9F/"]</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>אייל לוי</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>"אייל לוי" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%9C%D7%95%D7%99/", "https://rmc-med.co.il/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%90%D7%AA%D7%A8/", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/", "https://rmc-med.co.il/about/", "https://rmc-med.co.il/management/", "https://rmc-med.co.il/contact/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%9C%D7%95%D7%99/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjcxNDAiLCJ0b2dnbGUiOmZhbHNlfQ%3D%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%9C%D7%95%D7%99/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%95%D7%A1%D7%99%D7%9D-%D7%90%D7%91%D7%95-%D7%A0%D7%A1%D7%A8%D7%94/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%97%D7%95%D7%A1%D7%90%D7%9D-%D7%A0%D7%A1%D7%90%D7%A8/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%A8%D7%9F-%D7%9C%D7%99%D7%9F/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%95%D7%9F-%D7%9E%D7%A9%D7%99%D7%97/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%A0%D7%90%D7%93%D7%99-%D7%96%D7%9C%D7%99%D7%A6%D7%A0%D7%A7%D7%95/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%9B%D7%94%D7%9F-%D7%9E%D7%99%D7%9B%D7%90%D7%9C/", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjcxNDAiLCJ0b2dnbGUiOmZhbHNlfQ%3D%3D", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%99%D7%90-%D7%A8%D7%95%D7%91%D7%99%D7%9F/", "https://rmc-med.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%95%D7%94%D7%A0%D7%90-%D7%A0%D7%99%D7%93%D7%90%D7%9C/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%95%D7%A4%D7%90%D7%A0%D7%99-%D7%A2%D7%96%D7%99%D7%96/", "https://rmc-med.co.il/doctors/%D7%A2%D7%91%D7%90%D7%A1%D7%99-%D7%A2%D7%A0%D7%90%D7%9F/", "https://www.infomed.co.il/experts/151027/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>איילת גדרון אבדיק</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>"איילת גדרון אבדיק" מרפאה פרטית</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%93%D7%A8%D7%95%D7%9F-%D7%90%D7%91%D7%93%D7%99%D7%A7-%D7%90%D7%99%D7%99%D7%9C%D7%AA/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://www.infomed.co.il/experts/145230/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>איליה בנימינוב</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>"איליה בנימינוב" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/74906/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.doctorita.co.il/experts/96512", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors"]</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>אילן גל</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>"אילן גל" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/135371/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%9C%D7%9F-%D7%92%D7%9C-12279/", "https://www.facebook.com/israelshealthwebsite/", "https://medpage.co.il/search-doctors/", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%99%D7%99%D7%9C%D7%95%D7%93+%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%94+%D7%A4%D7%A0%D7%99%D7%9E%D7%99%D7%AA", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%99%D7%9C%D7%93%D7%99%D7%9D", "https://medpage.co.il/search-doctors/?exp=%D7%A4%D7%A1%D7%99%D7%9B%D7%99%D7%90%D7%98%D7%A8%D7%99%D7%94", "https://medpage.co.il/about/", "https://medpage.co.il/contact/", "https://medpage.co.il/search-doctors/?view=exps-index", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99-%D7%91%D7%9F-%D7%94%D7%A8%D7%95%D7%A9-114/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%91%D7%99%D7%AA-%D7%9B%D7%94%D7%9F-9839633/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%A0%D7%A2%D7%9D-%D7%A9%D7%95%D7%A4%D7%A8-15141/", "https://medpage.co.il/doctors/15962-%D7%90%D7%91%D7%A0%D7%A8-%D7%A8%D7%A9%D7%A3-359/", "https://medpage.co.il/doctors/%D7%90%D7%94%D7%95%D7%93-%D7%93%D7%A8%D7%95%D7%A7%D7%A8-10916/", "https://medpage.co.il/doctors/78924-%D7%9E%D7%A8%D7%99%D7%9D-%D7%9E%D7%A4%D7%A8%D7%A2-9589571/", "https://medpage.co.il/doctors/%D7%A6%D7%99%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%A1%D7%91%D7%A8%D7%92-2313046/", "https://medpage.co.il/doctors/60281-%D7%9C%D7%99%D7%93%D7%99%D7%94-%D7%91%D7%9C%D7%9B%D7%A8-18287/"]</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>אילן הלוי</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>"אילן הלוי" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/94151/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/63526110/", "https://www.doctors.co.il/websiteinfo/join-us/", "https://www.doctors.co.il/websiteinfo/terms/", "https://www.doctors.co.il/dr-search/israel/", "https://www.doctors.co.il/websiteinfo/about-us/", "https://www.doctors.co.il/websiteinfo/contact-us/", "https://www.doctors.co.il/", "https://www.doctors.co.il/medical-info/gynecology/", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1345", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1342", "https://www.doctors.co.il/dr-search/dental-clinics/israel/", "https://www.doctors.co.il/dr-search/health-clinics/israel/", "https://www.doctors.co.il/dr-search/clinical-psychologists/israel/", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1", "https://www.doctors.co.il/expert/ent-doctors/5877660/", "https://www.doctors.co.il/medical-info/all/", "https://www.doctors.co.il/all/", "https://www.doctors.co.il/bloodtest/", "https://www.doctors.co.il/cdn-cgi/l/email-protection#6801060e07280c070b1c071a1b460b07460104"]</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>אילן זיו</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>"אילן זיו" מרפאה פרטית</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=88C25B12-47A3-419A-9896-9F18AF9C6455", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=UcczKurRobDx5DacgIA3gYW4Sh0U2pSg0CT0/Hkf9PBZyNpVl1WWWXm1I84hp75jWpoPY1eFHsIRhI1QUEKYcA==", "http://www.maccabi4u.co.il/", "https://serguide.maccabi4u.co.il/heb/doctors/?SearchText=%D7%96%D7%99%D7%95%20%D7%90%D7%99%D7%9C%D7%9F", "https://serguide.maccabi4u.co.il/heb/doctors/", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=8&amp;ProviderID=52249612&amp;ProviderProfession=1&amp;docClinic=1425&amp;Service=1&amp;NewObjectId=61004302&amp;NewObjectType=S&amp;NewPerNr=90001609&amp;ol1=61004302&amp;ol2=S&amp;ol3=90001609&amp;beginDate=2026-08-31T20:01:49&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.infomed.co.il/experts/93842/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%96%D7%99%D7%95-%D7%90%D7%99%D7%9C%D7%9F/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>אילן שוורץ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>"אילן שוורץ" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/93501/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%95%D7%95%D7%A8%D7%A5-%D7%90%D7%99%D7%9C%D7%9F/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>אינה בלייכר</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>"אינה בלייכר" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/147166/", "https://www.helaclinic.com/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/experts/147166/#clinics", "https://www.infomed.co.il/experts/147166/#about", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://docsrated.com/doctors/אינה-בלייכר", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%91%D7%9C%D7%99%D7%99%D7%9B%D7%A8-%D7%90%D7%99%D7%A0%D7%94/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>אירינה ליטוין</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>"אירינה ליטוין" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/93929/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%9C%D7%99%D7%98%D7%95%D7%99%D7%9F-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>איריס אוהל שני</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>"איריס אוהל שני" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/151083/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%95%D7%94%D7%9C-%D7%A9%D7%A0%D7%99-%D7%90%D7%99%D7%A8%D7%99%D7%A1/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>איתן מרדכי</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>"איתן מרדכי" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>[{"email": "info@medico.co.il", "confidence": 75, "source_url": "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%AA%D7%9F-%D7%9E%D7%A8%D7%93%D7%9B%D7%99/", "evidence": "info@medico.co.il", "matched_query": "\"איתן מרדכי\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%AA%D7%9F-%D7%9E%D7%A8%D7%93%D7%9B%D7%99/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%A8%D7%90%D7%A9%D7%95%D7%9F-%D7%9C%D7%A6%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://docsrated.com/doctors/איתן-מרדכי", "https://www.infomed.co.il/experts/145112/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/experts/145112/#clinics", "https://www.infomed.co.il/experts/145112/#about", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>אלה אופיר</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>"אלה אופיר" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/94616/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://medpage.co.il/doctors/%D7%90%D7%9C%D7%94-%D7%90%D7%95%D7%A4%D7%99%D7%A8-41552/", "https://www.facebook.com/israelshealthwebsite/", "https://medpage.co.il/search-doctors/", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%99%D7%99%D7%9C%D7%95%D7%93+%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%94+%D7%A4%D7%A0%D7%99%D7%9E%D7%99%D7%AA", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%99%D7%9C%D7%93%D7%99%D7%9D", "https://medpage.co.il/search-doctors/?exp=%D7%A4%D7%A1%D7%99%D7%9B%D7%99%D7%90%D7%98%D7%A8%D7%99%D7%94", "https://medpage.co.il/about/", "https://medpage.co.il/contact/", "https://medpage.co.il/search-doctors/?view=exps-index", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99-%D7%91%D7%9F-%D7%94%D7%A8%D7%95%D7%A9-114/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%91%D7%99%D7%AA-%D7%9B%D7%94%D7%9F-9839633/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%A0%D7%A2%D7%9D-%D7%A9%D7%95%D7%A4%D7%A8-15141/", "https://medpage.co.il/doctors/15962-%D7%90%D7%91%D7%A0%D7%A8-%D7%A8%D7%A9%D7%A3-359/", "https://medpage.co.il/doctors/%D7%90%D7%94%D7%95%D7%93-%D7%93%D7%A8%D7%95%D7%A7%D7%A8-10916/", "https://medpage.co.il/doctors/78924-%D7%9E%D7%A8%D7%99%D7%9D-%D7%9E%D7%A4%D7%A8%D7%A2-9589571/", "https://medpage.co.il/doctors/%D7%A6%D7%99%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%A1%D7%91%D7%A8%D7%92-2313046/", "https://medpage.co.il/doctors/60281-%D7%9C%D7%99%D7%93%D7%99%D7%94-%D7%91%D7%9C%D7%9B%D7%A8-18287/"]</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>אלה אפשטיין</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>"אלה אפשטיין" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אלה-אפשטיין", "https://www.infomed.co.il/experts/75378/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A4%D7%A9%D7%98%D7%99%D7%99%D7%9F-%D7%90%D7%9C%D7%94/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>אלי מימון</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>"אלי מימון" מרפאה פרטית</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://drlevinger.co.il/doctor/%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9C%D7%99-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/", "https://drlevinger.co.il/site-map/", "https://drlevinger.co.il/procedure/keratoconus/keratoconus-contact-lenses/", "https://drlevinger.co.il/our-doctors/", "https://drlevinger.co.il/our-doctors/?_doctor_proc=8099", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2506", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2548", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2542", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2559", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2546", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2553", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2557", "https://drlevinger.co.il/our-doctors/?_doctor_sector=8999", "https://drlevinger.co.il/our-doctors/?_doctor_center=211", "https://www.infomed.co.il/experts/91609/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>אליאס חדוות</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>"אליאס חדוות" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/147487/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>אליהו וולפסון</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>"אליהו וולפסון" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/152737/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%95%D7%95%D7%9C%D7%A4%D7%A1%D7%95%D7%9F-%D7%90%D7%9C%D7%99%D7%94%D7%95/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>אלינה וילקין</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>"אלינה וילקין" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%95%D7%99%D7%9C%D7%A7%D7%99%D7%9F-%D7%90%D7%9C%D7%99%D7%A0%D7%94/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=YdbE87dpf9Ckia930mxf1ByQknzhT7k/tn8Ln7N4YoBolPMNy3OVzmIL9oNHADHeuUYMi879LXTvVsVHi9t2Kg==", "http://www.maccabi4u.co.il/", "https://serguide.maccabi4u.co.il/heb/doctors/?SearchText=%D7%95%D7%99%D7%9C%D7%A7%D7%99%D7%9F%20%D7%90%D7%9C%D7%99%D7%A0%D7%94", "https://serguide.maccabi4u.co.il/heb/doctors/", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=8&amp;ProviderID=308924687&amp;ProviderProfession=1&amp;docClinic=34619&amp;Service=1&amp;NewObjectId=61007675&amp;NewObjectType=S&amp;NewPerNr=90000994&amp;ol1=61007675&amp;ol2=S&amp;ol3=90000994&amp;beginDate=2026-08-31T21:54:25&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.infomed.co.il/experts/93782/", "https://darkred-ram-504111.hostingersite.com/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/experts/93782/#clinics", "https://www.infomed.co.il/experts/93782/#about", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>אליסף שמואל</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>"אליסף שמואל" מרפאה פרטית</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_e_shmuel.aspx", "https://www.infomed.co.il/experts/151074/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%9E%D7%95%D7%90%D7%9C-%D7%90%D7%9C%D7%99%D7%A1%D7%A3/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>אליעזר הורנשטיין</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>"אליעזר הורנשטיין" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/75662/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://medpage.co.il/doctors/%D7%90%D7%9C%D7%99%D7%A2%D7%96%D7%A8-%D7%94%D7%95%D7%A8%D7%A0%D7%A9%D7%98%D7%99%D7%99%D7%9F-424/", "https://www.facebook.com/israelshealthwebsite/", "https://medpage.co.il/search-doctors/", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%99%D7%99%D7%9C%D7%95%D7%93+%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%94+%D7%A4%D7%A0%D7%99%D7%9E%D7%99%D7%AA", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%99%D7%9C%D7%93%D7%99%D7%9D", "https://medpage.co.il/search-doctors/?exp=%D7%A4%D7%A1%D7%99%D7%9B%D7%99%D7%90%D7%98%D7%A8%D7%99%D7%94", "https://medpage.co.il/about/", "https://medpage.co.il/contact/", "https://medpage.co.il/search-doctors/?view=exps-index", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99-%D7%91%D7%9F-%D7%94%D7%A8%D7%95%D7%A9-114/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%91%D7%99%D7%AA-%D7%9B%D7%94%D7%9F-9839633/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%A0%D7%A2%D7%9D-%D7%A9%D7%95%D7%A4%D7%A8-15141/", "https://medpage.co.il/doctors/15962-%D7%90%D7%91%D7%A0%D7%A8-%D7%A8%D7%A9%D7%A3-359/", "https://medpage.co.il/doctors/%D7%90%D7%94%D7%95%D7%93-%D7%93%D7%A8%D7%95%D7%A7%D7%A8-10916/", "https://medpage.co.il/doctors/78924-%D7%9E%D7%A8%D7%99%D7%9D-%D7%9E%D7%A4%D7%A8%D7%A2-9589571/", "https://medpage.co.il/doctors/%D7%A6%D7%99%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%A1%D7%91%D7%A8%D7%92-2313046/", "https://medpage.co.il/doctors/60281-%D7%9C%D7%99%D7%93%D7%99%D7%94-%D7%91%D7%9C%D7%9B%D7%A8-18287/"]</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>אלכסנדר אבריאנוב</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>"אלכסנדר אבריאנוב" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אלכסנדר-אבריאנוב", "https://www.infomed.co.il/experts/75696/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.beok.co.il/doctors/Doctors-127644/", "https://www.doctorita.co.il/experts/133964", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors", "https://www.vimed.co.il/users/efc1a3ff-b730-499a-8e11-9ac7d92f35a2", "https://www.vimed.co.il/users", "https://www.vimed.co.il/users/daf4127d-8d7f-4fc5-ae39-67b74bc8ef26", "https://www.vimed.co.il/users/9d1ac106-2ead-4857-aa76-83aea36ab54d", "https://www.vimed.co.il/users/e4bd4091-5d6b-42bb-ad32-3f9afaf56942", "https://www.vimed.co.il/users/017527f8-a362-451c-ad8f-3a446eca6ef1", "https://www.vimed.co.il/users/150a8d2e-2ec4-47b7-8bb4-f1b0d6cbe3ea", "https://www.infomed.co.il/expertsresults/neonatal-and-gynecology/all_subspecialities/elat/"]</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>5</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>אלכסנדר ברנוב</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>"אלכסנדר ברנוב" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/75765/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.doctorita.co.il/experts/123009", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors", "https://findoctor.co.il/אלכסנדר-ברנוב-נשים-גינקולוגיה/", "https://www.beok.co.il/doctors/Doctors-126912/"]</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>אלכסנדר פינליס</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>"אלכסנדר פינליס" מרפאה פרטית</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/75842/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://docsrated.com/doctors/אלכסנדר-פינליס", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%99%D7%A0%D7%9C%D7%99%D7%A1-%D7%90%D7%9C%D7%9B%D7%A1%D7%A0%D7%93%D7%A8/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:R78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>איליה בורד</t>
+          <t>אלעד ברקוביץ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>galil@ima.org.il</t>
+          <t>info@medico.co.il</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -716,7 +716,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/DocHealth/</t>
+          <t>https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%A2%D7%93-%D7%91%D7%A8%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -726,30 +726,30 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>[email protected]</t>
+          <t xml:space="preserve"> הפניקס, מנורה, כלל, הראל, איילון, פרטי 4.0/5 10 גולשים דירגו מעוניינים לדרג את ד"ר אלעד ברקוביץ' במדיקו? על מנת לייצר דירוג אמין ואיכותי של גולשים אשר שהו במרפאת ד"ר אלעד ברקוביץ' רק מי שביקר במרפאה יוכל לבקש קישור ממזכירות המרפאה למילוי חוות דעת והפרטים יתפרסמו באתר הבריאות מדיקו רק לאחר אישור ובכפוף לאימות הפרטים ותקנון האתר. הכל על אנדומטריוזיס להתייעצות עם ד"ר אלעד ברקוביץ' השאירו פרטים אישור תקנון אתר הנני מאשר את תקנון אתר יש לאשר את תקנון האתר אני מאשר העברת הנתונים לצדדים שלישיים או לחל</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>"איליה בורד" יילוד גינקולוג</t>
+          <t>"אלעד ברקוביץ" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>cloudflare</t>
+          <t>text</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5703D069-0C8C-4562-AB4F-D2BDBF0DD5D9", "evidence": "[email protected]", "matched_query": "\"איליה בורד\" יילוד גינקולוג", "extraction_method": "cloudflare"}, {"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"איליה בורד\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+          <t>[{"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אלעד ברקוביץ\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/144354/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://docsrated.com/doctors/איליה-בורד", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5703D069-0C8C-4562-AB4F-D2BDBF0DD5D9", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#32665547445d46725b5f531c5d40551c5b5e", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/145971/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctors.assuta.co.il/doctor/elad-berkowitz-36964?readmore=true", "https://doctors.assuta.co.il/doctor/elad-berkowitz-36964", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%A2%D7%93-%D7%91%D7%A8%D7%A7%D7%95%D7%91%D7%99%D7%A5/", "https://www.dr-elad.co.il/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%AA%D7%9C-%D7%90%D7%91%D7%99%D7%91-%D7%99%D7%A4%D7%95/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/"]</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
@@ -760,7 +760,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>איליה קליינר</t>
+          <t>אלעד לרון</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>galil@ima.org.il</t>
+          <t>info@medico.co.il</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -798,7 +798,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/DocHealth/</t>
+          <t>https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%A2%D7%93-%D7%9C%D7%A8%D7%95%D7%9F/</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>[email protected]</t>
+          <t>מרכז, באר שבע והדרום קופות חולים: מכבי, מאוחדת, לאומית חברות ביטוח: פרטי 5.0/5 1 גולשים דירגו מעוניינים לדרג את ד"ר אלעד לרון במדיקו? על מנת לייצר דירוג אמין ואיכותי של גולשים אשר שהו במרפאת ד"ר אלעד לרון רק מי שביקר במרפאה יוכל לבקש קישור ממזכירות המרפאה למילוי חוות דעת והפרטים יתפרסמו באתר הבריאות מדיקו רק לאחר אישור ובכפוף לאימות הפרטים ותקנון האתר. להתייעצות עם ד"ר אלעד לרון השאירו פרטים אישור תקנון אתר הנני מאשר את תקנון אתר יש לאשר את תקנון האתר אני מאשר העברת הנתונים לצדדים שלישיים או לחל</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>"איליה קליינר" מרפאה פרטית</t>
+          <t>"אלעד לרון" מרפאה פרטית</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>cloudflare</t>
+          <t>text</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=567d39f0-ac4e-4c1f-bc0b-9e2d7df0fe55", "evidence": "[email protected]", "matched_query": "\"איליה קליינר\" מרפאה פרטית", "extraction_method": "cloudflare"}]</t>
+          <t>[{"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אלעד לרון\" מרפאה פרטית", "extraction_method": "mailto"}]</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -831,7 +831,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.doctorita.co.il/experts/96599", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=567d39f0-ac4e-4c1f-bc0b-9e2d7df0fe55", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#5d093a282b32291d34303c73322f3a733431", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.eladleron.com/", "https://www.eladleron.com/about", "https://www.eladleron.com/copy-of-%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%93-%D7%A8-%D7%9C%D7%A8%D7%95%D7%9F-1", "https://www.infomed.co.il/experts/75949/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%A2%D7%93-%D7%9C%D7%A8%D7%95%D7%9F/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%AA%D7%9C-%D7%90%D7%91%D7%99%D7%91-%D7%99%D7%A4%D7%95/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/"]</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>אילנה ויזל</t>
+          <t>אמיר ויס</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>galil@ima.org.il</t>
+          <t>info@medico.co.il</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -880,7 +880,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/DocHealth/</t>
+          <t>https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9E%D7%99%D7%A8-%D7%95%D7%99%D7%A1/</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -890,30 +890,30 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>[email protected]</t>
+          <t>ר באגודה הישראלית לחקר הפוריות- איל"ה. איזור: חיפה והצפון חברות ביטוח: פרטי 5.0/5 2 גולשים דירגו מעוניינים לדרג את ד"ר אמיר ויס במדיקו? על מנת לייצר דירוג אמין ואיכותי של גולשים אשר שהו במרפאת ד"ר אמיר ויס רק מי שביקר במרפאה יוכל לבקש קישור ממזכירות המרפאה למילוי חוות דעת והפרטים יתפרסמו באתר הבריאות מדיקו רק לאחר אישור ובכפוף לאימות הפרטים ותקנון האתר. להתייעצות עם ד"ר אמיר ויס השאירו פרטים אישור תקנון אתר הנני מאשר את תקנון אתר יש לאשר את תקנון האתר אני מאשר העברת הנתונים לצדדים שלישיים או לחל</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>"אילנה ויזל" יילוד גינקולוג</t>
+          <t>"אמיר ויס" מרפאה פרטית</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>cloudflare</t>
+          <t>text</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/DoctorsIndex/DoctorProfile.aspx?uDoc=355a292b-1d43-4a5d-90f0-4c32b6488b44", "evidence": "[email protected]", "matched_query": "\"אילנה ויזל\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אילנה-ויזל", "https://www.ima.org.il/DoctorsIndex/DoctorProfile.aspx?uDoc=355a292b-1d43-4a5d-90f0-4c32b6488b44", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#194d7e6c6f766d5970747837766b7e377075", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.medreviews.co.il/search/fertility/north/afula", "https://www.amirweiss.co.il/about/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9E%D7%99%D7%A8-%D7%95%D7%99%D7%A1/", "https://www.amirweiss.co.il/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%97%D7%99%D7%A4%D7%94/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/"]</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
@@ -924,7 +924,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>אימן חסדיה</t>
+          <t>אמיר רבהון</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>galil@ima.org.il</t>
+          <t>info@medico.co.il</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/DocHealth/</t>
+          <t>https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9E%D7%99%D7%A8-%D7%A8%D7%91%D7%94%D7%95%D7%9F/</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -972,22 +972,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>[email protected]</t>
+          <t>וחדת חברות ביטוח: פרטי 5.0/5 1 גולשים דירגו מעוניינים לדרג את ד"ר אמיר רבהון במדיקו? על מנת לייצר דירוג אמין ואיכותי של גולשים אשר שהו במרפאת ד"ר אמיר רבהון רק מי שביקר במרפאה יוכל לבקש קישור ממזכירות המרפאה למילוי חוות דעת והפרטים יתפרסמו באתר הבריאות מדיקו רק לאחר אישור ובכפוף לאימות הפרטים ותקנון האתר. חידוש במתן פרוגסטרון בהריון לאחר טיפולי פוריות להתייעצות עם ד"ר אמיר רבהון השאירו פרטים אישור תקנון אתר הנני מאשר את תקנון אתר יש לאשר את תקנון האתר אני מאשר העברת הנתונים לצדדים שלישיים או לחל</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>"אימן חסדיה" יילוד גינקולוג</t>
+          <t>"אמיר רבהון" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>cloudflare</t>
+          <t>text</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=bf476bbc-7f22-4f46-87a5-1c620fc9d9bb", "evidence": "[email protected]", "matched_query": "\"אימן חסדיה\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
+          <t>[{"email": "ravhon.clinic@gmail.com", "confidence": 90, "source_url": "https://www.dr-ravhon.co.il/", "evidence": "ד\"ר אמיר רבהון - מומחה במיילדות, גניקולוגיה ובפוריות דלג לתוכן לתיאום תור למרפאה הפרטית התקשרו: 05 4-468-5276 | שלחו מייל: ravhon.clinic@gmail.com Facebook דף בית הצעד הראשון מתי לפנות לטיפולי פוריות למה לצפות כשמצפים לטיפולי פוריות? טיפולים טיפולי פוריות הפריה חוץ גופית – IVF תרומת ביציות הקפאת ביציות צילומי רחם אודות כתבות פורום Infomed יצירת קשר תפריט דף בית הצעד הראשון מתי לפנות לטיפולי פוריות למה לצפות כשמצפים לטיפולי פוריות? טיפולים טיפולי פוריות הפריה חוץ גופית – IVF תרומת ביציות הקפאת בי", "matched_query": "\"אמיר רבהון\" יילוד גינקולוג", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -995,7 +995,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=bf476bbc-7f22-4f46-87a5-1c620fc9d9bb", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#64300311120b10240d09054a0b16034a0d08", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9E%D7%99%D7%A8-%D7%A8%D7%91%D7%94%D7%95%D7%9F/", "https://www.dr-ravhon.co.il/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%A8%D7%97%D7%95%D7%91%D7%95%D7%AA/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/"]</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>איתי גולדרט</t>
+          <t>אנה פדואה</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>galil@ima.org.il</t>
+          <t>info@medico.co.il</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/DocHealth/</t>
+          <t>https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A0%D7%94-%D7%A4%D7%93%D7%95%D7%90%D7%94/</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1054,30 +1054,30 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>[email protected]</t>
+          <t>tion איזור: תל-אביב והמרכז חברות ביטוח: מגדל, מנורה, איילון, הכשרה, פרטי 4.0/5 4 גולשים דירגו מעוניינים לדרג את ד"ר אנה פדואה במדיקו? על מנת לייצר דירוג אמין ואיכותי של גולשים אשר שהו במרפאת ד"ר אנה פדואה רק מי שביקר במרפאה יוכל לבקש קישור ממזכירות המרפאה למילוי חוות דעת והפרטים יתפרסמו באתר הבריאות מדיקו רק לאחר אישור ובכפוף לאימות הפרטים ותקנון האתר. להתייעצות עם ד"ר אנה פדואה השאירו פרטים אישור תקנון אתר הנני מאשר את תקנון אתר יש לאשר את תקנון האתר אני מאשר העברת הנתונים לצדדים שלישיים או לחל</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>"איתי גולדרט" יילוד גינקולוג</t>
+          <t>"אנה פדואה" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>cloudflare</t>
+          <t>text</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=7945a770-a22a-4e4c-928a-e2b01634ace5", "evidence": "[email protected]", "matched_query": "\"איתי גולדרט\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/איתי-גולדרט", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=7945a770-a22a-4e4c-928a-e2b01634ace5", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#b0e4d7c5c6dfc4f0d9ddd19edfc2d79ed9dc", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A0%D7%94-%D7%A4%D7%93%D7%95%D7%90%D7%94/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%94%D7%A8%D7%A6%D7%9C%D7%99%D7%94/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/"]</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>אליאס קסטל</t>
+          <t>אסנת ולפיש</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>galil@ima.org.il</t>
+          <t>info@medico.co.il</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/DocHealth/</t>
+          <t>https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%A1%D7%A0%D7%AA-%D7%95%D7%9C%D7%A4%D7%99%D7%A9/</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>[email protected]</t>
+          <t>איזור: יהודה ושומרון קופות חולים: כללית, מכבי חברות ביטוח: פרטי 5.0/5 1 גולשים דירגו מעוניינים לדרג את פרופ' אסנת ולפיש במדיקו? על מנת לייצר דירוג אמין ואיכותי של גולשים אשר שהו במרפאת פרופ' אסנת ולפיש רק מי שביקר במרפאה יוכל לבקש קישור ממזכירות המרפאה למילוי חוות דעת והפרטים יתפרסמו באתר הבריאות מדיקו רק לאחר אישור ובכפוף לאימות הפרטים ותקנון האתר. להתייעצות עם פרופ' אסנת ולפיש השאירו פרטים אישור תקנון אתר הנני מאשר את תקנון אתר יש לאשר את תקנון האתר אני מאשר העברת הנתונים לצדדים שלישיים או לחל</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>"אליאס קסטל" יילוד גינקולוג</t>
+          <t>"אסנת ולפיש" מרפאה פרטית</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>cloudflare</t>
+          <t>text</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=cd209e51-71a4-4071-b665-445363fad75c", "evidence": "[email protected]", "matched_query": "\"אליאס קסטל\" יילוד גינקולוג", "extraction_method": "cloudflare"}, {"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אליאס קסטל\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+          <t>[{"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אסנת ולפיש\" מרפאה פרטית", "extraction_method": "mailto"}]</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/93793/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.dr-castel.co.il/", "https://www.dr-castel.co.il/contact", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=cd209e51-71a4-4071-b665-445363fad75c", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#dd89baa8abb2a99db4b0bcf3b2afbaf3b4b1", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/76263/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.doctorita.co.il/experts/46275", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%A1%D7%A0%D7%AA-%D7%95%D7%9C%D7%A4%D7%99%D7%A9/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%99%D7%A8%D7%95%D7%A9%D7%9C%D7%99%D7%9D/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/"]</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>אליהו גוטרמן</t>
+          <t>אריה ישעיה</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>galil@ima.org.il</t>
+          <t>info@medico.co.il</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/DocHealth/</t>
+          <t>https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%94-%D7%99%D7%A9%D7%A2%D7%99%D7%94/</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1218,30 +1218,30 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>[email protected]</t>
+          <t>ים דירגו מעוניינים לדרג את ד"ר אריה ישעיה במדיקו? על מנת לייצר דירוג אמין ואיכותי של גולשים אשר שהו במרפאת ד"ר אריה ישעיה רק מי שביקר במרפאה יוכל לבקש קישור ממזכירות המרפאה למילוי חוות דעת והפרטים יתפרסמו באתר הבריאות מדיקו רק לאחר אישור ובכפוף לאימות הפרטים ותקנון האתר. כל מה שצריך לדעת על בדיקת מי שפיר טיפול בדליפת שתן בנשים בריאות הנרתיק בגיל המעבר להתייעצות עם ד"ר אריה ישעיה השאירו פרטים אישור תקנון אתר הנני מאשר את תקנון אתר יש לאשר את תקנון האתר אני מאשר העברת הנתונים לצדדים שלישיים או לחל</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>"אליהו גוטרמן" יילוד גינקולוג</t>
+          <t>"אריה ישעיה" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>cloudflare</t>
+          <t>text</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=62015b19-7b3b-418d-80b5-5d7bfe46ebff", "evidence": "[email protected]", "matched_query": "\"אליהו גוטרמן\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=62015b19-7b3b-418d-80b5-5d7bfe46ebff", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#e7b38092918893a78e8a86c9889580c98e8b", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%94-%D7%99%D7%A9%D7%A2%D7%99%D7%94/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%AA%D7%9C-%D7%90%D7%91%D7%99%D7%91-%D7%99%D7%A4%D7%95/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/"]</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>אליעזר טל</t>
+          <t>אביעד כהן</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>galil@ima.org.il</t>
+          <t>usw@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/DocHealth/</t>
+          <t>https://www.tasmc.org.il/lis/lis-units/drlis/</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1300,33 +1300,35 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>[email protected]</t>
+          <t xml:space="preserve">רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון </t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>"אליעזר טל" יילוד גינקולוג</t>
+          <t>"אביעד כהן" יילוד גינקולוג site:tasmc.org.il</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>cloudflare</t>
+          <t>hospital_text</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3b0b0096-b01b-413b-b98c-644ada1c7cba", "evidence": "[email protected]", "matched_query": "\"אליעזר טל\" יילוד גינקולוג", "extraction_method": "cloudflare"}, {"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אליעזר טל\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אליעזר-טל", "https://www.infomed.co.il/experts/93883/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3b0b0096-b01b-413b-b98c-644ada1c7cba", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#2f7b485a59405b6f46424e01405d48014643", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
+          <t>["https://www.tasmc.org.il/doctorssearch/dr/cohen-aviad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/"]</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1334,7 +1336,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>אליעזר שלו</t>
+          <t>איליה בורד</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1387,7 +1389,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>"אליעזר שלו" site:ima.org.il</t>
+          <t>"איליה בורד" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1397,15 +1399,15 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "evidence": "[email protected]", "matched_query": "\"אליעזר שלו\" site:ima.org.il", "extraction_method": "cloudflare"}]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5703D069-0C8C-4562-AB4F-D2BDBF0DD5D9", "evidence": "[email protected]", "matched_query": "\"איליה בורד\" יילוד גינקולוג", "extraction_method": "cloudflare"}, {"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"איליה בורד\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://he.hamichlol.org.il/אליעזר_שלו", "https://www.ima.org.il/medicinesite/article.aspx?newspaperarticleid=210", "https://www.hamichlol.org.il/אליעזר_שלו", "https://www.doctors.co.il/forum-18/message-149255/", "https://www.ima.org.il/(S(c4l3jumc5opcdmpgjk4orisw))/MedicineSite/Article.aspx?NewspaperArticleId=210", "https://www.ima.org.il/medicinesite/Article.aspx?NewspaperArticleId=210", "https://isuog.ima.org.il/ViewContent.aspx?CategoryId=14969", "https://gynecology.mednet.co.il/events/", "https://fetalmedicinebarcelona.org/calc/", "https://www.ima.org.il/Main/Default.aspx", "https://isuog.ima.org.il/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://isuog.ima.org.il/About.aspx", "https://isuog.ima.org.il/https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx", "https://www.ima.org.il/Main/Populations/DoctorsReturnFromAbroad.aspx", "https://www.ima.org.il/Main/Populations/IndependentDoctors.aspx", "https://www.ima.org.il/MemorialNew/Default.aspx", "https://www.ima.org.il/Main/TabsPage.aspx?tpId=5"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/144354/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://docsrated.com/doctors/איליה-בורד", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5703D069-0C8C-4562-AB4F-D2BDBF0DD5D9", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#32665547445d46725b5f531c5d40551c5b5e", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -1416,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>אייל גולדשמידט</t>
+          <t>איליה קליינר</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1441,7 +1443,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>galil@ima.org.il</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1454,7 +1456,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.ima.org.il/DocHealth/</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1464,30 +1466,30 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>[email protected]</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>"אייל גולדשמידט" יילוד גינקולוג</t>
+          <t>"איליה קליינר" מרפאה פרטית</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=567d39f0-ac4e-4c1f-bc0b-9e2d7df0fe55", "evidence": "[email protected]", "matched_query": "\"איליה קליינר\" מרפאה פרטית", "extraction_method": "cloudflare"}]</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/74822/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%92%D7%95%D7%9C%D7%93%D7%A9%D7%9E%D7%99%D7%93%D7%98/", "https://rmc-med.co.il/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%90%D7%AA%D7%A8/", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/", "https://rmc-med.co.il/about/", "https://rmc-med.co.il/management/", "https://rmc-med.co.il/contact/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%92%D7%95%D7%9C%D7%93%D7%A9%D7%9E%D7%99%D7%93%D7%98/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjcxNDAiLCJ0b2dnbGUiOmZhbHNlfQ%3D%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%92%D7%95%D7%9C%D7%93%D7%A9%D7%9E%D7%99%D7%93%D7%98/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%95%D7%A1%D7%99%D7%9D-%D7%90%D7%91%D7%95-%D7%A0%D7%A1%D7%A8%D7%94/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%97%D7%95%D7%A1%D7%90%D7%9D-%D7%A0%D7%A1%D7%90%D7%A8/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%A8%D7%9F-%D7%9C%D7%99%D7%9F/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%95%D7%9F-%D7%9E%D7%A9%D7%99%D7%97/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%A0%D7%90%D7%93%D7%99-%D7%96%D7%9C%D7%99%D7%A6%D7%A0%D7%A7%D7%95/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%9B%D7%94%D7%9F-%D7%9E%D7%99%D7%9B%D7%90%D7%9C/", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjcxNDAiLCJ0b2dnbGUiOmZhbHNlfQ%3D%3D", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%99%D7%90-%D7%A8%D7%95%D7%91%D7%99%D7%9F/", "https://rmc-med.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%95%D7%94%D7%A0%D7%90-%D7%A0%D7%99%D7%93%D7%90%D7%9C/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%95%D7%A4%D7%90%D7%A0%D7%99-%D7%A2%D7%96%D7%99%D7%96/", "https://rmc-med.co.il/doctors/%D7%A2%D7%91%D7%90%D7%A1%D7%99-%D7%A2%D7%A0%D7%90%D7%9F/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.doctorita.co.il/experts/96599", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=567d39f0-ac4e-4c1f-bc0b-9e2d7df0fe55", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#5d093a282b32291d34303c73322f3a733431", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1498,7 +1500,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>אייל לוי</t>
+          <t>אילנה ויזל</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1523,7 +1525,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>galil@ima.org.il</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1536,7 +1538,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.ima.org.il/DocHealth/</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1546,30 +1548,30 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>[email protected]</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>"אייל לוי" יילוד גינקולוג</t>
+          <t>"אילנה ויזל" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/DoctorsIndex/DoctorProfile.aspx?uDoc=355a292b-1d43-4a5d-90f0-4c32b6488b44", "evidence": "[email protected]", "matched_query": "\"אילנה ויזל\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%9C%D7%95%D7%99/", "https://rmc-med.co.il/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%90%D7%AA%D7%A8/", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/", "https://rmc-med.co.il/about/", "https://rmc-med.co.il/management/", "https://rmc-med.co.il/contact/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%9C%D7%95%D7%99/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjcxNDAiLCJ0b2dnbGUiOmZhbHNlfQ%3D%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%9C%D7%95%D7%99/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%95%D7%A1%D7%99%D7%9D-%D7%90%D7%91%D7%95-%D7%A0%D7%A1%D7%A8%D7%94/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%97%D7%95%D7%A1%D7%90%D7%9D-%D7%A0%D7%A1%D7%90%D7%A8/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%A8%D7%9F-%D7%9C%D7%99%D7%9F/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%95%D7%9F-%D7%9E%D7%A9%D7%99%D7%97/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%A0%D7%90%D7%93%D7%99-%D7%96%D7%9C%D7%99%D7%A6%D7%A0%D7%A7%D7%95/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%9B%D7%94%D7%9F-%D7%9E%D7%99%D7%9B%D7%90%D7%9C/", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjcxNDAiLCJ0b2dnbGUiOmZhbHNlfQ%3D%3D", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%99%D7%90-%D7%A8%D7%95%D7%91%D7%99%D7%9F/", "https://rmc-med.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%95%D7%94%D7%A0%D7%90-%D7%A0%D7%99%D7%93%D7%90%D7%9C/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%95%D7%A4%D7%90%D7%A0%D7%99-%D7%A2%D7%96%D7%99%D7%96/", "https://rmc-med.co.il/doctors/%D7%A2%D7%91%D7%90%D7%A1%D7%99-%D7%A2%D7%A0%D7%90%D7%9F/", "https://www.infomed.co.il/experts/151027/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אילנה-ויזל", "https://www.ima.org.il/DoctorsIndex/DoctorProfile.aspx?uDoc=355a292b-1d43-4a5d-90f0-4c32b6488b44", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#194d7e6c6f766d5970747837766b7e377075", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1580,7 +1582,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>איילת גדרון אבדיק</t>
+          <t>אימן חסדיה</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1605,7 +1607,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>galil@ima.org.il</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1618,7 +1620,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.ima.org.il/DocHealth/</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1628,30 +1630,30 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>[email protected]</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>"איילת גדרון אבדיק" מרפאה פרטית</t>
+          <t>"אימן חסדיה" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=bf476bbc-7f22-4f46-87a5-1c620fc9d9bb", "evidence": "[email protected]", "matched_query": "\"אימן חסדיה\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%93%D7%A8%D7%95%D7%9F-%D7%90%D7%91%D7%93%D7%99%D7%A7-%D7%90%D7%99%D7%99%D7%9C%D7%AA/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://www.infomed.co.il/experts/145230/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=bf476bbc-7f22-4f46-87a5-1c620fc9d9bb", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#64300311120b10240d09054a0b16034a0d08", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1662,7 +1664,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>איליה בנימינוב</t>
+          <t>איתי גולדרט</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1687,7 +1689,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>galil@ima.org.il</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1700,7 +1702,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.ima.org.il/DocHealth/</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1710,30 +1712,30 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>[email protected]</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>"איליה בנימינוב" יילוד גינקולוג</t>
+          <t>"איתי גולדרט" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=7945a770-a22a-4e4c-928a-e2b01634ace5", "evidence": "[email protected]", "matched_query": "\"איתי גולדרט\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/74906/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.doctorita.co.il/experts/96512", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/איתי-גולדרט", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=7945a770-a22a-4e4c-928a-e2b01634ace5", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#b0e4d7c5c6dfc4f0d9ddd19edfc2d79ed9dc", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1744,7 +1746,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>אילן גל</t>
+          <t>איתן גלעדי יעקובי</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1769,7 +1771,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>gen-c@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1782,7 +1784,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.tasmc.org.il/lis/lis-units/drlis/</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1792,30 +1794,30 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>טיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשות להקדמת תור שנקבע עקב דחיפות רפואית יש ללוות במסמכים רפואיים התומכים בבקשה ולהפנות בדואר אלקטרוני כמפורט: לזימון תורים: zimun@tlvmc.gov.il (כל</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>"אילן גל" יילוד גינקולוג</t>
+          <t>"איתן גלעדי יעקובי" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>text</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "og-clinic@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "ן למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון תורים באיכילוב לזימון מקוון למרפאות &gt; שליחת טופס פניה דיגיטלי לתיאום תור &gt; פנית טלפונית למוקד זימון תורים: 8801* או 03-6974000 לזימון תור אולטרא סאונד נשים שלילת מומים יש להעביר הפנייה בדואר אלקטרוני usw@tlvmc.gov.il בקשו", "matched_query": "\"איתן גלעדי יעקובי\" יילוד גינקולוג", "extraction_method": "text"}, {"email": "usw@tlvmc.gov.il", "confidence": 90, "source_url": "https://www.tasmc.org.il/lis/lis-units/drlis/", "evidence": "רופות מותר ליטול בהריון. במקרה של תרופות למחלות כרוניות, יש להתייעץ עם רופא. סקס בהריון: מותר ואסור מה קורה לחשק המיני בזמן ההריון? באילו מצבים חל איסור לקיים יחסי מין בהריון? כל מה שצריך לדעת שאלות ותשובות זימון תור מקוון למרפאות ליס מרפאת נשים &gt;&gt; מרפאה אורוגניקולוגית &gt;&gt;&gt; מרפאת גניקולוגיה-אונקולוגיה &gt;&gt; מרפאה להריון בר-סיכון &gt;&gt; טרטולוגיה - מרפאה &gt;&gt; מרפאת יסמין לטיפול מיני &gt;&gt; פריון הגבר ובנק הזרע &gt;&gt; איך מזמינים תור למרפאות הנשים באיכילוב ? הזמנת תור למרפאות נשים זימון התורים מתבצע דרך מרכז זימון ", "matched_query": "\"איתן גלעדי יעקובי\" יילוד גינקולוג", "extraction_method": "text"}]</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/135371/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%9C%D7%9F-%D7%92%D7%9C-12279/", "https://www.facebook.com/israelshealthwebsite/", "https://medpage.co.il/search-doctors/", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%99%D7%99%D7%9C%D7%95%D7%93+%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%94+%D7%A4%D7%A0%D7%99%D7%9E%D7%99%D7%AA", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%99%D7%9C%D7%93%D7%99%D7%9D", "https://medpage.co.il/search-doctors/?exp=%D7%A4%D7%A1%D7%99%D7%9B%D7%99%D7%90%D7%98%D7%A8%D7%99%D7%94", "https://medpage.co.il/about/", "https://medpage.co.il/contact/", "https://medpage.co.il/search-doctors/?view=exps-index", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99-%D7%91%D7%9F-%D7%94%D7%A8%D7%95%D7%A9-114/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%91%D7%99%D7%AA-%D7%9B%D7%94%D7%9F-9839633/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%A0%D7%A2%D7%9D-%D7%A9%D7%95%D7%A4%D7%A8-15141/", "https://medpage.co.il/doctors/15962-%D7%90%D7%91%D7%A0%D7%A8-%D7%A8%D7%A9%D7%A3-359/", "https://medpage.co.il/doctors/%D7%90%D7%94%D7%95%D7%93-%D7%93%D7%A8%D7%95%D7%A7%D7%A8-10916/", "https://medpage.co.il/doctors/78924-%D7%9E%D7%A8%D7%99%D7%9D-%D7%9E%D7%A4%D7%A8%D7%A2-9589571/", "https://medpage.co.il/doctors/%D7%A6%D7%99%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%A1%D7%91%D7%A8%D7%92-2313046/", "https://medpage.co.il/doctors/60281-%D7%9C%D7%99%D7%93%D7%99%D7%94-%D7%91%D7%9C%D7%9B%D7%A8-18287/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.tasmc.org.il/doctorssearch/dr/eytan-giladi-yacobi/", "https://www.tasmc.org.il/doctorssearch/dr/eytan-giladi-yacobi/#navbarSupportedContent", "https://www.tasmc.org.il/bewell/personalzonelogin/", "https://www.tasmc.org.il/bewell/pages/psite/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/unit-index-page/clinics-institutes/quick-diagnosis/", "https://www.tasmc.org.il/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/", "https://www.tasmc.org.il/lis/about/lis-talk-podcast/", "https://www.tasmc.org.il/media/staff-meeting-2026/", "https://www.tasmc.org.il/media/staff-meeting-2025/", "https://www.tasmc.org.il/media/2023-staff-meeting/", "https://www.tasmc.org.il/media/staff-meeting/", "https://www.tasmc.org.il/service-info/crmtpa/", "https://www.tasmc.org.il/lis/lis-units/drlis/", "https://www.tasmc.org.il/en/aboutl/about/", "https://www.tasmc.org.il/en/unit-index-page/clinics-institutes/", "https://www.tasmc.org.il/doctorssearch/dr/wolf-ido/", "https://www.tasmc.org.il/en/doctorssearch/", "https://www.tasmc.org.il/segel-unit/doctors/senior-doctors/"]</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -1826,7 +1828,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>אילן הלוי</t>
+          <t>אליאס קסטל</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1851,7 +1853,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>galil@ima.org.il</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1864,7 +1866,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.ima.org.il/DocHealth/</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1874,30 +1876,30 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>[email protected]</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>"אילן הלוי" יילוד גינקולוג</t>
+          <t>"אליאס קסטל" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=cd209e51-71a4-4071-b665-445363fad75c", "evidence": "[email protected]", "matched_query": "\"אליאס קסטל\" יילוד גינקולוג", "extraction_method": "cloudflare"}, {"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אליאס קסטל\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/94151/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/63526110/", "https://www.doctors.co.il/websiteinfo/join-us/", "https://www.doctors.co.il/websiteinfo/terms/", "https://www.doctors.co.il/dr-search/israel/", "https://www.doctors.co.il/websiteinfo/about-us/", "https://www.doctors.co.il/websiteinfo/contact-us/", "https://www.doctors.co.il/", "https://www.doctors.co.il/medical-info/gynecology/", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1345", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1342", "https://www.doctors.co.il/dr-search/dental-clinics/israel/", "https://www.doctors.co.il/dr-search/health-clinics/israel/", "https://www.doctors.co.il/dr-search/clinical-psychologists/israel/", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1", "https://www.doctors.co.il/expert/ent-doctors/5877660/", "https://www.doctors.co.il/medical-info/all/", "https://www.doctors.co.il/all/", "https://www.doctors.co.il/bloodtest/", "https://www.doctors.co.il/cdn-cgi/l/email-protection#6801060e07280c070b1c071a1b460b07460104"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/93793/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.dr-castel.co.il/", "https://www.dr-castel.co.il/contact", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=cd209e51-71a4-4071-b665-445363fad75c", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#dd89baa8abb2a99db4b0bcf3b2afbaf3b4b1", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -1908,7 +1910,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>אילן זיו</t>
+          <t>אליהו גוטרמן</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1933,7 +1935,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>galil@ima.org.il</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1946,7 +1948,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.ima.org.il/DocHealth/</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1956,30 +1958,30 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>[email protected]</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>"אילן זיו" מרפאה פרטית</t>
+          <t>"אליהו גוטרמן" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=62015b19-7b3b-418d-80b5-5d7bfe46ebff", "evidence": "[email protected]", "matched_query": "\"אליהו גוטרמן\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=88C25B12-47A3-419A-9896-9F18AF9C6455", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=UcczKurRobDx5DacgIA3gYW4Sh0U2pSg0CT0/Hkf9PBZyNpVl1WWWXm1I84hp75jWpoPY1eFHsIRhI1QUEKYcA==", "http://www.maccabi4u.co.il/", "https://serguide.maccabi4u.co.il/heb/doctors/?SearchText=%D7%96%D7%99%D7%95%20%D7%90%D7%99%D7%9C%D7%9F", "https://serguide.maccabi4u.co.il/heb/doctors/", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=8&amp;ProviderID=52249612&amp;ProviderProfession=1&amp;docClinic=1425&amp;Service=1&amp;NewObjectId=61004302&amp;NewObjectType=S&amp;NewPerNr=90001609&amp;ol1=61004302&amp;ol2=S&amp;ol3=90001609&amp;beginDate=2026-08-31T20:01:49&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.infomed.co.il/experts/93842/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%96%D7%99%D7%95-%D7%90%D7%99%D7%9C%D7%9F/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=62015b19-7b3b-418d-80b5-5d7bfe46ebff", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#e7b38092918893a78e8a86c9889580c98e8b", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
@@ -1990,7 +1992,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>אילן שוורץ</t>
+          <t>אליעזר טל</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2015,7 +2017,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>galil@ima.org.il</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2028,7 +2030,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.ima.org.il/DocHealth/</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2038,30 +2040,30 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>[email protected]</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>"אילן שוורץ" יילוד גינקולוג</t>
+          <t>"אליעזר טל" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3b0b0096-b01b-413b-b98c-644ada1c7cba", "evidence": "[email protected]", "matched_query": "\"אליעזר טל\" יילוד גינקולוג", "extraction_method": "cloudflare"}, {"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אליעזר טל\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/93501/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%95%D7%95%D7%A8%D7%A5-%D7%90%D7%99%D7%9C%D7%9F/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אליעזר-טל", "https://www.infomed.co.il/experts/93883/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3b0b0096-b01b-413b-b98c-644ada1c7cba", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#2f7b485a59405b6f46424e01405d48014643", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
@@ -2072,7 +2074,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>אינה בלייכר</t>
+          <t>אליעזר שלו</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2097,7 +2099,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>galil@ima.org.il</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2110,7 +2112,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.ima.org.il/DocHealth/</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2120,30 +2122,30 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>[email protected]</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>"אינה בלייכר" יילוד גינקולוג</t>
+          <t>"אליעזר שלו" site:ima.org.il</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "evidence": "[email protected]", "matched_query": "\"אליעזר שלו\" site:ima.org.il", "extraction_method": "cloudflare"}]</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/147166/", "https://www.helaclinic.com/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/experts/147166/#clinics", "https://www.infomed.co.il/experts/147166/#about", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://docsrated.com/doctors/אינה-בלייכר", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%91%D7%9C%D7%99%D7%99%D7%9B%D7%A8-%D7%90%D7%99%D7%A0%D7%94/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://he.hamichlol.org.il/אליעזר_שלו", "https://www.ima.org.il/medicinesite/article.aspx?newspaperarticleid=210", "https://www.hamichlol.org.il/אליעזר_שלו", "https://www.doctors.co.il/forum-18/message-149255/", "https://www.ima.org.il/(S(c4l3jumc5opcdmpgjk4orisw))/MedicineSite/Article.aspx?NewspaperArticleId=210", "https://www.ima.org.il/medicinesite/Article.aspx?NewspaperArticleId=210", "https://isuog.ima.org.il/ViewContent.aspx?CategoryId=14969", "https://gynecology.mednet.co.il/events/", "https://fetalmedicinebarcelona.org/calc/", "https://www.ima.org.il/Main/Default.aspx", "https://isuog.ima.org.il/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://isuog.ima.org.il/About.aspx", "https://isuog.ima.org.il/https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx", "https://www.ima.org.il/Main/Populations/DoctorsReturnFromAbroad.aspx", "https://www.ima.org.il/Main/Populations/IndependentDoctors.aspx", "https://www.ima.org.il/MemorialNew/Default.aspx", "https://www.ima.org.il/Main/TabsPage.aspx?tpId=5"]</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
@@ -2154,7 +2156,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>אירינה ליטוין</t>
+          <t>אלנה מיניץ'</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2179,7 +2181,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>galil@ima.org.il</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2192,7 +2194,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.ima.org.il/DocHealth/</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2202,30 +2204,30 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>[email protected]</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>"אירינה ליטוין" יילוד גינקולוג</t>
+          <t>"אלנה מיניץ'" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=38A1BDA7-4761-4336-AC75-44B113A8F52C", "evidence": "[email protected]", "matched_query": "\"אלנה מיניץ'\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/93929/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%9C%D7%99%D7%98%D7%95%D7%99%D7%9F-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אלנה-מיניץ", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=38A1BDA7-4761-4336-AC75-44B113A8F52C", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#590d3e2c2f362d1930343877362b3e773035", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
@@ -2236,7 +2238,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>איריס אוהל שני</t>
+          <t>אמיר נאה</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2261,7 +2263,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>galil@ima.org.il</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2274,7 +2276,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.ima.org.il/DocHealth/</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2284,30 +2286,30 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>[email protected]</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>"איריס אוהל שני" יילוד גינקולוג</t>
+          <t>"אמיר נאה" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d58e624a-1c29-4ee3-ae44-b484f19768b1", "evidence": "[email protected]", "matched_query": "\"אמיר נאה\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/151083/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%95%D7%94%D7%9C-%D7%A9%D7%A0%D7%99-%D7%90%D7%99%D7%A8%D7%99%D7%A1/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://medpage.co.il/doctors/%D7%90%D7%9E%D7%99%D7%A8-%D7%A0%D7%90%D7%94-23596/", "https://www.facebook.com/israelshealthwebsite/", "https://medpage.co.il/search-doctors/", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%99%D7%99%D7%9C%D7%95%D7%93+%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%94+%D7%A4%D7%A0%D7%99%D7%9E%D7%99%D7%AA", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%99%D7%9C%D7%93%D7%99%D7%9D", "https://medpage.co.il/search-doctors/?exp=%D7%A4%D7%A1%D7%99%D7%9B%D7%99%D7%90%D7%98%D7%A8%D7%99%D7%94", "https://medpage.co.il/about/", "https://medpage.co.il/contact/", "https://medpage.co.il/search-doctors/?view=exps-index", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99-%D7%91%D7%9F-%D7%94%D7%A8%D7%95%D7%A9-114/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%91%D7%99%D7%AA-%D7%9B%D7%94%D7%9F-9839633/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%A0%D7%A2%D7%9D-%D7%A9%D7%95%D7%A4%D7%A8-15141/", "https://medpage.co.il/doctors/15962-%D7%90%D7%91%D7%A0%D7%A8-%D7%A8%D7%A9%D7%A3-359/", "https://medpage.co.il/doctors/%D7%90%D7%94%D7%95%D7%93-%D7%93%D7%A8%D7%95%D7%A7%D7%A8-10916/", "https://medpage.co.il/doctors/78924-%D7%9E%D7%A8%D7%99%D7%9D-%D7%9E%D7%A4%D7%A8%D7%A2-9589571/", "https://medpage.co.il/doctors/%D7%A6%D7%99%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%A1%D7%91%D7%A8%D7%92-2313046/", "https://medpage.co.il/doctors/60281-%D7%9C%D7%99%D7%93%D7%99%D7%94-%D7%91%D7%9C%D7%9B%D7%A8-18287/", "https://docsrated.com/doctors/אמיר-נאה", "https://www.doctorita.co.il/experts/125952", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d58e624a-1c29-4ee3-ae44-b484f19768b1", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#96c2f1e3e0f9e2d6fffbf7b8f9e4f1b8fffa", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
@@ -2318,7 +2320,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>איתן מרדכי</t>
+          <t>אן דקלו</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2343,7 +2345,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>galil@ima.org.il</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2356,7 +2358,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.ima.org.il/DocHealth/</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2366,22 +2368,22 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>[email protected]</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>"איתן מרדכי" יילוד גינקולוג</t>
+          <t>"אן דקלו" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>[{"email": "info@medico.co.il", "confidence": 75, "source_url": "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%AA%D7%9F-%D7%9E%D7%A8%D7%93%D7%9B%D7%99/", "evidence": "info@medico.co.il", "matched_query": "\"איתן מרדכי\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=f82d6f50-76a7-4343-8b53-ca9af6a453b6", "evidence": "[email protected]", "matched_query": "\"אן דקלו\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2389,7 +2391,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%AA%D7%9F-%D7%9E%D7%A8%D7%93%D7%9B%D7%99/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%A8%D7%90%D7%A9%D7%95%D7%9F-%D7%9C%D7%A6%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://docsrated.com/doctors/איתן-מרדכי", "https://www.infomed.co.il/experts/145112/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/experts/145112/#clinics", "https://www.infomed.co.il/experts/145112/#about", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אן-דקלו", "https://www.nashim.net/?CategoryID=1048&amp;ArticleID=3176", "https://www.nashim.net/?pg=sitemap&amp;CategoryID=1062", "https://www.nashim.net/?CategoryID=1048", "https://www.nashim.net/?CategoryID=1143", "https://www.nashim.net/?CategoryID=1163&amp;ArticleID=2361", "https://www.nashim.net/?CategoryID=1215", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=f82d6f50-76a7-4343-8b53-ca9af6a453b6", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#cd99aab8bba2b98da4a0ace3a2bfaae3a4a1", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
@@ -2400,7 +2402,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>אלה אופיר</t>
+          <t>אנדרס אלחנדרו סילברפיש</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2425,7 +2427,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>galil@ima.org.il</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2438,7 +2440,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.ima.org.il/DocHealth/</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2448,30 +2450,30 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>[email protected]</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>"אלה אופיר" יילוד גינקולוג</t>
+          <t>"אנדרס אלחנדרו סילברפיש" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=6802b293-9e46-481b-8b2c-ea6cb4412e7d", "evidence": "[email protected]", "matched_query": "\"אנדרס אלחנדרו סילברפיש\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/94616/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://medpage.co.il/doctors/%D7%90%D7%9C%D7%94-%D7%90%D7%95%D7%A4%D7%99%D7%A8-41552/", "https://www.facebook.com/israelshealthwebsite/", "https://medpage.co.il/search-doctors/", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%99%D7%99%D7%9C%D7%95%D7%93+%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%94+%D7%A4%D7%A0%D7%99%D7%9E%D7%99%D7%AA", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%99%D7%9C%D7%93%D7%99%D7%9D", "https://medpage.co.il/search-doctors/?exp=%D7%A4%D7%A1%D7%99%D7%9B%D7%99%D7%90%D7%98%D7%A8%D7%99%D7%94", "https://medpage.co.il/about/", "https://medpage.co.il/contact/", "https://medpage.co.il/search-doctors/?view=exps-index", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99-%D7%91%D7%9F-%D7%94%D7%A8%D7%95%D7%A9-114/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%91%D7%99%D7%AA-%D7%9B%D7%94%D7%9F-9839633/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%A0%D7%A2%D7%9D-%D7%A9%D7%95%D7%A4%D7%A8-15141/", "https://medpage.co.il/doctors/15962-%D7%90%D7%91%D7%A0%D7%A8-%D7%A8%D7%A9%D7%A3-359/", "https://medpage.co.il/doctors/%D7%90%D7%94%D7%95%D7%93-%D7%93%D7%A8%D7%95%D7%A7%D7%A8-10916/", "https://medpage.co.il/doctors/78924-%D7%9E%D7%A8%D7%99%D7%9D-%D7%9E%D7%A4%D7%A8%D7%A2-9589571/", "https://medpage.co.il/doctors/%D7%A6%D7%99%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%A1%D7%91%D7%A8%D7%92-2313046/", "https://medpage.co.il/doctors/60281-%D7%9C%D7%99%D7%93%D7%99%D7%94-%D7%91%D7%9C%D7%9B%D7%A8-18287/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=6802b293-9e46-481b-8b2c-ea6cb4412e7d", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#a2f6c5d7d4cdd6e2cbcfc38ccdd0c58ccbce", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
         </is>
       </c>
       <c r="R25" t="inlineStr"/>
@@ -2482,7 +2484,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>אלה אפשטיין</t>
+          <t>אנה אידלסון</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2507,7 +2509,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>galil@ima.org.il</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2520,7 +2522,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.ima.org.il/DocHealth/</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2530,30 +2532,30 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>[email protected]</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>"אלה אפשטיין" יילוד גינקולוג</t>
+          <t>"אנה אידלסון" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/DoctorsIndex/DoctorProfile.aspx?uDoc=027c20fb-26df-4c5f-b39e-e2be1cc77a77", "evidence": "[email protected]", "matched_query": "\"אנה אידלסון\" יילוד גינקולוג", "extraction_method": "cloudflare"}, {"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אנה אידלסון\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אלה-אפשטיין", "https://www.infomed.co.il/experts/75378/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A4%D7%A9%D7%98%D7%99%D7%99%D7%9F-%D7%90%D7%9C%D7%94/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/93785/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.ima.org.il/DoctorsIndex/DoctorProfile.aspx?uDoc=027c20fb-26df-4c5f-b39e-e2be1cc77a77", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#8dd9eaf8fbe2f9cde4e0eca3e2ffeaa3e4e1", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
@@ -2564,7 +2566,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>אלי מימון</t>
+          <t>אפרים גדנסקי</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2589,7 +2591,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>galil@ima.org.il</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2602,7 +2604,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.ima.org.il/DocHealth/</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2612,30 +2614,30 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>[email protected]</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>"אלי מימון" מרפאה פרטית</t>
+          <t>"אפרים גדנסקי" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=AF8236EC-C187-4C26-B179-C3B078478059", "evidence": "[email protected]", "matched_query": "\"אפרים גדנסקי\" יילוד גינקולוג", "extraction_method": "cloudflare"}, {"email": "cs@infomed.co.il", "confidence": 85, "source_url": "https://www.infomed.co.il/articles/4153/", "evidence": "אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ", "matched_query": "\"אפרים גדנסקי\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://drlevinger.co.il/doctor/%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9C%D7%99-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/", "https://drlevinger.co.il/site-map/", "https://drlevinger.co.il/procedure/keratoconus/keratoconus-contact-lenses/", "https://drlevinger.co.il/our-doctors/", "https://drlevinger.co.il/our-doctors/?_doctor_proc=8099", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2506", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2548", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2542", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2559", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2546", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2553", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2557", "https://drlevinger.co.il/our-doctors/?_doctor_sector=8999", "https://drlevinger.co.il/our-doctors/?_doctor_center=211", "https://www.infomed.co.il/experts/91609/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/76346/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=AF8236EC-C187-4C26-B179-C3B078478059", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#ecb88b999a8398ac85818dc2839e8bc28580", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
@@ -2646,7 +2648,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>אליאס חדוות</t>
+          <t>ארי רייס</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2671,7 +2673,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>galil@ima.org.il</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2684,7 +2686,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.ima.org.il/DocHealth/</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2694,30 +2696,30 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>[email protected]</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>"אליאס חדוות" יילוד גינקולוג</t>
+          <t>"ארי רייס" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/DoctorsIndex/DoctorProfile.aspx?uDoc=571347AD-B044-41BF-BFCA-1F0CC0EAF5F1", "evidence": "[email protected]", "matched_query": "\"ארי רייס\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/147487/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/ארי-רייס", "https://arireissmd.com/", "https://arireissmd.com/accessibility-statement/", "https://arireissmd.com/#about", "https://arireissmd.com/#contact", "https://doctors.assuta.co.il/doctor/ari-reiss-34132?readmore=true", "https://www.ima.org.il/DoctorsIndex/DoctorProfile.aspx?uDoc=571347AD-B044-41BF-BFCA-1F0CC0EAF5F1", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#184c7f6d6e776c5871757936776a7f367174", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
@@ -2728,7 +2730,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>אליהו וולפסון</t>
+          <t>אריאל שטטמן</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2753,7 +2755,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>cs@infomed.co.il</t>
+          <t>galil@ima.org.il</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2766,7 +2768,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://www.infomed.co.il/articles/4153/</t>
+          <t>https://www.ima.org.il/DocHealth/</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2776,30 +2778,30 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+          <t>[email protected]</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>"אליהו וולפסון" יילוד גינקולוג</t>
+          <t>"אריאל שטטמן" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>mailto</t>
+          <t>cloudflare</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "tguvot@ima.org.il", "confidence": 90, "source_url": "https://www.ima.org.il/DoctorsIndex/DoctorProfile.aspx?uDoc=11b2150b-9d9f-4867-9943-bf126e555aa2", "evidence": "[email protected]", "matched_query": "\"אריאל שטטמן\" יילוד גינקולוג", "extraction_method": "cloudflare"}]</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/152737/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%95%D7%95%D7%9C%D7%A4%D7%A1%D7%95%D7%9F-%D7%90%D7%9C%D7%99%D7%94%D7%95/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.ima.org.il/DoctorsIndex/DoctorProfile.aspx?uDoc=11b2150b-9d9f-4867-9943-bf126e555aa2", "https://www.ima.org.il/main/default.aspx", "https://www.ima.org.il/Internship/Default.aspx", "https://www.ima.org.il/memorialnew/default.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/join.aspx", "https://www.ima.org.il/doctorsindex/results.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/doctorsindex/phonebookresults.aspx", "https://www.ima.org.il/cdn-cgi/l/email-protection#62360517140d16220b0f034c0d10054c0b0e", "https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/main/SubjectsPage.aspx?spId=9", "https://www.ima.org.il/Main/Forms/FormPasswordReminder.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fmainsitenew%2fdoctorcard%2fmain.aspx", "https://www.ima.org.il/Main/Login.aspx?uo=True&amp;rp=https://www.ima.org.il/MainSiteNew/DoctorCard/Update.aspx", "https://www.ima.org.il/main/contactus.aspx", "https://www.ima.org.il/DoctorsIndex/", "https://www.ima.org.il/DocHealth/", "https://www.ima.org.il/Main/Login.aspx?rp=https://www.ima.org.il/Main/ContactUs.aspx", "https://www.ima.org.il/Main/Login.aspx?drpb=1&amp;rp=https%3a%2f%2fwww.ima.org.il%2fMainSiteNew%2fDoctorCard%2fMain.aspx", "https://www.ima.org.il/Main/Populations/Experts.aspx", "https://www.ima.org.il/Main/Populations/Retiring.aspx"]</t>
         </is>
       </c>
       <c r="R29" t="inlineStr"/>
@@ -2810,7 +2812,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>אלינה וילקין</t>
+          <t>אייל גולדשמידט</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2863,7 +2865,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>"אלינה וילקין" יילוד גינקולוג</t>
+          <t>"אייל גולדשמידט" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2881,7 +2883,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%95%D7%99%D7%9C%D7%A7%D7%99%D7%9F-%D7%90%D7%9C%D7%99%D7%A0%D7%94/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=YdbE87dpf9Ckia930mxf1ByQknzhT7k/tn8Ln7N4YoBolPMNy3OVzmIL9oNHADHeuUYMi879LXTvVsVHi9t2Kg==", "http://www.maccabi4u.co.il/", "https://serguide.maccabi4u.co.il/heb/doctors/?SearchText=%D7%95%D7%99%D7%9C%D7%A7%D7%99%D7%9F%20%D7%90%D7%9C%D7%99%D7%A0%D7%94", "https://serguide.maccabi4u.co.il/heb/doctors/", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=8&amp;ProviderID=308924687&amp;ProviderProfession=1&amp;docClinic=34619&amp;Service=1&amp;NewObjectId=61007675&amp;NewObjectType=S&amp;NewPerNr=90000994&amp;ol1=61007675&amp;ol2=S&amp;ol3=90000994&amp;beginDate=2026-08-31T21:54:25&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.infomed.co.il/experts/93782/", "https://darkred-ram-504111.hostingersite.com/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/experts/93782/#clinics", "https://www.infomed.co.il/experts/93782/#about", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/74822/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%92%D7%95%D7%9C%D7%93%D7%A9%D7%9E%D7%99%D7%93%D7%98/", "https://rmc-med.co.il/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%90%D7%AA%D7%A8/", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/", "https://rmc-med.co.il/about/", "https://rmc-med.co.il/management/", "https://rmc-med.co.il/contact/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%92%D7%95%D7%9C%D7%93%D7%A9%D7%9E%D7%99%D7%93%D7%98/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjcxNDAiLCJ0b2dnbGUiOmZhbHNlfQ%3D%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%92%D7%95%D7%9C%D7%93%D7%A9%D7%9E%D7%99%D7%93%D7%98/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%95%D7%A1%D7%99%D7%9D-%D7%90%D7%91%D7%95-%D7%A0%D7%A1%D7%A8%D7%94/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%97%D7%95%D7%A1%D7%90%D7%9D-%D7%A0%D7%A1%D7%90%D7%A8/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%A8%D7%9F-%D7%9C%D7%99%D7%9F/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%95%D7%9F-%D7%9E%D7%A9%D7%99%D7%97/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%A0%D7%90%D7%93%D7%99-%D7%96%D7%9C%D7%99%D7%A6%D7%A0%D7%A7%D7%95/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%9B%D7%94%D7%9F-%D7%9E%D7%99%D7%9B%D7%90%D7%9C/", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjcxNDAiLCJ0b2dnbGUiOmZhbHNlfQ%3D%3D", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%99%D7%90-%D7%A8%D7%95%D7%91%D7%99%D7%9F/", "https://rmc-med.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%95%D7%94%D7%A0%D7%90-%D7%A0%D7%99%D7%93%D7%90%D7%9C/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%95%D7%A4%D7%90%D7%A0%D7%99-%D7%A2%D7%96%D7%99%D7%96/", "https://rmc-med.co.il/doctors/%D7%A2%D7%91%D7%90%D7%A1%D7%99-%D7%A2%D7%A0%D7%90%D7%9F/"]</t>
         </is>
       </c>
       <c r="R30" t="inlineStr"/>
@@ -2892,7 +2894,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>אליסף שמואל</t>
+          <t>אייל לוי</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2945,7 +2947,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>"אליסף שמואל" מרפאה פרטית</t>
+          <t>"אייל לוי" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2963,7 +2965,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_e_shmuel.aspx", "https://www.infomed.co.il/experts/151074/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%9E%D7%95%D7%90%D7%9C-%D7%90%D7%9C%D7%99%D7%A1%D7%A3/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%9C%D7%95%D7%99/", "https://rmc-med.co.il/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%90%D7%AA%D7%A8/", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/", "https://rmc-med.co.il/about/", "https://rmc-med.co.il/management/", "https://rmc-med.co.il/contact/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%9C%D7%95%D7%99/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjcxNDAiLCJ0b2dnbGUiOmZhbHNlfQ%3D%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%9C%D7%95%D7%99/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%95%D7%A1%D7%99%D7%9D-%D7%90%D7%91%D7%95-%D7%A0%D7%A1%D7%A8%D7%94/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%97%D7%95%D7%A1%D7%90%D7%9D-%D7%A0%D7%A1%D7%90%D7%A8/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%A8%D7%9F-%D7%9C%D7%99%D7%9F/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%9C%D7%95%D7%9F-%D7%9E%D7%A9%D7%99%D7%97/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%A0%D7%90%D7%93%D7%99-%D7%96%D7%9C%D7%99%D7%A6%D7%A0%D7%A7%D7%95/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%9B%D7%94%D7%9F-%D7%9E%D7%99%D7%9B%D7%90%D7%9C/", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjcxNDAiLCJ0b2dnbGUiOmZhbHNlfQ%3D%3D", "https://rmc-med.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%99%D7%90-%D7%A8%D7%95%D7%91%D7%99%D7%9F/", "https://rmc-med.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%95%D7%94%D7%A0%D7%90-%D7%A0%D7%99%D7%93%D7%90%D7%9C/", "https://rmc-med.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%95%D7%A4%D7%90%D7%A0%D7%99-%D7%A2%D7%96%D7%99%D7%96/", "https://rmc-med.co.il/doctors/%D7%A2%D7%91%D7%90%D7%A1%D7%99-%D7%A2%D7%A0%D7%90%D7%9F/", "https://www.infomed.co.il/experts/151027/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
         </is>
       </c>
       <c r="R31" t="inlineStr"/>
@@ -2974,7 +2976,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>אליעזר הורנשטיין</t>
+          <t>איילת גדרון אבדיק</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3027,7 +3029,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>"אליעזר הורנשטיין" יילוד גינקולוג</t>
+          <t>"איילת גדרון אבדיק" מרפאה פרטית</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3045,7 +3047,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/75662/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://medpage.co.il/doctors/%D7%90%D7%9C%D7%99%D7%A2%D7%96%D7%A8-%D7%94%D7%95%D7%A8%D7%A0%D7%A9%D7%98%D7%99%D7%99%D7%9F-424/", "https://www.facebook.com/israelshealthwebsite/", "https://medpage.co.il/search-doctors/", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%99%D7%99%D7%9C%D7%95%D7%93+%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%94+%D7%A4%D7%A0%D7%99%D7%9E%D7%99%D7%AA", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%99%D7%9C%D7%93%D7%99%D7%9D", "https://medpage.co.il/search-doctors/?exp=%D7%A4%D7%A1%D7%99%D7%9B%D7%99%D7%90%D7%98%D7%A8%D7%99%D7%94", "https://medpage.co.il/about/", "https://medpage.co.il/contact/", "https://medpage.co.il/search-doctors/?view=exps-index", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99-%D7%91%D7%9F-%D7%94%D7%A8%D7%95%D7%A9-114/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%91%D7%99%D7%AA-%D7%9B%D7%94%D7%9F-9839633/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%A0%D7%A2%D7%9D-%D7%A9%D7%95%D7%A4%D7%A8-15141/", "https://medpage.co.il/doctors/15962-%D7%90%D7%91%D7%A0%D7%A8-%D7%A8%D7%A9%D7%A3-359/", "https://medpage.co.il/doctors/%D7%90%D7%94%D7%95%D7%93-%D7%93%D7%A8%D7%95%D7%A7%D7%A8-10916/", "https://medpage.co.il/doctors/78924-%D7%9E%D7%A8%D7%99%D7%9D-%D7%9E%D7%A4%D7%A8%D7%A2-9589571/", "https://medpage.co.il/doctors/%D7%A6%D7%99%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%A1%D7%91%D7%A8%D7%92-2313046/", "https://medpage.co.il/doctors/60281-%D7%9C%D7%99%D7%93%D7%99%D7%94-%D7%91%D7%9C%D7%9B%D7%A8-18287/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%93%D7%A8%D7%95%D7%9F-%D7%90%D7%91%D7%93%D7%99%D7%A7-%D7%90%D7%99%D7%99%D7%9C%D7%AA/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://www.infomed.co.il/experts/145230/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
         </is>
       </c>
       <c r="R32" t="inlineStr"/>
@@ -3056,7 +3058,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>אלכסנדר אבריאנוב</t>
+          <t>איליה בנימינוב</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3109,7 +3111,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>"אלכסנדר אבריאנוב" יילוד גינקולוג</t>
+          <t>"איליה בנימינוב" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3127,7 +3129,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אלכסנדר-אבריאנוב", "https://www.infomed.co.il/experts/75696/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.beok.co.il/doctors/Doctors-127644/", "https://www.doctorita.co.il/experts/133964", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors", "https://www.vimed.co.il/users/efc1a3ff-b730-499a-8e11-9ac7d92f35a2", "https://www.vimed.co.il/users", "https://www.vimed.co.il/users/daf4127d-8d7f-4fc5-ae39-67b74bc8ef26", "https://www.vimed.co.il/users/9d1ac106-2ead-4857-aa76-83aea36ab54d", "https://www.vimed.co.il/users/e4bd4091-5d6b-42bb-ad32-3f9afaf56942", "https://www.vimed.co.il/users/017527f8-a362-451c-ad8f-3a446eca6ef1", "https://www.vimed.co.il/users/150a8d2e-2ec4-47b7-8bb4-f1b0d6cbe3ea", "https://www.infomed.co.il/expertsresults/neonatal-and-gynecology/all_subspecialities/elat/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/74906/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.doctorita.co.il/experts/96512", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors"]</t>
         </is>
       </c>
       <c r="R33" t="inlineStr"/>
@@ -3138,7 +3140,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>אלכסנדר ברנוב</t>
+          <t>אילן גל</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3191,7 +3193,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>"אלכסנדר ברנוב" יילוד גינקולוג</t>
+          <t>"אילן גל" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3209,7 +3211,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/75765/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.doctorita.co.il/experts/123009", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors", "https://findoctor.co.il/אלכסנדר-ברנוב-נשים-גינקולוגיה/", "https://www.beok.co.il/doctors/Doctors-126912/"]</t>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/135371/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%9C%D7%9F-%D7%92%D7%9C-12279/", "https://www.facebook.com/israelshealthwebsite/", "https://medpage.co.il/search-doctors/", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%99%D7%99%D7%9C%D7%95%D7%93+%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%94+%D7%A4%D7%A0%D7%99%D7%9E%D7%99%D7%AA", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%99%D7%9C%D7%93%D7%99%D7%9D", "https://medpage.co.il/search-doctors/?exp=%D7%A4%D7%A1%D7%99%D7%9B%D7%99%D7%90%D7%98%D7%A8%D7%99%D7%94", "https://medpage.co.il/about/", "https://medpage.co.il/contact/", "https://medpage.co.il/search-doctors/?view=exps-index", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99-%D7%91%D7%9F-%D7%94%D7%A8%D7%95%D7%A9-114/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%91%D7%99%D7%AA-%D7%9B%D7%94%D7%9F-9839633/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%A0%D7%A2%D7%9D-%D7%A9%D7%95%D7%A4%D7%A8-15141/", "https://medpage.co.il/doctors/15962-%D7%90%D7%91%D7%A0%D7%A8-%D7%A8%D7%A9%D7%A3-359/", "https://medpage.co.il/doctors/%D7%90%D7%94%D7%95%D7%93-%D7%93%D7%A8%D7%95%D7%A7%D7%A8-10916/", "https://medpage.co.il/doctors/78924-%D7%9E%D7%A8%D7%99%D7%9D-%D7%9E%D7%A4%D7%A8%D7%A2-9589571/", "https://medpage.co.il/doctors/%D7%A6%D7%99%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%A1%D7%91%D7%A8%D7%92-2313046/", "https://medpage.co.il/doctors/60281-%D7%9C%D7%99%D7%93%D7%99%D7%94-%D7%91%D7%9C%D7%9B%D7%A8-18287/"]</t>
         </is>
       </c>
       <c r="R34" t="inlineStr"/>
@@ -3220,7 +3222,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>אלכסנדר פינליס</t>
+          <t>אילן הלוי</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3273,7 +3275,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>"אלכסנדר פינליס" מרפאה פרטית</t>
+          <t>"אילן הלוי" יילוד גינקולוג</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3291,10 +3293,3536 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/94151/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/63526110/", "https://www.doctors.co.il/websiteinfo/join-us/", "https://www.doctors.co.il/websiteinfo/terms/", "https://www.doctors.co.il/dr-search/israel/", "https://www.doctors.co.il/websiteinfo/about-us/", "https://www.doctors.co.il/websiteinfo/contact-us/", "https://www.doctors.co.il/", "https://www.doctors.co.il/medical-info/gynecology/", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1345", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1342", "https://www.doctors.co.il/dr-search/dental-clinics/israel/", "https://www.doctors.co.il/dr-search/health-clinics/israel/", "https://www.doctors.co.il/dr-search/clinical-psychologists/israel/", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1", "https://www.doctors.co.il/expert/ent-doctors/5877660/", "https://www.doctors.co.il/medical-info/all/", "https://www.doctors.co.il/all/", "https://www.doctors.co.il/bloodtest/", "https://www.doctors.co.il/cdn-cgi/l/email-protection#6801060e07280c070b1c071a1b460b07460104"]</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>אילן זיו</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>"אילן זיו" מרפאה פרטית</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=88C25B12-47A3-419A-9896-9F18AF9C6455", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=UcczKurRobDx5DacgIA3gYW4Sh0U2pSg0CT0/Hkf9PBZyNpVl1WWWXm1I84hp75jWpoPY1eFHsIRhI1QUEKYcA==", "http://www.maccabi4u.co.il/", "https://serguide.maccabi4u.co.il/heb/doctors/?SearchText=%D7%96%D7%99%D7%95%20%D7%90%D7%99%D7%9C%D7%9F", "https://serguide.maccabi4u.co.il/heb/doctors/", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=8&amp;ProviderID=52249612&amp;ProviderProfession=1&amp;docClinic=1425&amp;Service=1&amp;NewObjectId=61004302&amp;NewObjectType=S&amp;NewPerNr=90001609&amp;ol1=61004302&amp;ol2=S&amp;ol3=90001609&amp;beginDate=2026-08-31T20:01:49&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.infomed.co.il/experts/93842/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%96%D7%99%D7%95-%D7%90%D7%99%D7%9C%D7%9F/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>5</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>אילן שוורץ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>"אילן שוורץ" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/93501/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%95%D7%95%D7%A8%D7%A5-%D7%90%D7%99%D7%9C%D7%9F/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>אינה בלייכר</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>"אינה בלייכר" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/147166/", "https://www.helaclinic.com/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/experts/147166/#clinics", "https://www.infomed.co.il/experts/147166/#about", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://docsrated.com/doctors/אינה-בלייכר", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%91%D7%9C%D7%99%D7%99%D7%9B%D7%A8-%D7%90%D7%99%D7%A0%D7%94/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>5</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>אירינה ליטוין</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>"אירינה ליטוין" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/93929/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%9C%D7%99%D7%98%D7%95%D7%99%D7%9F-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>5</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>איריס אוהל שני</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>"איריס אוהל שני" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/151083/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%95%D7%94%D7%9C-%D7%A9%D7%A0%D7%99-%D7%90%D7%99%D7%A8%D7%99%D7%A1/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>5</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>איתן מרדכי</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>"איתן מרדכי" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>[{"email": "info@medico.co.il", "confidence": 75, "source_url": "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%AA%D7%9F-%D7%9E%D7%A8%D7%93%D7%9B%D7%99/", "evidence": "info@medico.co.il", "matched_query": "\"איתן מרדכי\" יילוד גינקולוג", "extraction_method": "mailto"}]</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%AA%D7%9F-%D7%9E%D7%A8%D7%93%D7%9B%D7%99/", "https://www.medico.co.il/%D7%AA%D7%A0%D7%90%D7%99-%D7%A9%D7%99%D7%9E%D7%95%D7%A9-%D7%91%D7%90%D7%AA%D7%A8-%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-medico-%D7%9C%D7%94%D7%9C%D7%9F-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/", "https://www.medico.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%98%D7%9C-%D7%9E%D7%93%D7%99%D7%A7%D7%95/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/", "https://www.medico.co.il/doctors/specialization/%D7%99%D7%99%D7%9C%D7%95%D7%93-%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/city/%D7%A8%D7%90%D7%A9%D7%95%D7%9F-%D7%9C%D7%A6%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%99%D7%A7%D7%99-%D7%91%D7%91%D7%99%D7%99%D7%91/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%99%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8%D7%90/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%94%D7%93%D7%A8-%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99/", "https://www.medico.co.il/doctors/%D7%A4%D7%A8%D7%95%D7%A4-%D7%9E%D7%A8%D7%93%D7%9B%D7%99-%D7%A7%D7%A8%D7%9E%D7%A8/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%A1%D7%91%D7%99%D7%95%D7%9F/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94-%D7%99%D7%A4%D7%99%D7%9E%D7%95%D7%91/", "https://www.medico.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://docsrated.com/doctors/איתן-מרדכי", "https://www.infomed.co.il/experts/145112/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/experts/145112/#clinics", "https://www.infomed.co.il/experts/145112/#about", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>אלה אופיר</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>"אלה אופיר" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/94616/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://medpage.co.il/doctors/%D7%90%D7%9C%D7%94-%D7%90%D7%95%D7%A4%D7%99%D7%A8-41552/", "https://www.facebook.com/israelshealthwebsite/", "https://medpage.co.il/search-doctors/", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%99%D7%99%D7%9C%D7%95%D7%93+%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%94+%D7%A4%D7%A0%D7%99%D7%9E%D7%99%D7%AA", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%99%D7%9C%D7%93%D7%99%D7%9D", "https://medpage.co.il/search-doctors/?exp=%D7%A4%D7%A1%D7%99%D7%9B%D7%99%D7%90%D7%98%D7%A8%D7%99%D7%94", "https://medpage.co.il/about/", "https://medpage.co.il/contact/", "https://medpage.co.il/search-doctors/?view=exps-index", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99-%D7%91%D7%9F-%D7%94%D7%A8%D7%95%D7%A9-114/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%91%D7%99%D7%AA-%D7%9B%D7%94%D7%9F-9839633/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%A0%D7%A2%D7%9D-%D7%A9%D7%95%D7%A4%D7%A8-15141/", "https://medpage.co.il/doctors/15962-%D7%90%D7%91%D7%A0%D7%A8-%D7%A8%D7%A9%D7%A3-359/", "https://medpage.co.il/doctors/%D7%90%D7%94%D7%95%D7%93-%D7%93%D7%A8%D7%95%D7%A7%D7%A8-10916/", "https://medpage.co.il/doctors/78924-%D7%9E%D7%A8%D7%99%D7%9D-%D7%9E%D7%A4%D7%A8%D7%A2-9589571/", "https://medpage.co.il/doctors/%D7%A6%D7%99%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%A1%D7%91%D7%A8%D7%92-2313046/", "https://medpage.co.il/doctors/60281-%D7%9C%D7%99%D7%93%D7%99%D7%94-%D7%91%D7%9C%D7%9B%D7%A8-18287/"]</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>אלה אפשטיין</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>"אלה אפשטיין" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אלה-אפשטיין", "https://www.infomed.co.il/experts/75378/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A4%D7%A9%D7%98%D7%99%D7%99%D7%9F-%D7%90%D7%9C%D7%94/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>5</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>אלי מימון</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>"אלי מימון" מרפאה פרטית</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://drlevinger.co.il/doctor/%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9C%D7%99-%D7%9E%D7%99%D7%9E%D7%95%D7%9F/", "https://drlevinger.co.il/site-map/", "https://drlevinger.co.il/procedure/keratoconus/keratoconus-contact-lenses/", "https://drlevinger.co.il/our-doctors/", "https://drlevinger.co.il/our-doctors/?_doctor_proc=8099", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2506", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2548", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2542", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2559", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2546", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2553", "https://drlevinger.co.il/our-doctors/?_doctor_sector=2557", "https://drlevinger.co.il/our-doctors/?_doctor_sector=8999", "https://drlevinger.co.il/our-doctors/?_doctor_center=211", "https://www.infomed.co.il/experts/91609/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>5</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>אליאס חדוות</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>"אליאס חדוות" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/147487/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>אליהו וולפסון</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>"אליהו וולפסון" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/152737/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%95%D7%95%D7%9C%D7%A4%D7%A1%D7%95%D7%9F-%D7%90%D7%9C%D7%99%D7%94%D7%95/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>אלינה וילקין</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>"אלינה וילקין" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%95%D7%99%D7%9C%D7%A7%D7%99%D7%9F-%D7%90%D7%9C%D7%99%D7%A0%D7%94/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=YdbE87dpf9Ckia930mxf1ByQknzhT7k/tn8Ln7N4YoBolPMNy3OVzmIL9oNHADHeuUYMi879LXTvVsVHi9t2Kg==", "http://www.maccabi4u.co.il/", "https://serguide.maccabi4u.co.il/heb/doctors/?SearchText=%D7%95%D7%99%D7%9C%D7%A7%D7%99%D7%9F%20%D7%90%D7%9C%D7%99%D7%A0%D7%94", "https://serguide.maccabi4u.co.il/heb/doctors/", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=8&amp;ProviderID=308924687&amp;ProviderProfession=1&amp;docClinic=34619&amp;Service=1&amp;NewObjectId=61007675&amp;NewObjectType=S&amp;NewPerNr=90000994&amp;ol1=61007675&amp;ol2=S&amp;ol3=90000994&amp;beginDate=2026-08-31T21:54:25&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.infomed.co.il/experts/93782/", "https://darkred-ram-504111.hostingersite.com/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/experts/93782/#clinics", "https://www.infomed.co.il/experts/93782/#about", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>5</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>אליסף שמואל</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>"אליסף שמואל" מרפאה פרטית</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_e_shmuel.aspx", "https://www.infomed.co.il/experts/151074/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%9E%D7%95%D7%90%D7%9C-%D7%90%D7%9C%D7%99%D7%A1%D7%A3/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>5</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>אליעזר הורנשטיין</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>"אליעזר הורנשטיין" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/75662/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://medpage.co.il/doctors/%D7%90%D7%9C%D7%99%D7%A2%D7%96%D7%A8-%D7%94%D7%95%D7%A8%D7%A0%D7%A9%D7%98%D7%99%D7%99%D7%9F-424/", "https://www.facebook.com/israelshealthwebsite/", "https://medpage.co.il/search-doctors/", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%99%D7%99%D7%9C%D7%95%D7%93+%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%94+%D7%A4%D7%A0%D7%99%D7%9E%D7%99%D7%AA", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%99%D7%9C%D7%93%D7%99%D7%9D", "https://medpage.co.il/search-doctors/?exp=%D7%A4%D7%A1%D7%99%D7%9B%D7%99%D7%90%D7%98%D7%A8%D7%99%D7%94", "https://medpage.co.il/about/", "https://medpage.co.il/contact/", "https://medpage.co.il/search-doctors/?view=exps-index", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99-%D7%91%D7%9F-%D7%94%D7%A8%D7%95%D7%A9-114/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%91%D7%99%D7%AA-%D7%9B%D7%94%D7%9F-9839633/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%A0%D7%A2%D7%9D-%D7%A9%D7%95%D7%A4%D7%A8-15141/", "https://medpage.co.il/doctors/15962-%D7%90%D7%91%D7%A0%D7%A8-%D7%A8%D7%A9%D7%A3-359/", "https://medpage.co.il/doctors/%D7%90%D7%94%D7%95%D7%93-%D7%93%D7%A8%D7%95%D7%A7%D7%A8-10916/", "https://medpage.co.il/doctors/78924-%D7%9E%D7%A8%D7%99%D7%9D-%D7%9E%D7%A4%D7%A8%D7%A2-9589571/", "https://medpage.co.il/doctors/%D7%A6%D7%99%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%A1%D7%91%D7%A8%D7%92-2313046/", "https://medpage.co.il/doctors/60281-%D7%9C%D7%99%D7%93%D7%99%D7%94-%D7%91%D7%9C%D7%9B%D7%A8-18287/"]</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>5</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>אלכסנדר אבריאנוב</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>"אלכסנדר אבריאנוב" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אלכסנדר-אבריאנוב", "https://www.infomed.co.il/experts/75696/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.beok.co.il/doctors/Doctors-127644/", "https://www.doctorita.co.il/experts/133964", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors", "https://www.vimed.co.il/users/efc1a3ff-b730-499a-8e11-9ac7d92f35a2", "https://www.vimed.co.il/users", "https://www.vimed.co.il/users/daf4127d-8d7f-4fc5-ae39-67b74bc8ef26", "https://www.vimed.co.il/users/9d1ac106-2ead-4857-aa76-83aea36ab54d", "https://www.vimed.co.il/users/e4bd4091-5d6b-42bb-ad32-3f9afaf56942", "https://www.vimed.co.il/users/017527f8-a362-451c-ad8f-3a446eca6ef1", "https://www.vimed.co.il/users/150a8d2e-2ec4-47b7-8bb4-f1b0d6cbe3ea", "https://www.infomed.co.il/expertsresults/neonatal-and-gynecology/all_subspecialities/elat/"]</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>5</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>אלכסנדר ברנוב</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>"אלכסנדר ברנוב" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/75765/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.doctorita.co.il/experts/123009", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors", "https://findoctor.co.il/אלכסנדר-ברנוב-נשים-גינקולוגיה/", "https://www.beok.co.il/doctors/Doctors-126912/"]</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>5</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>אלכסנדר פינליס</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>"אלכסנדר פינליס" מרפאה פרטית</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
           <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/75842/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://docsrated.com/doctors/אלכסנדר-פינליס", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%99%D7%A0%D7%9C%D7%99%D7%A1-%D7%90%D7%9C%D7%9B%D7%A1%D7%A0%D7%93%D7%A8/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>5</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>אלכסנדר פישמן</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>"אלכסנדר פישמן" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/151020/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://docsrated.com/doctors/אלכסנדר-פישמן", "https://www.doctorita.co.il/experts/99543", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors", "https://www.vimed.co.il/users/049c161c-4002-41b7-b93a-b79930bfc889", "https://www.vimed.co.il/users", "https://www.vimed.co.il/users/daf4127d-8d7f-4fc5-ae39-67b74bc8ef26", "https://www.vimed.co.il/users/9d1ac106-2ead-4857-aa76-83aea36ab54d", "https://www.vimed.co.il/users/e4bd4091-5d6b-42bb-ad32-3f9afaf56942", "https://www.vimed.co.il/users/017527f8-a362-451c-ad8f-3a446eca6ef1", "https://www.vimed.co.il/users/150a8d2e-2ec4-47b7-8bb4-f1b0d6cbe3ea", "https://www.infomed.co.il/expertsresults/neonatal-and-gynecology/all_subspecialities/afula/", "https://www.infomed.co.il/expertsresults/neonatal-and-gynecology/all_subspecialities/all_areas/", "https://knowmore.co.il/doctors/אלכסנדר-פישמן/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/afula/", "https://www.doctorita.co.il/gynecologic-ultrasound/north/eilabun"]</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>5</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>אלכסנדר פרי</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>"אלכסנדר פרי" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/151050/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.doctorita.co.il/experts/99560", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors", "https://docsrated.com/doctors/אלכס-פרי", "https://www.beok.co.il/doctors/Doctors-122982/", "https://www.doctorim.co.il/doctor-21283/דר-אלכסנדר-פרי/מומחה-יילוד-וגניקולוגיה", "https://www.doctorim.co.il/SearchBySpecialty/פריון/all/all/", "https://www.doctorim.co.il/SearchBySpecialty/יילוד+וגניקולוגיה/מעיליא/all/", "https://www.doctorim.co.il/SearchBySpecialty/יילוד+וגניקולוגיה/כאוכב+אל-היג`א/all/", "https://www.beok.co.il/index/", "https://www.infomed.co.il/expertsresults/neonatal-and-gynecology/all_subspecialities/nahariyya/", "https://www.infomed.co.il/expertsresults/neonatal-and-gynecology/all_subspecialities/all_areas/", "https://www.doctorim.co.il/SearchBySpecialty/יילוד+וגניקולוגיה/אום+אל-פחם/all/", "https://www.doctorim.co.il/SearchBySpecialty/יילוד+וגניקולוגיה/קיסריה/all/"]</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>5</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>אמיר ויסמן</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>"אמיר ויסמן" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/76009/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%95%D7%99%D7%A1%D7%9E%D7%9F-%D7%90%D7%9E%D7%99%D7%A8/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>5</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>אמיר מישל</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>"אמיר מישל" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/76017/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://docsrated.com/doctors/אמיר-מישל", "https://medpage.co.il/doctors/%D7%90%D7%9E%D7%99%D7%A8-%D7%9E%D7%99%D7%A9%D7%9C-214/", "https://www.facebook.com/israelshealthwebsite/", "https://medpage.co.il/search-doctors/", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%99%D7%99%D7%9C%D7%95%D7%93+%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%94+%D7%A4%D7%A0%D7%99%D7%9E%D7%99%D7%AA", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%99%D7%9C%D7%93%D7%99%D7%9D", "https://medpage.co.il/search-doctors/?exp=%D7%A4%D7%A1%D7%99%D7%9B%D7%99%D7%90%D7%98%D7%A8%D7%99%D7%94", "https://medpage.co.il/about/", "https://medpage.co.il/contact/", "https://medpage.co.il/search-doctors/?view=exps-index", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99-%D7%91%D7%9F-%D7%94%D7%A8%D7%95%D7%A9-114/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%91%D7%99%D7%AA-%D7%9B%D7%94%D7%9F-9839633/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%A0%D7%A2%D7%9D-%D7%A9%D7%95%D7%A4%D7%A8-15141/", "https://medpage.co.il/doctors/15962-%D7%90%D7%91%D7%A0%D7%A8-%D7%A8%D7%A9%D7%A3-359/", "https://medpage.co.il/doctors/%D7%90%D7%94%D7%95%D7%93-%D7%93%D7%A8%D7%95%D7%A7%D7%A8-10916/", "https://medpage.co.il/doctors/78924-%D7%9E%D7%A8%D7%99%D7%9D-%D7%9E%D7%A4%D7%A8%D7%A2-9589571/", "https://medpage.co.il/doctors/%D7%A6%D7%99%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%A1%D7%91%D7%A8%D7%92-2313046/", "https://medpage.co.il/doctors/60281-%D7%9C%D7%99%D7%93%D7%99%D7%94-%D7%91%D7%9C%D7%9B%D7%A8-18287/"]</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>5</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>אמיר פרויד</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>"אמיר פרויד" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/151035/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.doctorita.co.il/experts/45112", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors", "https://docsrated.com/doctors/אמיר-פרויד", "https://www.bgu.ac.il/people/amirfre/", "https://www.freud.co.il/about-1", "https://www.bgu.ac.il/en/people/amirfre/", "https://www.freud.co.il/", "https://www.facebook.com/groups/182189369721678/posts/1134603814480224/", "https://www.medreviews.co.il/search/treatment/ivf/north/acre", "https://www.medreviews.co.il/search/treatment/female-infertility/south/omer", "https://www.medreviews.co.il/search/treatment/ivf/south/meitar", "https://www.medreviews.co.il/search/treatment/gynecology-fertility/south/arad", "https://www.medreviews.co.il/search/treatment/ivf/north/kiryat-yam", "https://www.medreviews.co.il/search/treatment/female-infertility/south/lehavim", "https://www.medreviews.co.il/search/treatment/male-infertility-pharmacological-treatment/north/kfar-yasif"]</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>5</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>אמיר שלו</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>"אמיר שלו" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://medpage.co.il/doctors/%D7%90%D7%9E%D7%99%D7%A8-%D7%A9%D7%9C%D7%95-7651/", "https://www.facebook.com/israelshealthwebsite/", "https://medpage.co.il/search-doctors/", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%99%D7%99%D7%9C%D7%95%D7%93+%D7%95%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%94+%D7%A4%D7%A0%D7%99%D7%9E%D7%99%D7%AA", "https://medpage.co.il/search-doctors/?exp=%D7%A8%D7%A4%D7%95%D7%90%D7%AA+%D7%99%D7%9C%D7%93%D7%99%D7%9D", "https://medpage.co.il/search-doctors/?exp=%D7%A4%D7%A1%D7%99%D7%9B%D7%99%D7%90%D7%98%D7%A8%D7%99%D7%94", "https://medpage.co.il/about/", "https://medpage.co.il/contact/", "https://medpage.co.il/search-doctors/?view=exps-index", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99-%D7%91%D7%9F-%D7%94%D7%A8%D7%95%D7%A9-114/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%91%D7%99%D7%AA-%D7%9B%D7%94%D7%9F-9839633/", "https://medpage.co.il/doctors/%D7%90%D7%91%D7%99%D7%A0%D7%A2%D7%9D-%D7%A9%D7%95%D7%A4%D7%A8-15141/", "https://medpage.co.il/doctors/15962-%D7%90%D7%91%D7%A0%D7%A8-%D7%A8%D7%A9%D7%A3-359/", "https://medpage.co.il/doctors/%D7%90%D7%94%D7%95%D7%93-%D7%93%D7%A8%D7%95%D7%A7%D7%A8-10916/", "https://medpage.co.il/doctors/78924-%D7%9E%D7%A8%D7%99%D7%9D-%D7%9E%D7%A4%D7%A8%D7%A2-9589571/", "https://medpage.co.il/doctors/%D7%A6%D7%99%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%A1%D7%91%D7%A8%D7%92-2313046/", "https://medpage.co.il/doctors/60281-%D7%9C%D7%99%D7%93%D7%99%D7%94-%D7%91%D7%9C%D7%9B%D7%A8-18287/", "https://www.infomed.co.il/experts/151069/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>5</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>אמנון דויד</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>"אמנון דויד" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/76050/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%99%D7%93-%D7%90%D7%9E%D7%A0%D7%95%D7%9F/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>5</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>אמנון עמית</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>"אמנון עמית" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/89367/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A2%D7%9E%D7%99%D7%AA-%D7%90%D7%9E%D7%A0%D7%95%D7%9F/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>5</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>אמנון רופא</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>"אמנון רופא" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/95248/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%95%D7%A4%D7%90-%D7%90%D7%9E%D7%A0%D7%95%D7%9F/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>5</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>אנדרי קריינין</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>"אנדרי קריינין" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/151054/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctors.assuta.co.il/doctor/andrey-kreinin-118230"]</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>5</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>אנה זיידין</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>"אנה זיידין" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>[{"email": "info@medreviews.co.il", "confidence": 75, "source_url": "https://www.medreviews.co.il/contact-us", "evidence": "MedReviews - יצירת קשר יצירת קשר קשר עם MedReviews פנחס ספיר 8, נס ציונה 055-4548554 info@medreviews.co.il Loading... מלאו  פרטים ונציג שלנו יצור עמך קשר בהקדם שם * שם * טלפון * טלפון * אימייל אימייל הערות * הערות * בהשארת פרטים אני מאשר כי אני מעוניין לקבל התקשרות חוזרת מהמרפאה, וכן מאשר את תנאי השימוש ומדיניות הפרטיות באתר MedReviews. אני מעוניין לקבל דברי פרסומת כהגדרתם בחוק מ-MedReviews ומהמרפאה ובאפשרותי לחזור בי מהסכמה זו בכל עת. שליחה אודות MedReviews היא אינדקס לרופאים המתקדם והאמין בישר", "matched_query": "\"אנה זיידין\" יילוד גינקולוג", "extraction_method": "text"}]</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/151056/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.medreviews.co.il/provider/dr-zaidin-anna", "https://www.waze.com/live-map/directions?navigate=yes&amp;utm_campaign=default&amp;utm_source=waze_website&amp;utm_medium=lm_share_location&amp;to=place.EiZIYUJhcnplbCBTdCAxMTgsIFRlbCBBdml2LVlhZm8sIElzcmFlbCIwEi4KFAoSCfk229nqSR0VEep0X3t0RUixEHYqFAoSCQOjGX6USR0VEZHCi-bi7pH4", "https://dr-zaidin.co.il/", "https://www.medreviews.co.il/provider/dr-zaidin-anna#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://www.medreviews.co.il/search/eye-doctor", "https://www.medreviews.co.il/provider/dr-tal-kfir#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-nasser-orwa#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-spierer-oriel#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-feldman-ilan#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-douieb-joseph#contact-doctor-section", "https://www.medreviews.co.il/provider/medical-village", "https://www.medreviews.co.il/provider/medical-village#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-barbara-adel#contact-doctor-section", "https://www.medreviews.co.il/provider/prof-lifshitz-tova#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-socea-sergiu#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-guttman-sharon#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-rock-oded#contact-doctor-section"]</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>5</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>אנטולי שפרברג</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>"אנטולי שפרברג" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://docsrated.com/doctors/אנטולי-שפרברג", "https://www.infomed.co.il/experts/76210/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%A4%D7%A8%D7%91%D7%A8%D7%92-%D7%90%D7%A0%D7%98%D7%95%D7%9C%D7%99/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>5</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>אניטה סילבר</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>"אניטה סילבר" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%99%D7%9C%D7%91%D7%A8-%D7%90%D7%A0%D7%99%D7%98%D7%94/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://docsrated.com/doctors/אניטה-סילבר", "https://www.infomed.co.il/experts/93510/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>5</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>אניס כלדאוי</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>"אניס כלדאוי" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.elishahospital.com/%D7%93%D7%A8-%D7%90%D7%A0%D7%99%D7%A1-%D7%9B%D7%9C%D7%93%D7%90%D7%95%D7%99/", "https://www.elishahospital.com/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%90%D7%AA%D7%A8/", "https://www.elishahospital.com/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/", "https://www.elishahospital.com/about/", "https://www.elishahospital.com/%D7%9E%D7%A8%D7%A4%D7%90%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%90%D7%A9%D7%94/", "https://www.elishahospital.com/contact/", "https://www.elishahospital.com/%D7%93%D7%A8-%D7%90%D7%A0%D7%99%D7%A1-%D7%9B%D7%9C%D7%93%D7%90%D7%95%D7%99/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://www.elishahospital.com/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://www.elishahospital.com/about/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://www.elishahospital.com/%D7%9E%D7%A8%D7%A4%D7%90%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%90%D7%A9%D7%94/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://www.elishahospital.com/contact/#elementor-action%3Aaction%3Dpopup%3Aopen%26settings%3DeyJpZCI6IjE3MzE4IiwidG9nZ2xlIjpmYWxzZX0%3D", "https://www.elishahospital.com/cdn-cgi/l/email-protection#670a02030e04064a04060b0b270a02030e0406490408490e0b", "https://www.infomed.co.il/experts/150777/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>5</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>אסתר מאור שגיא</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>"אסתר מאור שגיא" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/144349/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/80304800/", "https://www.doctors.co.il/websiteinfo/join-us/", "https://www.doctors.co.il/websiteinfo/terms/", "https://www.doctors.co.il/dr-search/israel/", "https://www.doctors.co.il/websiteinfo/about-us/", "https://www.doctors.co.il/websiteinfo/contact-us/", "https://www.doctors.co.il/", "https://www.doctors.co.il/medical-info/gynecology/", "https://www.doctors.co.il/forum-2065/message-1410731/", "https://www.doctors.co.il/forum-2065/message-1410551/", "https://www.doctors.co.il/forum-2065/message-1410512/", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1345", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1342", "https://www.doctors.co.il/dr-search/dental-clinics/israel/", "https://www.doctors.co.il/dr-search/health-clinics/israel/", "https://www.doctors.co.il/dr-search/clinical-psychologists/israel/", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1", "https://www.doctors.co.il/expert/ent-doctors/5877660/", "https://www.doctors.co.il/medical-info/all/", "https://www.doctors.co.il/all/"]</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>5</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>אפרים סיגלר</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>"אפרים סיגלר" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/76357/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=NRapZKaXseJXzIlbLJ8QVLajh7LQyZGQWUPAROIP1qSt5W43Sin9uJj6Ubotn5HjHzuySM+5RxayX8hP5IHQ6g==", "https://doctors.assuta.co.il/doctor/efraim-sigler-16737", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%99%D7%92%D7%9C%D7%A8-%D7%90%D7%A4%D7%A8%D7%99%D7%9D/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>5</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>אפרת ברנע לוי</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>"אפרת ברנע לוי" site:infomed.co.il</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/80316806/", "https://www.doctors.co.il/dr-search/obstetrics-and-gynecologists/aseret/", "https://www.doctors.co.il/websiteinfo/join-us/", "https://www.doctors.co.il/websiteinfo/terms/", "https://www.doctors.co.il/dr-search/israel/", "https://www.doctors.co.il/websiteinfo/about-us/", "https://www.doctors.co.il/websiteinfo/contact-us/", "https://www.doctors.co.il/", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1345", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1342", "https://www.doctors.co.il/dr-search/dental-clinics/israel/", "https://www.doctors.co.il/dr-search/health-clinics/israel/", "https://www.doctors.co.il/dr-search/clinical-psychologists/israel/", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1", "https://www.doctors.co.il/expert/ent-doctors/5877660/", "https://www.doctors.co.il/medical-info/all/", "https://www.doctors.co.il/all/", "https://www.doctors.co.il/bloodtest/", "https://www.doctors.co.il/cdn-cgi/l/email-protection#b7ded9d1d8f7d3d8d4c3d8c5c499d4d899dedb", "https://www.doctors.co.il/cdn-cgi/l/email-protection#84e1e0edf0ebf6c4e0ebe7f0ebf6f7aae7ebaaede8", "https://www.doctors.co.il/forum-4068/", "https://www.doctors.co.il/dr-search/obstetrics-and-gynecologists/kfar-ahim/", "https://www.doctors.co.il/dr-search/tzrifin/", "https://www.infomed.co.il/experts/149372/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>5</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>אפרת שפיגל</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>"אפרת שפיגל" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>[{"email": "info@medreviews.co.il", "confidence": 75, "source_url": "https://www.medreviews.co.il/contact-us", "evidence": "MedReviews - יצירת קשר יצירת קשר קשר עם MedReviews פנחס ספיר 8, נס ציונה 055-4548554 info@medreviews.co.il Loading... מלאו  פרטים ונציג שלנו יצור עמך קשר בהקדם שם * שם * טלפון * טלפון * אימייל אימייל הערות * הערות * בהשארת פרטים אני מאשר כי אני מעוניין לקבל התקשרות חוזרת מהמרפאה, וכן מאשר את תנאי השימוש ומדיניות הפרטיות באתר MedReviews. אני מעוניין לקבל דברי פרסומת כהגדרתם בחוק מ-MedReviews ומהמרפאה ובאפשרותי לחזור בי מהסכמה זו בכל עת. שליחה אודות MedReviews היא אינדקס לרופאים המתקדם והאמין בישר", "matched_query": "\"אפרת שפיגל\" יילוד גינקולוג", "extraction_method": "text"}]</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/149996/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://www.doctorita.co.il/experts/46707", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors", "https://www.bgu.ac.il/people/spiegele/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/spiegel-e.aspx", "https://www.bgu.ac.il/en/people/spiegele/", "https://www.esgyn.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.medreviews.co.il/provider/dr-spiegel-efrat", "https://www.esgyn.co.il/", "https://www.medreviews.co.il/provider/dr-spiegel-efrat#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://www.medreviews.co.il/search/eye-doctor", "https://www.medreviews.co.il/provider/dr-tal-kfir#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-nasser-orwa#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-spierer-oriel#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-feldman-ilan#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-douieb-joseph#contact-doctor-section", "https://www.medreviews.co.il/provider/medical-village", "https://www.medreviews.co.il/provider/medical-village#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-barbara-adel#contact-doctor-section", "https://www.medreviews.co.il/provider/prof-lifshitz-tova#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-socea-sergiu#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-guttman-sharon#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-rock-oded#contact-doctor-section"]</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>5</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>אראלה ברלב</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>"אראלה ברלב" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/93390/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=YZexjbbvtfL0cAmsjqe3PvbYUKkxhBrhnjPQNHEyulKoKE1eO8B4jj93jttt2yY0MplJnbgFc7oLe27sRQgYpA==", "http://www.maccabi4u.co.il/", "https://serguide.maccabi4u.co.il/heb/doctors/?SearchText=%D7%91%D7%A8%D7%9C%D7%91%20%D7%90%D7%A8%D7%90%D7%9C%D7%94", "https://serguide.maccabi4u.co.il/heb/doctors/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%91%D7%A8%D7%9C%D7%91-%D7%90%D7%A8%D7%90%D7%9C%D7%94/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>5</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ארז בן שם</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>"ארז בן שם" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/93645/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=723F9FDAD5033A972CF1F04C3A097A9EC3722CB7800DFEE66C9827FB44BFFBC0&amp;RequestId=00000000-0000-0000-0001-000000000153", "https://www.maccabi4u.co.il/kosher", "https://go.serguide.maccabi4u.co.il/heb/doctors/?SearchText=%D7%91%D7%9F-%D7%A9%D7%9D%20%D7%90%D7%A8%D7%96", "https://go.serguide.maccabi4u.co.il/heb/doctors/", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=8&amp;ProviderID=57659096&amp;ProviderProfession=1&amp;docClinic=34462&amp;Service=1&amp;NewObjectId=61005483&amp;NewObjectType=S&amp;NewPerNr=90003787&amp;ol1=61005483&amp;ol2=S&amp;ol3=90003787&amp;isKosher=1&amp;beginDate=2026-09-01T02:06:31&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%91%D7%9F-%D7%A9%D7%9D-%D7%90%D7%A8%D7%96/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>5</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>אריאל אוקסהורן</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>"אריאל אוקסהורן" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/76428/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%95%D7%A7%D7%A1%D7%94%D7%95%D7%A8%D7%9F-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>5</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>אריאל מני</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>"אריאל מני" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.mymc.co.il/doctors/prof-mani/", "https://www.infomed.co.il/experts/91805/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://docsrated.com/doctors/אריאל-מני", "https://www.arielmany.co.il/", "https://zap.dbusiness.co/js/accessibility.html", "https://www.arielmany.co.il/cdn-cgi/l/email-protection#1578747b6c55657a66613b6174603b74763b7c79", "https://www.doctors.co.il/expert/obstetrics-and-gynecologists/62952650/", "https://www.doctors.co.il/websiteinfo/join-us/", "https://www.doctors.co.il/websiteinfo/terms/", "https://www.doctors.co.il/dr-search/israel/", "https://www.doctors.co.il/websiteinfo/about-us/", "https://www.doctors.co.il/websiteinfo/contact-us/", "https://www.doctors.co.il/", "https://www.doctors.co.il/medical-info/gynecology/", "https://www.doctors.co.il/cdn-cgi/l/email-protection#7d420e081f17181e0940aae9aae3aae1aadbaae95daadfaaecaae8aad5aae75daae3aaedaad7aad55daaeeaae8aadaaae5aae8aad5aadc515daad9aad5aae8aad95b5e4e44465daaedaad5aae4aaedaae15daae3aaddaae45b1c100d461f12190440aad5aae8aad9aaedaae45daaefaae4aaddaadaaae8aae1aae8aaefaae4aae95daae8aae3aae4aae4aae1aaeeaae8aad75d55aaddaad4aae4aae0545d1509090d0e4752520a0a0a5319121e09120f0e531e125314115218050d180f0952121f0e0918090f141e0e501c1319501a0413181e1211121a140e090e524b4f44484f4b484d52", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1345", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1342", "https://www.doctors.co.il/dr-search/dental-clinics/israel/", "https://www.doctors.co.il/dr-search/health-clinics/israel/", "https://www.doctors.co.il/dr-search/clinical-psychologists/israel/", "https://www.doctors.co.il/doctors-search/filters/israel/?titleid=1", "https://www.doctors.co.il/expert/ent-doctors/5877660/", "https://www.doctors.co.il/medical-info/all/", "https://www.doctors.co.il/all/", "https://www.doctors.co.il/bloodtest/"]</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>5</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>אריה אליעזר הורביץ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>"אריה אליעזר הורביץ" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%94%D7%95%D7%A8%D7%91%D7%99%D7%A5-%D7%90%D7%A8%D7%99%D7%94-%D7%90%D7%9C%D7%99%D7%A2%D7%96%D7%A8/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/", "https://www.infomed.co.il/experts/76502/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/"]</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>5</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>אריה גינגולד</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>"אריה גינגולד" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/76497/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%99%D7%A0%D7%92%D7%95%D7%9C%D7%93-%D7%90%D7%A8%D7%99%D7%94/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>5</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>אריה ודס</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>cs@infomed.co.il</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://www.infomed.co.il/articles/4153/</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>אנו גאים לשתף פעולה עם קשת רחבה של גורמים מקצועיים שונים מתחום הרפואה, בהם רופאים/ות, מוסדות רפואיים, מכונים, מטפלים/ות, חברות ביטוח ועוד . פיתחנו מגוון כלים חכמים המותאמים לצורכי המפרסם כדי לשפר את המוניטין הדיגיטלי בפלטפורמות שונות. לבירור פרטים על הצטרפות לאינדקס cs@infomed.co.il מדיניות עריכת תוכן תהליך יצירת התכנים שלנו מוקפד ומדויק: התכנים מתבססים על מידע רפואי מהימן בלבד הנלקח מאנשי ונשות מקצוע מתחומי הרפואה הקונבנציונלית והמשלימה, לרבות רופאים ורופאות, רוקחים/ות ומטפלים מוסמכים, וכן על מ</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>"אריה ודס" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>mailto</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://www.infomed.co.il/experts/93466/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/all_areas/", "https://www.infomed.co.il/contentworlds/general-practitioners/articles/", "https://www.infomed.co.il/contactus/", "https://www.infomed.co.il/articles/4153/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/tel-aviv/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/south-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/shfela-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/hamerkaz/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/sharon-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/haifa-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/jerusalem-area/", "https://www.infomed.co.il/expertsresults/all_specialities/all_subspecialities/north-area/", "https://www.infomed.co.il/articles/7655/", "https://www.infomed.co.il/experts/153739/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%95%D7%93%D7%A1-%D7%90%D7%A8%D7%99%D7%94/", "https://doctorindex.co.il/", "https://doctorindex.co.il/about/", "https://doctorindex.co.il/details/", "https://doctorindex.co.il/%D7%97%D7%99%D7%A4%D7%95%D7%A9-%D7%9C%D7%A4%D7%99-%D7%94%D7%AA%D7%9E%D7%97%D7%95%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%A0%D7%9E%D7%A8%D7%A5-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%93%D7%97%D7%95%D7%A4%D7%94-%D7%9E%D7%A1%D7%9C%D7%95%D7%9C-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A0%D7%95%D7%99%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%99%D7%AA-%D7%99%D7%9C%D7%93%D7%99%D7%9D/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%A3-%D7%90%D7%95%D7%96%D7%9F-%D7%95%D7%92%D7%A8%D7%95%D7%9F/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9E%D7%97%D7%9C%D7%95%D7%AA-%D7%90%D7%90%D7%92-%D7%95%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%99%D7%AA-%D7%A8%D7%90/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%AA%D7%95%D7%A4%D7%93%D7%99%D7%AA/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%9B%D7%99%D7%A8%D7%95%D7%A8%D7%92%D7%99%D7%94-%D7%90%D7%95%D7%A8%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>5</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>איתמר זילברמן רון</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>info@medreviews.co.il</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>CLINIC_OR_ORGANIZATION</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://www.medreviews.co.il/contact-us</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>REVIEW_SHARED_EMAIL</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>MedReviews - יצירת קשר יצירת קשר קשר עם MedReviews פנחס ספיר 8, נס ציונה 055-4548554 info@medreviews.co.il Loading... מלאו  פרטים ונציג שלנו יצור עמך קשר בהקדם שם * שם * טלפון * טלפון * אימייל אימייל הערות * הערות * בהשארת פרטים אני מאשר כי אני מעוניין לקבל התקשרות חוזרת מהמרפאה, וכן מאשר את תנאי השימוש ומדיניות הפרטיות באתר MedReviews. אני מעוניין לקבל דברי פרסומת כהגדרתם בחוק מ-MedReviews ומהמרפאה ובאפשרותי לחזור בי מהסכמה זו בכל עת. שליחה אודות MedReviews היא אינדקס לרופאים המתקדם והאמין בישר</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>"איתמר זילברמן רון" יילוד גינקולוג</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>["https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e", "https://itamar-clinic.co.il/", "https://itamar-clinic.co.il/wp-content/uploads/2024/02/1.jpg", "https://itamar-clinic.co.il/wp-content/uploads/2024/02/6.jpg", "https://itamar-clinic.co.il/wp-content/uploads/2024/02/3.jpg", "https://itamar-clinic.co.il/wp-content/uploads/2024/02/5.jpg", "https://itamar-clinic.co.il/wp-content/uploads/2024/02/4.jpg", "https://www.medreviews.co.il/provider/dr-zilberman-ron-itamar", "https://clinica-med.co.il/doctors/%D7%93%D7%B4%D7%A8-%D7%90%D7%99%D7%AA%D7%9E%D7%A8-%D7%96%D7%99%D7%9C%D7%91%D7%A8%D7%9E%D7%9F-%D7%A8%D7%95%D7%9F/", "https://www.medreviews.co.il/provider/dr-zilberman-ron-itamar#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://www.medreviews.co.il/search/eye-doctor", "https://www.medreviews.co.il/provider/dr-tal-kfir#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-nasser-orwa#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-spierer-oriel#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-feldman-ilan#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-douieb-joseph#contact-doctor-section", "https://www.medreviews.co.il/provider/medical-village", "https://www.medreviews.co.il/provider/medical-village#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-barbara-adel#contact-doctor-section", "https://www.medreviews.co.il/provider/prof-lifshitz-tova#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-socea-sergiu#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-guttman-sharon#contact-doctor-section", "https://www.medreviews.co.il/provider/dr-rock-oded#contact-doctor-section", "https://clinica-med.co.il/", "https://www.doctorita.co.il/experts/97780", "https://www.doctorita.co.il/articles/about", "https://www.doctorita.co.il/registration/doctors"]</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,77 +449,112 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>license_number</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>seed_type</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>email</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>email_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>matched_query</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>extraction_method</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>alternate_emails</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>candidate_count</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>retry_count</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>next_retry_at</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>search_queries</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>search_errors</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>search_results</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>pages_fetched</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>fetch_failures</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>search_provider</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
         <is>
           <t>attempted_urls</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>hospital_pass</t>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>identity_url</t>
         </is>
       </c>
     </row>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,42 +519,57 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>last_attempt_at</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>search_queries</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>search_errors</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>search_results</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pages_fetched</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>fetch_failures</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>search_provider</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>attempted_urls</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>identity_url</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>previous_status</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>previous_candidate</t>
         </is>
       </c>
     </row>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,16 +560,6 @@
       <c r="AC1" t="inlineStr">
         <is>
           <t>identity_url</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>previous_status</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>previous_candidate</t>
         </is>
       </c>
     </row>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC1"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,6 +560,11 @@
       <c r="AC1" t="inlineStr">
         <is>
           <t>identity_url</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>previous_status</t>
         </is>
       </c>
     </row>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,10 +559,15 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>physician_search_version</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>identity_url</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>previous_status</t>
         </is>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,17 +559,22 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>merged_checkpoint_rows</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>identity_url</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>previous_status</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
           <t>physician_search_version</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>identity_url</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>previous_status</t>
         </is>
       </c>
     </row>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -424,157 +424,157 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>physician_search_version</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>target_kind</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>seed_source</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>license_number</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>seed_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>email_type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>matched_query</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>extraction_method</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>alternate_emails</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>candidate_count</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>retry_count</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>next_retry_at</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>last_attempt_at</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>search_queries</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>search_errors</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>search_results</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pages_fetched</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>fetch_failures</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>search_provider</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>attempted_urls</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>merged_checkpoint_rows</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>identity_url</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>previous_status</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>physician_search_version</t>
         </is>
       </c>
     </row>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,168 +425,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>algo_version</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>physician_search_version</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>target_kind</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>seed_source</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>license_number</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>seed_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>email_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>matched_query</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>extraction_method</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>alternate_emails</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>candidate_count</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>retry_count</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>next_retry_at</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>last_attempt_at</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>search_queries</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>search_errors</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>search_results</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pages_fetched</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>fetch_failures</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>search_provider</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>attempted_urls</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>merged_checkpoint_rows</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>previous_status</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>identity_url</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>previous_status</t>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>previous_candidate</t>
         </is>
       </c>
     </row>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -581,15 +581,20 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>identity_url</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>shared_target_count</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>previous_status</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>identity_url</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>previous_candidate</t>
         </is>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>shared_target_count</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>identity_url</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>shared_target_count</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>identity_url</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>shared_target_count</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>identity_url</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,178 +413,198 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>algo_version</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>physician_search_version</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>target_kind</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>seed_source</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>license_number</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>seed_type</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>email_type</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>matched_query</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>extraction_method</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>alternate_emails</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>candidate_count</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>retry_count</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>next_retry_at</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>last_attempt_at</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>search_queries</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>search_errors</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>search_results</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pages_fetched</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>fetch_failures</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>search_provider</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>attempted_urls</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>merged_checkpoint_rows</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>shared_target_count</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>unchanged_search_count</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>identity_url</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>previous_status</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>verification_review_required</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>previous_candidate</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>resolution_reason</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>search_fingerprint</t>
         </is>
       </c>
     </row>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,194 +429,194 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>algo_version</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>physician_search_version</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>target_kind</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>seed_source</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>license_number</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>seed_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>email_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>matched_query</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>extraction_method</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>alternate_emails</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>candidate_count</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>retry_count</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>next_retry_at</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>last_attempt_at</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>search_queries</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>search_errors</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>search_results</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pages_fetched</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>fetch_failures</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>search_provider</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>attempted_urls</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>merged_checkpoint_rows</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>shared_target_count</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>unchanged_search_count</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>identity_url</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>resolution_reason</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>search_fingerprint</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>previous_status</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>verification_review_required</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>previous_candidate</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>resolution_reason</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>search_fingerprint</t>
         </is>
       </c>
     </row>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,11 +612,6 @@
       <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>verification_review_required</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>previous_candidate</t>
         </is>
       </c>
     </row>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AK8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,6 +614,727 @@
           <t>verification_review_required</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>בית חולים אסותא אשדוד</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.assutaashdod.co.il/?catid={18D56B82-8E8D-4996-BB10-A4DE18EC43D9}</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2026-09-08T08:08:51.052949+00:00</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>6</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>["https://www.assutaashdod.co.il/?catid={18D56B82-8E8D-4996-BB10-A4DE18EC43D9}", "https://www.assutaashdod.co.il/pain-managemen/", "https://www.assutaashdod.co.il/?catid={69126ae3-1d19-4f65-b244-00a1cde97a13}", "https://doctors.assuta.co.il/search/speciality/gastroenterology-6", "https://www.medreviews.co.il/search/all?hospital=assuta", "https://doctors.assuta.co.il/search/speciality/gastroenterology-6/-0", "https://www.assutaashdod.co.il/?catid={ee360582-387d-4ce7-9105-bdef14d4a4da}", "https://www.assutaashdod.co.il/?catid={1D97A7C5-85DE-4048-A454-B25B02DE8B80}", "https://medplus.co.il/hospitals/assutaashdod/", "https://customer-service.co.il/שירות-לקוחות-בית-חולים-אסותא-אשדוד/", "https://sherut.org.il/שירות-לקוחות-בית-חולים-אסותא-אשדוד/", "https://www.govserv.org/IL/Ashdod/199778337049012/בית-החולים-אסותא-אשדוד-ע\"ש-סמסון", "https://www.assutaashdod.co.il/?catid={A62C8A32-23A4-46EE-BC63-5AF55AD4EC4A}", "https://onlineappointment-client.assutaashdod.co.il/header.html", "https://ashdods.co.il/%D7%97%D7%93%D7%A9%D7%95%D7%AA/%D7%94%D7%A9%D7%99%D7%A0%D7%95%D7%99-%D7%9E%D7%95%D7%A8%D7%92%D7%A9-%D7%A8%D7%91%D7%A0%D7%99-%D7%94%D7%A7%D7%A8%D7%99%D7%95%D7%AA-%D7%A0%D7%A4%D7%92%D7%A9%D7%95-%D7%A2%D7%9D-%D7%9E%D7%A0%D7%9B-%D7%9C%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%94%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%90%D7%A1%D7%95%D7%AA%D7%90-%D7%90%D7%A9%D7%93%D7%95%D7%93-803824", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/", "https://or-balev.co.il/%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%90%D7%A1%D7%95%D7%AA%D7%90-%D7%90%D7%A9%D7%93%D7%95%D7%93/", "https://doctors.assuta.co.il/doctor/emad-sakhnini-27920", "https://doctors.assuta.co.il/doctor/bernard-davidovich-19581", "https://www.badatz.biz/biz/%D7%91%D7%92%D7%98%D7%95%D7%A1-2/", "https://moovitapp.com/index/he/תחבורה_ציבורית-בית_חולים_אסותא_אשדוד-Israel-site_33059550-1", "https://refua360.co.il/%D7%9E%D7%A4%D7%92%D7%A9-%D7%A2%D7%93%D7%9B%D7%95%D7%9F-%D7%91%D7%9B%D7%99%D7%A8%D7%99-%D7%99%D7%95%D7%A2%D7%A6%D7%99-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%91%D7%9E%D7%97%D7%9C%D7%A7%D7%94-%D7%9C/", "https://mamy-le.co.il/שעות-ביקור-יולדות-אסותא-אשדוד/", "https://www.gov.il/he/departments/dynamiccollectors/genetic-counseling-institute"]</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>25418919765394</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>בית חולים השרון</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100066618046510/posts/דר-איתן-לבון-מונה-למנהל-בית-חולים-השרון-דר-איתן-לבון-51-מונה-למנהל-בית-חולים-השר/901683082062285/</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-09-08T08:08:51.055391+00:00</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>6</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>["https://www.facebook.com/100066618046510/posts/%D7%93%D7%A8-%D7%90%D7%99%D7%AA%D7%9F-%D7%9C%D7%91%D7%95%D7%9F-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%94%D7%A9%D7%A8%D7%95%D7%9F-%D7%93%D7%A8-%D7%90%D7%99%D7%AA%D7%9F-%D7%9C%D7%91%D7%95%D7%9F-51-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%94%D7%A9%D7%A8/901683082062285/", "https://www.medonline.co.il/section/clalit/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%97%D7%91%D7%A8-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%94%D7%A9%D7%A8%D7%95%D7%9F", "https://www.medreviews.co.il/search/urology/center/tel-aviv", "https://hospitals.clalit.co.il/rabin/he", "https://www.b144.co.il/b144_sip/401C04134079615A49170317/", "https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/rheumatology/Pages/default.aspx", "https://hospitals.clalit.co.il/rabin/he/about/Pages/rmc_management.aspx", "https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/dermatology/Pages/dermatology_department_beilinson.aspx", "https://sherut.org.il/שירות-לקוחות-בית-חולים-השרון/", "https://hospitals.clalit.co.il/rabin/he/Pages/default.aspx/", "https://hospitals.clalit.co.il/rabin/he/patient-information/patient-services/Pages/patient_services_hasharon.aspx", "https://serviced.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA-%D7%91%D7%99%D7%AA-%D7%94%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%94%D7%A9%D7%A8%D7%95%D7%9F/", "https://www.b144.co.il/b144_sip/401C04134079615A49160213/", "https://www.b144.co.il/b144_sip/401C04134079615A49170C15/", "https://www.melabes.co.il/health/97063", "https://www.ptnow.co.il/articles/18210/", "https://hospitals.clalit.co.il/rabin/he/Pages/default.aspx", "https://www.ima.org.il/CollectiveAgreements/Default.aspx", "https://hospitals.clalit.co.il/rabin/he/news/2019/Pages/new_management.aspx", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F100066618046510%2Fposts%2F%25D7%2593%25D7%25A8-%25D7%2590%25D7%2599%25D7%25AA%25D7%259F-%25D7%259C%25D7%2591%25D7%2595%25D7%259F-%25D7%259E%25D7%2595%25D7%25A0%25D7%2594-%25D7%259C%25D7%259E%25D7%25A0%25D7%2594%25D7%259C-%25D7%2591%25D7%2599%25D7%25AA-%25D7%2597%25D7%2595%25D7%259C%25D7%2599%25D7%259D-%25D7%2594%25D7%25A9%25D7%25A8%25D7%2595%25D7%259F-%25D7%2593%25D7%25A8-%25D7%2590%25D7%2599%25D7%25AA%25D7%259F-%25D7%259C%25D7%2591%25D7%2595%25D7%259F-51-%25D7%259E%25D7%2595%25D7%25A0%25D7%2594-%25D7%259C%25D7%259E%25D7%25A0%25D7%2594%25D7%259C-%25D7%2591%25D7%2599%25D7%25AA-%25D7%2597%25D7%2595%25D7%259C%25D7%2599%25D7%259D-%25D7%2594%25D7%25A9%25D7%25A8%2F901683082062285%2F"]</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>25418919765394</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>בית חולים לניאדו בנתניה</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.laniado.org.il/</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-09-08T08:08:59.617334+00:00</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>6</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>["https://www.laniado.org.il/", "https://www.laniado.org.il/%D7%94%D7%A0%D7%94%D7%9C%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/", "https://medpage.co.il/%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/", "https://le-la.co.il/בית-חולים-לניאדו/", "https://www.ksn.co.il/%D7%9E%D7%A0%D7%94%D7%9C-%D7%9B%D7%9C%D7%9C%D7%99-%D7%97%D7%93%D7%A9-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/"]</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>25418919765394</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>המרכז הרפואי תל אביב ע"ש סוראסקי איכילוב</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.tasmc.org.il/</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-09-08T08:09:08.130956+00:00</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>6</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>["https://www.tasmc.org.il/", "https://aisrael.org/%D7%9E%D7%99%D7%93%D7%A2-%D7%9E%D7%A1%D7%99%D7%99%D7%A2/%D7%AA%D7%9C%D7%95%D7%A0%D7%95%D7%AA-%D7%A0%D7%92%D7%99%D7%A9%D7%95%D7%AA/%D7%97%D7%A0%D7%99%D7%95%D7%AA-%D7%A0%D7%9B%D7%99%D7%9D-2/%D7%97%D7%A0%D7%99%D7%94-%D7%9C%D7%A0%D7%9B%D7%99%D7%9D-%D7%95%D7%A0%D7%92%D7%99%D7%A9%D7%95%D7%AA-%D7%91%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%90%D7%99%D7%9B%D7%99%D7%9C%D7%95%D7%91/", "https://sherut.org.il/שירות-לקוחות-בית-חולים-איכילוב/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fgroups%2F303506218783941%2F"]</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>25418919765394</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>הנהלת המרכז הרפואי לב השרון</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.lev-hasharon.co.il/?page_id=37</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-09-08T08:09:19.555696+00:00</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>6</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>["https://www.lev-hasharon.co.il/?page_id=37"]</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>25418919765394</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>כללית , משרדי מנהלת פתח תקוה</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.b144.co.il/b144_sip/401C0413407662554D170210/</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-09-08T08:09:24.205637+00:00</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>["https://www.b144.co.il/b144_sip/401C0413407662554D170210/", "https://www.b144.co.il/b144_sip/401C0413407662554D170214/"]</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>25418919765394</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>עיריית פתח תקווה</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.petah-tikva.muni.il/health/kupatholiim</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-09-08T08:08:51.054289+00:00</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>6</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>["https://www.petah-tikva.muni.il/health/kupatholiim", "https://www.petah-tikva.muni.il/city-and-municipality/bids", "https://www.govojobs.co.il/govjobs/more/עיריית-פתח-תקווה-דרושים?page=8181", "https://www.alljobs.co.il/Employer/HP/Default.aspx?cid=180065", "https://www.davar1.co.il/topic/פתח-תקווה/", "https://www.be106.net/207/157035", "https://www.petah-tikva.muni.il/", "https://petachtikva.co.il/%D7%90%D7%AA%D7%A8-%D7%A2%D7%99%D7%A8%D7%99%D7%99%D7%AA-%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-%D7%94%D7%97%D7%93%D7%A9-%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99%D7%9D-%D7%93%D7%99%D7%92%D7%99/", "https://www.facebook.com/Petah.Tikva.Muni/about_contact_and_basic_info/", "https://sherut.org.il/שירות-לקוחות-עיריית-פתח-תקווה/", "https://sherut-kal.co.il/org/iriyat-petah-tikva", "https://xn----9hcbajix2gfiog.org.il/%D7%A2%D7%99%D7%A8%D7%99%D7%99%D7%AA-%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA/", "https://customer-service.co.il/שירות-לקוחות-עיריית-פתח-תקווה/", "https://serviced.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA-%D7%A2%D7%99%D7%A8%D7%99%D7%99%D7%AA-%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-%D7%98/", "https://www.sherut.net/PetahTikva", "https://www.petah-tikva.muni.il/city-and-municipality/departments", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F%40Petah.Tikva.Muni%2F", "https://www.govserv.org/IL/Petah-Tikva/116563891775107/עיריית-פתח-תקווה"]</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>25418919752272</v>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK8"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -706,9 +706,11 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>25418919765394</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>76256759296182</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
@@ -809,9 +811,11 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>25418919765394</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
+        <v>76256759296182</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
@@ -912,9 +916,11 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>25418919765394</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
+        <v>76256759296182</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
       <c r="AF4" t="n">
         <v>0</v>
       </c>
@@ -1015,9 +1021,11 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>25418919765394</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
+        <v>76256759296182</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
@@ -1118,9 +1126,11 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>25418919765394</v>
-      </c>
-      <c r="AE6" t="inlineStr"/>
+        <v>76256759296182</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
@@ -1221,9 +1231,11 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>25418919765394</v>
-      </c>
-      <c r="AE7" t="inlineStr"/>
+        <v>76256759296182</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
       <c r="AF7" t="n">
         <v>0</v>
       </c>
@@ -1242,7 +1254,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>עיריית פתח תקווה</t>
+          <t>לשכת בריאות מחוז תל אביב</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1262,7 +1274,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.petah-tikva.muni.il/health/kupatholiim</t>
+          <t>https://www.gov.il/he/government-service-branches/health_bureau_tel_aviv</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1299,20 +1311,20 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-08T08:08:51.054289+00:00</t>
+          <t>2026-09-08T08:09:50.293768+00:00</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>6</v>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
         <v>2</v>
@@ -1320,13 +1332,15 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>["https://www.petah-tikva.muni.il/health/kupatholiim", "https://www.petah-tikva.muni.il/city-and-municipality/bids", "https://www.govojobs.co.il/govjobs/more/עיריית-פתח-תקווה-דרושים?page=8181", "https://www.alljobs.co.il/Employer/HP/Default.aspx?cid=180065", "https://www.davar1.co.il/topic/פתח-תקווה/", "https://www.be106.net/207/157035", "https://www.petah-tikva.muni.il/", "https://petachtikva.co.il/%D7%90%D7%AA%D7%A8-%D7%A2%D7%99%D7%A8%D7%99%D7%99%D7%AA-%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-%D7%94%D7%97%D7%93%D7%A9-%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99%D7%9D-%D7%93%D7%99%D7%92%D7%99/", "https://www.facebook.com/Petah.Tikva.Muni/about_contact_and_basic_info/", "https://sherut.org.il/שירות-לקוחות-עיריית-פתח-תקווה/", "https://sherut-kal.co.il/org/iriyat-petah-tikva", "https://xn----9hcbajix2gfiog.org.il/%D7%A2%D7%99%D7%A8%D7%99%D7%99%D7%AA-%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA/", "https://customer-service.co.il/שירות-לקוחות-עיריית-פתח-תקווה/", "https://serviced.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA-%D7%A2%D7%99%D7%A8%D7%99%D7%99%D7%AA-%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-%D7%98/", "https://www.sherut.net/PetahTikva", "https://www.petah-tikva.muni.il/city-and-municipality/departments", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F%40Petah.Tikva.Muni%2F", "https://www.govserv.org/IL/Petah-Tikva/116563891775107/עיריית-פתח-תקווה"]</t>
+          <t>["https://www.gov.il/he/government-service-branches/health_bureau_tel_aviv", "https://www.gov.il/he/government-service-branches/moh-tel-aviv-management", "https://serviced.co.il/health-office/%D7%A9%D7%A2%D7%95%D7%AA-%D7%A4%D7%AA%D7%99%D7%97%D7%94-%D7%95%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA-%D7%9C%D7%A7%D7%91%D7%9C%D7%AA-%D7%A7%D7%94%D7%9C-%D7%9C%D7%A9%D7%9B%D7%AA-%D7%94%D7%91%D7%A8%D7%99-7/"]</t>
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>25418919752272</v>
-      </c>
-      <c r="AE8" t="inlineStr"/>
+        <v>50837839530789</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
       <c r="AF8" t="n">
         <v>0</v>
       </c>
@@ -1336,6 +1350,111 @@
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>עיריית פתח תקווה</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.petah-tikva.muni.il/health/kupatholiim</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-09-08T08:08:51.054289+00:00</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>6</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>["https://www.petah-tikva.muni.il/health/kupatholiim", "https://www.petah-tikva.muni.il/city-and-municipality/bids", "https://www.govojobs.co.il/govjobs/more/עיריית-פתח-תקווה-דרושים?page=8181", "https://www.alljobs.co.il/Employer/HP/Default.aspx?cid=180065", "https://www.davar1.co.il/topic/פתח-תקווה/", "https://www.be106.net/207/157035", "https://www.petah-tikva.muni.il/", "https://petachtikva.co.il/%D7%90%D7%AA%D7%A8-%D7%A2%D7%99%D7%A8%D7%99%D7%99%D7%AA-%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-%D7%94%D7%97%D7%93%D7%A9-%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99%D7%9D-%D7%93%D7%99%D7%92%D7%99/", "https://www.facebook.com/Petah.Tikva.Muni/about_contact_and_basic_info/", "https://sherut.org.il/שירות-לקוחות-עיריית-פתח-תקווה/", "https://sherut-kal.co.il/org/iriyat-petah-tikva", "https://xn----9hcbajix2gfiog.org.il/%D7%A2%D7%99%D7%A8%D7%99%D7%99%D7%AA-%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA/", "https://customer-service.co.il/שירות-לקוחות-עיריית-פתח-תקווה/", "https://serviced.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA-%D7%A2%D7%99%D7%A8%D7%99%D7%99%D7%AA-%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-%D7%98/", "https://www.sherut.net/PetahTikva", "https://www.petah-tikva.muni.il/city-and-municipality/departments", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F%40Petah.Tikva.Muni%2F", "https://www.govserv.org/IL/Petah-Tikva/116563891775107/עיריית-פתח-תקווה"]</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>76256759256816</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK9"/>
+  <dimension ref="A1:AK48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,17 +596,17 @@
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
+          <t>previous_status</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
           <t>resolution_reason</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>search_fingerprint</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>previous_status</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
@@ -624,12 +624,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>בית חולים אסותא אשדוד</t>
+          <t>DocAdvisor אתר דירוג הרופאים של ישראל</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>clinic_manager</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.assutaashdod.co.il/?catid={18D56B82-8E8D-4996-BB10-A4DE18EC43D9}</t>
+          <t>https://www.docadvisor.co.il/</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -681,36 +681,34 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-08T08:08:51.052949+00:00</t>
+          <t>2026-09-08T13:58:23.356672+00:00</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>["https://www.assutaashdod.co.il/?catid={18D56B82-8E8D-4996-BB10-A4DE18EC43D9}", "https://www.assutaashdod.co.il/pain-managemen/", "https://www.assutaashdod.co.il/?catid={69126ae3-1d19-4f65-b244-00a1cde97a13}", "https://doctors.assuta.co.il/search/speciality/gastroenterology-6", "https://www.medreviews.co.il/search/all?hospital=assuta", "https://doctors.assuta.co.il/search/speciality/gastroenterology-6/-0", "https://www.assutaashdod.co.il/?catid={ee360582-387d-4ce7-9105-bdef14d4a4da}", "https://www.assutaashdod.co.il/?catid={1D97A7C5-85DE-4048-A454-B25B02DE8B80}", "https://medplus.co.il/hospitals/assutaashdod/", "https://customer-service.co.il/שירות-לקוחות-בית-חולים-אסותא-אשדוד/", "https://sherut.org.il/שירות-לקוחות-בית-חולים-אסותא-אשדוד/", "https://www.govserv.org/IL/Ashdod/199778337049012/בית-החולים-אסותא-אשדוד-ע\"ש-סמסון", "https://www.assutaashdod.co.il/?catid={A62C8A32-23A4-46EE-BC63-5AF55AD4EC4A}", "https://onlineappointment-client.assutaashdod.co.il/header.html", "https://ashdods.co.il/%D7%97%D7%93%D7%A9%D7%95%D7%AA/%D7%94%D7%A9%D7%99%D7%A0%D7%95%D7%99-%D7%9E%D7%95%D7%A8%D7%92%D7%A9-%D7%A8%D7%91%D7%A0%D7%99-%D7%94%D7%A7%D7%A8%D7%99%D7%95%D7%AA-%D7%A0%D7%A4%D7%92%D7%A9%D7%95-%D7%A2%D7%9D-%D7%9E%D7%A0%D7%9B-%D7%9C%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%94%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%90%D7%A1%D7%95%D7%AA%D7%90-%D7%90%D7%A9%D7%93%D7%95%D7%93-803824", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/", "https://or-balev.co.il/%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%90%D7%A1%D7%95%D7%AA%D7%90-%D7%90%D7%A9%D7%93%D7%95%D7%93/", "https://doctors.assuta.co.il/doctor/emad-sakhnini-27920", "https://doctors.assuta.co.il/doctor/bernard-davidovich-19581", "https://www.badatz.biz/biz/%D7%91%D7%92%D7%98%D7%95%D7%A1-2/", "https://moovitapp.com/index/he/תחבורה_ציבורית-בית_חולים_אסותא_אשדוד-Israel-site_33059550-1", "https://refua360.co.il/%D7%9E%D7%A4%D7%92%D7%A9-%D7%A2%D7%93%D7%9B%D7%95%D7%9F-%D7%91%D7%9B%D7%99%D7%A8%D7%99-%D7%99%D7%95%D7%A2%D7%A6%D7%99-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%91%D7%9E%D7%97%D7%9C%D7%A7%D7%94-%D7%9C/", "https://mamy-le.co.il/שעות-ביקור-יולדות-אסותא-אשדוד/", "https://www.gov.il/he/departments/dynamiccollectors/genetic-counseling-institute"]</t>
+          <t>["https://www.docadvisor.co.il/"]</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>76256759296182</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1</v>
-      </c>
+        <v>183079455104316</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
@@ -729,7 +727,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>בית חולים השרון</t>
+          <t>בית חולים אסותא אשדוד</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -749,7 +747,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100066618046510/posts/דר-איתן-לבון-מונה-למנהל-בית-חולים-השרון-דר-איתן-לבון-51-מונה-למנהל-בית-חולים-השר/901683082062285/</t>
+          <t>https://www.assutaashdod.co.il/?catid={18D56B82-8E8D-4996-BB10-A4DE18EC43D9}</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -786,7 +784,7 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-08T08:08:51.055391+00:00</t>
+          <t>2026-09-08T08:08:51.052949+00:00</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -796,22 +794,22 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>["https://www.facebook.com/100066618046510/posts/%D7%93%D7%A8-%D7%90%D7%99%D7%AA%D7%9F-%D7%9C%D7%91%D7%95%D7%9F-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%94%D7%A9%D7%A8%D7%95%D7%9F-%D7%93%D7%A8-%D7%90%D7%99%D7%AA%D7%9F-%D7%9C%D7%91%D7%95%D7%9F-51-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%94%D7%A9%D7%A8/901683082062285/", "https://www.medonline.co.il/section/clalit/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%97%D7%91%D7%A8-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%94%D7%A9%D7%A8%D7%95%D7%9F", "https://www.medreviews.co.il/search/urology/center/tel-aviv", "https://hospitals.clalit.co.il/rabin/he", "https://www.b144.co.il/b144_sip/401C04134079615A49170317/", "https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/rheumatology/Pages/default.aspx", "https://hospitals.clalit.co.il/rabin/he/about/Pages/rmc_management.aspx", "https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/dermatology/Pages/dermatology_department_beilinson.aspx", "https://sherut.org.il/שירות-לקוחות-בית-חולים-השרון/", "https://hospitals.clalit.co.il/rabin/he/Pages/default.aspx/", "https://hospitals.clalit.co.il/rabin/he/patient-information/patient-services/Pages/patient_services_hasharon.aspx", "https://serviced.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA-%D7%91%D7%99%D7%AA-%D7%94%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%94%D7%A9%D7%A8%D7%95%D7%9F/", "https://www.b144.co.il/b144_sip/401C04134079615A49160213/", "https://www.b144.co.il/b144_sip/401C04134079615A49170C15/", "https://www.melabes.co.il/health/97063", "https://www.ptnow.co.il/articles/18210/", "https://hospitals.clalit.co.il/rabin/he/Pages/default.aspx", "https://www.ima.org.il/CollectiveAgreements/Default.aspx", "https://hospitals.clalit.co.il/rabin/he/news/2019/Pages/new_management.aspx", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F100066618046510%2Fposts%2F%25D7%2593%25D7%25A8-%25D7%2590%25D7%2599%25D7%25AA%25D7%259F-%25D7%259C%25D7%2591%25D7%2595%25D7%259F-%25D7%259E%25D7%2595%25D7%25A0%25D7%2594-%25D7%259C%25D7%259E%25D7%25A0%25D7%2594%25D7%259C-%25D7%2591%25D7%2599%25D7%25AA-%25D7%2597%25D7%2595%25D7%259C%25D7%2599%25D7%259D-%25D7%2594%25D7%25A9%25D7%25A8%25D7%2595%25D7%259F-%25D7%2593%25D7%25A8-%25D7%2590%25D7%2599%25D7%25AA%25D7%259F-%25D7%259C%25D7%2591%25D7%2595%25D7%259F-51-%25D7%259E%25D7%2595%25D7%25A0%25D7%2594-%25D7%259C%25D7%259E%25D7%25A0%25D7%2594%25D7%259C-%25D7%2591%25D7%2599%25D7%25AA-%25D7%2597%25D7%2595%25D7%259C%25D7%2599%25D7%259D-%25D7%2594%25D7%25A9%25D7%25A8%2F901683082062285%2F"]</t>
+          <t>["https://www.assutaashdod.co.il/?catid={18D56B82-8E8D-4996-BB10-A4DE18EC43D9}", "https://www.assutaashdod.co.il/pain-managemen/", "https://www.assutaashdod.co.il/?catid={69126ae3-1d19-4f65-b244-00a1cde97a13}", "https://doctors.assuta.co.il/search/speciality/gastroenterology-6", "https://www.medreviews.co.il/search/all?hospital=assuta", "https://doctors.assuta.co.il/search/speciality/gastroenterology-6/-0", "https://www.assutaashdod.co.il/?catid={ee360582-387d-4ce7-9105-bdef14d4a4da}", "https://www.assutaashdod.co.il/?catid={1D97A7C5-85DE-4048-A454-B25B02DE8B80}", "https://medplus.co.il/hospitals/assutaashdod/", "https://customer-service.co.il/שירות-לקוחות-בית-חולים-אסותא-אשדוד/", "https://sherut.org.il/שירות-לקוחות-בית-חולים-אסותא-אשדוד/", "https://www.govserv.org/IL/Ashdod/199778337049012/בית-החולים-אסותא-אשדוד-ע\"ש-סמסון", "https://www.assutaashdod.co.il/?catid={A62C8A32-23A4-46EE-BC63-5AF55AD4EC4A}", "https://onlineappointment-client.assutaashdod.co.il/header.html", "https://ashdods.co.il/%D7%97%D7%93%D7%A9%D7%95%D7%AA/%D7%94%D7%A9%D7%99%D7%A0%D7%95%D7%99-%D7%9E%D7%95%D7%A8%D7%92%D7%A9-%D7%A8%D7%91%D7%A0%D7%99-%D7%94%D7%A7%D7%A8%D7%99%D7%95%D7%AA-%D7%A0%D7%A4%D7%92%D7%A9%D7%95-%D7%A2%D7%9D-%D7%9E%D7%A0%D7%9B-%D7%9C%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%94%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%90%D7%A1%D7%95%D7%AA%D7%90-%D7%90%D7%A9%D7%93%D7%95%D7%93-803824", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/", "https://or-balev.co.il/%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%90%D7%A1%D7%95%D7%AA%D7%90-%D7%90%D7%A9%D7%93%D7%95%D7%93/", "https://doctors.assuta.co.il/doctor/emad-sakhnini-27920", "https://doctors.assuta.co.il/doctor/bernard-davidovich-19581", "https://www.badatz.biz/biz/%D7%91%D7%92%D7%98%D7%95%D7%A1-2/", "https://moovitapp.com/index/he/תחבורה_ציבורית-בית_חולים_אסותא_אשדוד-Israel-site_33059550-1", "https://refua360.co.il/%D7%9E%D7%A4%D7%92%D7%A9-%D7%A2%D7%93%D7%9B%D7%95%D7%9F-%D7%91%D7%9B%D7%99%D7%A8%D7%99-%D7%99%D7%95%D7%A2%D7%A6%D7%99-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%91%D7%9E%D7%97%D7%9C%D7%A7%D7%94-%D7%9C/", "https://mamy-le.co.il/שעות-ביקור-יולדות-אסותא-אשדוד/", "https://www.gov.il/he/departments/dynamiccollectors/genetic-counseling-institute"]</t>
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>76256759296182</v>
+        <v>228770277888546</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -834,7 +832,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>בית חולים לניאדו בנתניה</t>
+          <t>בית חולים השרון</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -854,7 +852,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.laniado.org.il/</t>
+          <t>https://www.facebook.com/100066618046510/posts/דר-איתן-לבון-מונה-למנהל-בית-חולים-השרון-דר-איתן-לבון-51-מונה-למנהל-בית-חולים-השר/901683082062285/</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -891,7 +889,7 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-08T08:08:59.617334+00:00</t>
+          <t>2026-09-08T08:08:51.055391+00:00</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -901,22 +899,22 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>["https://www.laniado.org.il/", "https://www.laniado.org.il/%D7%94%D7%A0%D7%94%D7%9C%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/", "https://medpage.co.il/%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/", "https://le-la.co.il/בית-חולים-לניאדו/", "https://www.ksn.co.il/%D7%9E%D7%A0%D7%94%D7%9C-%D7%9B%D7%9C%D7%9C%D7%99-%D7%97%D7%93%D7%A9-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/"]</t>
+          <t>["https://www.facebook.com/100066618046510/posts/%D7%93%D7%A8-%D7%90%D7%99%D7%AA%D7%9F-%D7%9C%D7%91%D7%95%D7%9F-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%94%D7%A9%D7%A8%D7%95%D7%9F-%D7%93%D7%A8-%D7%90%D7%99%D7%AA%D7%9F-%D7%9C%D7%91%D7%95%D7%9F-51-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%94%D7%A9%D7%A8/901683082062285/", "https://www.medonline.co.il/section/clalit/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%97%D7%91%D7%A8-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%94%D7%A9%D7%A8%D7%95%D7%9F", "https://www.medreviews.co.il/search/urology/center/tel-aviv", "https://hospitals.clalit.co.il/rabin/he", "https://www.b144.co.il/b144_sip/401C04134079615A49170317/", "https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/rheumatology/Pages/default.aspx", "https://hospitals.clalit.co.il/rabin/he/about/Pages/rmc_management.aspx", "https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/dermatology/Pages/dermatology_department_beilinson.aspx", "https://sherut.org.il/שירות-לקוחות-בית-חולים-השרון/", "https://hospitals.clalit.co.il/rabin/he/Pages/default.aspx/", "https://hospitals.clalit.co.il/rabin/he/patient-information/patient-services/Pages/patient_services_hasharon.aspx", "https://serviced.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA-%D7%91%D7%99%D7%AA-%D7%94%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%94%D7%A9%D7%A8%D7%95%D7%9F/", "https://www.b144.co.il/b144_sip/401C04134079615A49160213/", "https://www.b144.co.il/b144_sip/401C04134079615A49170C15/", "https://www.melabes.co.il/health/97063", "https://www.ptnow.co.il/articles/18210/", "https://hospitals.clalit.co.il/rabin/he/Pages/default.aspx", "https://www.ima.org.il/CollectiveAgreements/Default.aspx", "https://hospitals.clalit.co.il/rabin/he/news/2019/Pages/new_management.aspx", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F100066618046510%2Fposts%2F%25D7%2593%25D7%25A8-%25D7%2590%25D7%2599%25D7%25AA%25D7%259F-%25D7%259C%25D7%2591%25D7%2595%25D7%259F-%25D7%259E%25D7%2595%25D7%25A0%25D7%2594-%25D7%259C%25D7%259E%25D7%25A0%25D7%2594%25D7%259C-%25D7%2591%25D7%2599%25D7%25AA-%25D7%2597%25D7%2595%25D7%259C%25D7%2599%25D7%259D-%25D7%2594%25D7%25A9%25D7%25A8%25D7%2595%25D7%259F-%25D7%2593%25D7%25A8-%25D7%2590%25D7%2599%25D7%25AA%25D7%259F-%25D7%259C%25D7%2591%25D7%2595%25D7%259F-51-%25D7%259E%25D7%2595%25D7%25A0%25D7%2594-%25D7%259C%25D7%259E%25D7%25A0%25D7%2594%25D7%259C-%25D7%2591%25D7%2599%25D7%25AA-%25D7%2597%25D7%2595%25D7%259C%25D7%2599%25D7%259D-%25D7%2594%25D7%25A9%25D7%25A8%2F901683082062285%2F"]</t>
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>76256759296182</v>
+        <v>228770277888546</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -939,7 +937,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>המרכז הרפואי תל אביב ע"ש סוראסקי איכילוב</t>
+          <t>בית חולים לניאדו בנתניה</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -959,7 +957,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/</t>
+          <t>https://www.laniado.org.il/</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -996,7 +994,7 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-08T08:09:08.130956+00:00</t>
+          <t>2026-09-08T08:08:59.617334+00:00</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -1006,10 +1004,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="n">
         <v>1</v>
@@ -1017,11 +1015,11 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>["https://www.tasmc.org.il/", "https://aisrael.org/%D7%9E%D7%99%D7%93%D7%A2-%D7%9E%D7%A1%D7%99%D7%99%D7%A2/%D7%AA%D7%9C%D7%95%D7%A0%D7%95%D7%AA-%D7%A0%D7%92%D7%99%D7%A9%D7%95%D7%AA/%D7%97%D7%A0%D7%99%D7%95%D7%AA-%D7%A0%D7%9B%D7%99%D7%9D-2/%D7%97%D7%A0%D7%99%D7%94-%D7%9C%D7%A0%D7%9B%D7%99%D7%9D-%D7%95%D7%A0%D7%92%D7%99%D7%A9%D7%95%D7%AA-%D7%91%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%90%D7%99%D7%9B%D7%99%D7%9C%D7%95%D7%91/", "https://sherut.org.il/שירות-לקוחות-בית-חולים-איכילוב/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fgroups%2F303506218783941%2F"]</t>
+          <t>["https://www.laniado.org.il/", "https://www.laniado.org.il/%D7%94%D7%A0%D7%94%D7%9C%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/", "https://medpage.co.il/%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/", "https://le-la.co.il/בית-חולים-לניאדו/", "https://www.ksn.co.il/%D7%9E%D7%A0%D7%94%D7%9C-%D7%9B%D7%9C%D7%9C%D7%99-%D7%97%D7%93%D7%A9-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/"]</t>
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>76256759296182</v>
+        <v>228770277888546</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1044,7 +1042,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>הנהלת המרכז הרפואי לב השרון</t>
+          <t>המרכז הרפואי תל אביב ע"ש סוראסקי איכילוב</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1064,7 +1062,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.lev-hasharon.co.il/?page_id=37</t>
+          <t>https://www.tasmc.org.il/</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1101,7 +1099,7 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-08T08:09:19.555696+00:00</t>
+          <t>2026-09-08T08:09:08.130956+00:00</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1111,22 +1109,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" t="n">
         <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>["https://www.lev-hasharon.co.il/?page_id=37"]</t>
+          <t>["https://www.tasmc.org.il/", "https://aisrael.org/%D7%9E%D7%99%D7%93%D7%A2-%D7%9E%D7%A1%D7%99%D7%99%D7%A2/%D7%AA%D7%9C%D7%95%D7%A0%D7%95%D7%AA-%D7%A0%D7%92%D7%99%D7%A9%D7%95%D7%AA/%D7%97%D7%A0%D7%99%D7%95%D7%AA-%D7%A0%D7%9B%D7%99%D7%9D-2/%D7%97%D7%A0%D7%99%D7%94-%D7%9C%D7%A0%D7%9B%D7%99%D7%9D-%D7%95%D7%A0%D7%92%D7%99%D7%A9%D7%95%D7%AA-%D7%91%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%90%D7%99%D7%9B%D7%99%D7%9C%D7%95%D7%91/", "https://sherut.org.il/שירות-לקוחות-בית-חולים-איכילוב/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fgroups%2F303506218783941%2F"]</t>
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>76256759296182</v>
+        <v>228770277888546</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1149,7 +1147,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>כללית , משרדי מנהלת פתח תקוה</t>
+          <t>המרפאה לבריאות הנפש פתח תקווה</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1169,7 +1167,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.b144.co.il/b144_sip/401C0413407662554D170210/</t>
+          <t>https://www.gov.il/he/departments/units/yaffo-petach-tikva</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1206,36 +1204,34 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-08T08:09:24.205637+00:00</t>
+          <t>2026-09-08T13:43:19.704038+00:00</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>6</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>["https://www.b144.co.il/b144_sip/401C0413407662554D170210/", "https://www.b144.co.il/b144_sip/401C0413407662554D170214/"]</t>
+          <t>["https://www.gov.il/he/departments/units/yaffo-petach-tikva", "https://www.gov.il/he/departments/publicbodies/yaffo-petach-tikva", "https://www.gov.il/he/pages/allstuffpetachtikva", "https://www.facebook.com/pages/%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94%20%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA%20%D7%94%D7%A0%D7%A4%D7%A9%20%D7%A4%D7%AA%D7%97%20%D7%AA%D7%A7%D7%95%D7%95%D7%94/101135286422385/"]</t>
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>76256759296182</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
+        <v>228958564246194</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
         <v>0</v>
       </c>
@@ -1254,7 +1250,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>לשכת בריאות מחוז תל אביב</t>
+          <t>הנהלת המרכז הרפואי לב השרון</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1274,7 +1270,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.gov.il/he/government-service-branches/health_bureau_tel_aviv</t>
+          <t>https://www.lev-hasharon.co.il/?page_id=37</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1311,7 +1307,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-08T08:09:50.293768+00:00</t>
+          <t>2026-09-08T08:09:19.555696+00:00</t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -1321,22 +1317,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>["https://www.gov.il/he/government-service-branches/health_bureau_tel_aviv", "https://www.gov.il/he/government-service-branches/moh-tel-aviv-management", "https://serviced.co.il/health-office/%D7%A9%D7%A2%D7%95%D7%AA-%D7%A4%D7%AA%D7%99%D7%97%D7%94-%D7%95%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA-%D7%9C%D7%A7%D7%91%D7%9C%D7%AA-%D7%A7%D7%94%D7%9C-%D7%9C%D7%A9%D7%9B%D7%AA-%D7%94%D7%91%D7%A8%D7%99-7/"]</t>
+          <t>["https://www.lev-hasharon.co.il/?page_id=37"]</t>
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>50837839530789</v>
+        <v>228770277888546</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1359,7 +1355,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>עיריית פתח תקווה</t>
+          <t>כללית , מחוז חיפה</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1379,7 +1375,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.petah-tikva.muni.il/health/kupatholiim</t>
+          <t>https://www.b144.co.il/b144_sip/401C04134675615A491C0515/</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1416,7 +1412,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-08T08:08:51.054289+00:00</t>
+          <t>2026-09-08T13:42:57.846288+00:00</t>
         </is>
       </c>
       <c r="W9" t="n">
@@ -1429,23 +1425,21 @@
         <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>["https://www.petah-tikva.muni.il/health/kupatholiim", "https://www.petah-tikva.muni.il/city-and-municipality/bids", "https://www.govojobs.co.il/govjobs/more/עיריית-פתח-תקווה-דרושים?page=8181", "https://www.alljobs.co.il/Employer/HP/Default.aspx?cid=180065", "https://www.davar1.co.il/topic/פתח-תקווה/", "https://www.be106.net/207/157035", "https://www.petah-tikva.muni.il/", "https://petachtikva.co.il/%D7%90%D7%AA%D7%A8-%D7%A2%D7%99%D7%A8%D7%99%D7%99%D7%AA-%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-%D7%94%D7%97%D7%93%D7%A9-%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99%D7%9D-%D7%93%D7%99%D7%92%D7%99/", "https://www.facebook.com/Petah.Tikva.Muni/about_contact_and_basic_info/", "https://sherut.org.il/שירות-לקוחות-עיריית-פתח-תקווה/", "https://sherut-kal.co.il/org/iriyat-petah-tikva", "https://xn----9hcbajix2gfiog.org.il/%D7%A2%D7%99%D7%A8%D7%99%D7%99%D7%AA-%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA/", "https://customer-service.co.il/שירות-לקוחות-עיריית-פתח-תקווה/", "https://serviced.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA-%D7%A2%D7%99%D7%A8%D7%99%D7%99%D7%AA-%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-%D7%98/", "https://www.sherut.net/PetahTikva", "https://www.petah-tikva.muni.il/city-and-municipality/departments", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F%40Petah.Tikva.Muni%2F", "https://www.govserv.org/IL/Petah-Tikva/116563891775107/עיריית-פתח-תקווה"]</t>
+          <t>["https://www.b144.co.il/b144_sip/401C04134675615A491C0515/", "https://carmelist.co.il/item/86297", "https://ycom.co.il/%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%9E%D7%97%D7%95%D7%96-%D7%97%D7%99%D7%A4%D7%94-%D7%95%D7%92%D7%9C%D7%99%D7%9C-%D7%9E%D7%A2%D7%A8%D7%91%D7%99-%D7%9C%D7%94%D7%99%D7%95%D7%AA-%D7%A8%D7%90%D7%A9%D7%95/", "https://haipo.co.il/item/496259", "https://www.zhk.co.il/כללית-מחוז-חיפה-וגליל-מערבי-להיות-ראשו/", "https://haifa.mynet.co.il/health/article/hyojiptxlg", "https://www.colbonews.co.il/health/166678/", "https://hospitals.clalit.co.il/carmel/he/Our-doctors-and-experts/Pages/afifa-yaakov.aspx", "https://www.clalit.co.il/he/info/tenders/Pages/kol-kore.aspx", "https://www.gov.il/BlobFolder/reports/hmo-clalit-haifa-11092014/he/files_reports_hmo_Clalit_haifa_11092014.pdf", "https://haipo.co.il/item/575696", "https://www.clalit.co.il/he/info/tenders/Pages/mkomi_mhozot.aspx", "https://newzim.co.il/zafon/", "https://hospitals.clalit.co.il/carmel/he/Pages/default.aspx", "https://www.b144.co.il/b144_sip/4D1C01154C75645C491405/", "https://haipo.co.il/item/500989", "https://cdn.mednet.co.il/2018/04/igod-FD_cenes-dan-eilat-OCT-2018_tochniyaCLALI_SMS.pdf"]</t>
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>76256759256816</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
+        <v>228770277888540</v>
+      </c>
+      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
         <v>0</v>
       </c>
@@ -1455,6 +1449,4029 @@
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>כללית , מנהלת באר שבע</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.b144.co.il/b144_sip/401C04134079675E48160012/</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:43:35.534200+00:00</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>6</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>["https://www.b144.co.il/b144_sip/401C04134079675E48160012/", "https://www.b144.co.il/b144_sip/401C04134175605441150115/"]</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>כללית , משרדי מנהלת פתח תקוה</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.b144.co.il/b144_sip/401C0413407662554D170210/</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-09-08T08:09:24.205637+00:00</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>["https://www.b144.co.il/b144_sip/401C0413407662554D170210/", "https://www.b144.co.il/b144_sip/401C0413407662554D170214/"]</t>
+        </is>
+      </c>
+      <c r="AD11" t="n">
+        <v>228770277888546</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>לשכת בריאות מחוז חיפה</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.gov.il/he/government-service-branches/health_bureau_haifa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:41:01.613021+00:00</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>6</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>["https://www.gov.il/he/government-service-branches/health_bureau_haifa", "https://serviced.co.il/health-office/%D7%A9%D7%A2%D7%95%D7%AA-%D7%A4%D7%AA%D7%99%D7%97%D7%94-%D7%95%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA-%D7%9C%D7%A7%D7%91%D7%9C%D7%AA-%D7%A7%D7%94%D7%9C-%D7%9C%D7%A9%D7%9B%D7%AA-%D7%94%D7%91%D7%A8%D7%99-3/", "https://www.d.co.il/80120070/34675/"]</t>
+        </is>
+      </c>
+      <c r="AD12" t="n">
+        <v>228770277888540</v>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>לשכת בריאות מחוז תל אביב</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.gov.il/he/government-service-branches/health_bureau_tel_aviv</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-09-08T08:09:50.293768+00:00</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>6</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>["https://www.gov.il/he/government-service-branches/health_bureau_tel_aviv", "https://www.gov.il/he/government-service-branches/moh-tel-aviv-management", "https://serviced.co.il/health-office/%D7%A9%D7%A2%D7%95%D7%AA-%D7%A4%D7%AA%D7%99%D7%97%D7%94-%D7%95%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA-%D7%9C%D7%A7%D7%91%D7%9C%D7%AA-%D7%A7%D7%94%D7%9C-%D7%9C%D7%A9%D7%9B%D7%AA-%D7%94%D7%91%D7%A8%D7%99-7/"]</t>
+        </is>
+      </c>
+      <c r="AD13" t="n">
+        <v>152513518592367</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>מנהל "סורוקה" מזהיר</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://publichealth.doctorsonly.co.il/2019/12/178510/</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:43:49.307240+00:00</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>6</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>["https://publichealth.doctorsonly.co.il/2019/12/178510/"]</t>
+        </is>
+      </c>
+      <c r="AD14" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>מנהל חדש לבית החולים אסותא אשדוד</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://publichealth.doctorsonly.co.il/2019/11/176190/</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:43:59.719628+00:00</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>6</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>["https://publichealth.doctorsonly.co.il/2019/11/176190/"]</t>
+        </is>
+      </c>
+      <c r="AD15" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>מנהל.ת בריאות הנפש מחוזי.ת</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.leumit.co.il/jobs/work-in-leumit/administrative-positions/5293/</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:41:01.614114+00:00</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>6</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>["https://www.leumit.co.il/jobs/work-in-leumit/administrative-positions/5293/", "https://www.wikirefua.org.il/w/index.php?title=%D7%94%D7%A4%D7%A2%D7%9C%D7%94_%D7%A9%D7%9C_%D7%9E%D7%A2%D7%A0%D7%94_%D7%A0%D7%A4%D7%A9%D7%99_%D7%9C%D7%90%D7%95%D7%9B%D7%9C%D7%95%D7%A1%D7%99%D7%99%D7%94_%D7%91%D7%A9%D7%A2%D7%AA_%D7%97%D7%99%D7%A8%D7%95%D7%9D_-_%D7%97%D7%95%D7%96%D7%A8_%D7%9E%D7%A9%D7%A8%D7%93_%D7%94%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA"]</t>
+        </is>
+      </c>
+      <c r="AD16" t="n">
+        <v>228770277888540</v>
+      </c>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>מנהל.ת תחום התפתחות הילד</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.leumit.co.il/jobs/work-in-leumit/administrative-positions/5696/</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:41:01.615471+00:00</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>["https://www.leumit.co.il/jobs/work-in-leumit/administrative-positions/5696/", "https://jobify360.co.il/jobs/2590863-jk", "https://jobify360.co.il/jobs/4226403a4b2bd590-id"]</t>
+        </is>
+      </c>
+      <c r="AD17" t="n">
+        <v>228770277888540</v>
+      </c>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>מנהל/ת מחלקת שירות ותיאום רפואי</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/lior-mandil-⭐-i-m-hiring-⭐-69387bab_מנהלת-מחלקת-שירות-ותיאום-רפואי-שפלה-activity-7192856183970377728-L3st</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:44:14.762298+00:00</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>6</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD18" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>מנהל/ת רפואי/ת אזורי/ת ל80% משרה</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://il.indeed.com/viewjob?jk=3b29890f13d5a898</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:44:17.247502+00:00</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>6</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>["https://il.indeed.com/viewjob?jk=3b29890f13d5a898", "https://www.jobnet.co.il/jobs?positionid=13397334", "https://www.glassdoor.com/job-listing/מנהל-ת-רפואי-ת-אזורי-ת-ל80-משרה-מכבי-טבעי-JV_KO0,31_KE32,41.htm?jl=1010241650998", "https://il.indeed.com/viewjob?jk=8fd39c38ab31b39d"]</t>
+        </is>
+      </c>
+      <c r="AD19" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>מנהלת חדשה למחוז דרום של הכללית</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.b7net.co.il/בריאות/מנהלת-חדשה-למחוז-דרום-של-הכללית-399924</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:41:13.090061+00:00</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>6</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>["https://www.b7net.co.il/%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA/%D7%9E%D7%A0%D7%94%D7%9C%D7%AA-%D7%97%D7%93%D7%A9%D7%94-%D7%9C%D7%9E%D7%97%D7%95%D7%96-%D7%93%D7%A8%D7%95%D7%9D-%D7%A9%D7%9C-%D7%94%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-399924"]</t>
+        </is>
+      </c>
+      <c r="AD20" t="n">
+        <v>228770277888540</v>
+      </c>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>מנהלת רופאים ומקצועות רפואה נדרשים</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.gov.il/he/departments/units/physicians-and-other-medical-professions-directorate</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:44:25.942301+00:00</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>6</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>["https://www.gov.il/he/departments/units/physicians-and-other-medical-professions-directorate", "https://www.gov.il/h+e/Departments/Units/physicians-and-other-medical-professions-directorate", "https://www.gov.il/he/pages/kolkoraklitabmada_doctor"]</t>
+        </is>
+      </c>
+      <c r="AD21" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>מנהלת רפואית חדשה באסותא אשדוד</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.inn.co.il/news/686948</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:44:36.491618+00:00</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>6</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>["https://www.inn.co.il/news/686948"]</t>
+        </is>
+      </c>
+      <c r="AD22" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>מערך מנהל ומשק</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.lev-hasharon.co.il/</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:44:39.643303+00:00</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>6</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>["https://www.lev-hasharon.co.il/", "https://www.lev-hasharon.co.il/?ward=%D7%9E%D7%A0%D7%94%D7%9C-%D7%95%D7%9E%D7%A9%D7%A7"]</t>
+        </is>
+      </c>
+      <c r="AD23" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>מרפאת כללית סמייל אשדוד שפירא</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.clalitsmile.co.il/clinic/מרפאת-כללית-סמייל-אשדוד-יב</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:44:56.220817+00:00</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>6</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>["https://www.clalitsmile.co.il/clinic/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%A1%D7%9E%D7%99%D7%99%D7%9C-%D7%90%D7%A9%D7%93%D7%95%D7%93-%D7%99%D7%91", "https://www.clalitsmile.co.il/clinic/מרפאת-כללית-סמייל-אשדוד-יב"]</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>מרפאת כללית סמייל חיפה</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.clalitsmile.co.il/clinic/9020</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:41:20.049884+00:00</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>6</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>["https://www.clalitsmile.co.il/clinic/9020", "https://zips.co.il/%D7%A2%D7%A1%D7%A7%D7%99%D7%9D/%D7%97%D7%99%D7%A4%D7%94/%D7%9E%D7%A8%D7%A4%D7%90%D7%95%D7%AA-%D7%A9%D7%99%D7%A0%D7%99%D7%99%D7%9D/42953/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%A1%D7%9E%D7%99%D7%99%D7%9C-%D7%97%D7%99%D7%A4%D7%94-%D7%90%D7%A8%D7%9E%D7%95%D7%9F", "https://textmap.guide/192456/9798", "https://www.clalitsmile.co.il/clinic/9716", "https://il.near-place.com/mrpt-kllyt-smyyl-hyph-grnd-qnywn-drk-smhh-gwln-54-hyph", "https://il.near-place.com/mrpt-kllyt-smyyl-hyph-wdytwrywm-mthm-wdytwrywm-sdrwt-hnsy-134-hyph", "https://il.directmap.info/חיפה/3267", "https://zips.co.il/%D7%A2%D7%A1%D7%A7%D7%99%D7%9D/%D7%97%D7%99%D7%A4%D7%94/%D7%9E%D7%A8%D7%A4%D7%90%D7%95%D7%AA-%D7%A9%D7%99%D7%A0%D7%99%D7%99%D7%9D/42945/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%A1%D7%9E%D7%99%D7%99%D7%9C-%D7%97%D7%99%D7%A4%D7%94-%D7%92%D7%A8%D7%A0%D7%93-%D7%A7%D7%A0%D7%99%D7%95%D7%9F"]</t>
+        </is>
+      </c>
+      <c r="AD25" t="n">
+        <v>228770277888540</v>
+      </c>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>מרפאת כללית סמייל נתניה</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.clalitsmile.co.il/clinic/מרפאת-כללית-סמייל-נתניה-עיר-ימים</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:43:12.535395+00:00</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>6</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>["https://www.clalitsmile.co.il/clinic/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%A1%D7%9E%D7%99%D7%99%D7%9C-%D7%A0%D7%AA%D7%A0%D7%99%D7%94-%D7%A2%D7%99%D7%A8-%D7%99%D7%9E%D7%99%D7%9D", "https://www.clalitsmile.co.il/clinic/מרפאת-כללית-סמייל-נתניה-עיר-ימים", "https://www.clalitsmile.co.il/clinic/מרפאת-כללית-סמייל-נתניה-רמז", "https://www.clalitsmile.co.il/clinic/מרפאת-כללית-סמייל-נתניה-קריית-השרון", "https://www.doctors.co.il/forum-13/message-176405/"]</t>
+        </is>
+      </c>
+      <c r="AD26" t="n">
+        <v>228770277888540</v>
+      </c>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>מרפאת כללית סמייל פתח תקווה</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.clalitsmile.co.il/clinic/מרפאת-כללית-סמייל-פתח-תקווה-אם-המושבות</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:44:46.940364+00:00</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>6</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>["https://www.clalitsmile.co.il/clinic/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%A1%D7%9E%D7%99%D7%99%D7%9C-%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-%D7%90%D7%9D-%D7%94%D7%9E%D7%95%D7%A9%D7%91%D7%95%D7%AA", "https://www.clalitsmile.co.il/clinic/מרפאת-כללית-סמייל-פתח-תקווה-אם-המושבות"]</t>
+        </is>
+      </c>
+      <c r="AD27" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>12</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>מרפאת כללית סמייל ראשון לציון</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.clalitsmile.co.il/clinic/מרפאת-כללית-סמייל-ראשון-לציון-רוטשילד</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:44:58.373736+00:00</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>6</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>["https://www.clalitsmile.co.il/clinic/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%A1%D7%9E%D7%99%D7%99%D7%9C-%D7%A8%D7%90%D7%A9%D7%95%D7%9F-%D7%9C%D7%A6%D7%99%D7%95%D7%9F-%D7%A8%D7%95%D7%98%D7%A9%D7%99%D7%9C%D7%93", "https://www.clalitsmile.co.il/clinic/מרפאת-כללית-סמייל-ראשון-לציון-רוטשילד", "https://www.clalitsmile.co.il/clinic/9702", "https://il.near-place.com/mrpt-kllyt-smyyl-rswn-lzywnrwtsyld-rwtsyld-45-rswn-lzywn", "https://il.near-place.com/mrpt-kllyt-smyyl-rswn-lzywn-slym-htzmwrt-30-rswn-lzywn/en", "https://www.d.co.il/33256100/32060/", "https://openinghours.co.il/מרפאת-כללית-סמייל-ראשון-לציון-אשלים-התזמורת-30-ראש"]</t>
+        </is>
+      </c>
+      <c r="AD28" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>מרפאת כללית רובע ד' אשדוד שעות פתיחה</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://xn----8hcbjj5cq0blc.org.il/opening-hours/מרפאת-כללית-רובע-ד-אשדוד/</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:45:05.275658+00:00</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>6</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>["https://xn----8hcbjj5cq0blc.org.il/opening-hours/מרפאת-כללית-רובע-ד-אשדוד/"]</t>
+        </is>
+      </c>
+      <c r="AD29" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>12</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>מרפאת כללית רפואה משלימה תל אביב</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.clalitmashlima.co.il/מרפאות-כללית-רפואה-משלימה/מרפאת-כללית-רפואה-משלימה-תל-אביב-רמת-י/</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:41:31.027486+00:00</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>6</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>["https://www.clalitmashlima.co.il/%D7%9E%D7%A8%D7%A4%D7%90%D7%95%D7%AA-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%9E%D7%A9%D7%9C%D7%99%D7%9E%D7%94/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%A8%D7%A4%D7%95%D7%90%D7%94-%D7%9E%D7%A9%D7%9C%D7%99%D7%9E%D7%94-%D7%AA%D7%9C-%D7%90%D7%91%D7%99%D7%91-%D7%A8%D7%9E%D7%AA-%D7%99/", "https://easy.co.il/page/27146209", "https://www.clalitmashlima.co.il/מרפאות-כללית-רפואה-משלימה/מרפאת-כללית-רפואה-משלימה-תל-אביב-רמת-י/"]</t>
+        </is>
+      </c>
+      <c r="AD30" t="n">
+        <v>228770277888540</v>
+      </c>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>מרפאת מבוגרים נתניה</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.lev-hasharon.co.il/?clinic=marpeot-mevugarim-natanya</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:41:41.437529+00:00</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>6</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>["https://www.lev-hasharon.co.il/?clinic=marpeot-mevugarim-natanya", "https://www.hakkolasakim.com/המרפאה-לבריאות-הנפש-מבוגרים-נתניה-09-834-5666", "https://www.kolsherut.org.il/p/card/c/ee8aa98e", "https://yellowpages-he.cybo.com/IL-biz/המרפאה-לבריאות-הנפש-מבוגרים-נתניה", "https://www.d.co.il/80157713/7670/", "https://www.lev-hasharon.co.il/?page_id=98"]</t>
+        </is>
+      </c>
+      <c r="AD31" t="n">
+        <v>228770277888540</v>
+      </c>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>מרפאת ראשון לציון</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.bikurofe.co.il/rashlatz/</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:41:50.405395+00:00</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>6</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>["https://www.bikurofe.co.il/rashlatz/", "https://www.dr-arama.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://dr-swissa.infomed.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://dr-danguttman.info/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.draviram.co.il/", "https://mor.org.il/branches/rishon-lezion/", "https://www.myrishon.co.il/מרפאת--רקפות--של-כללית-נפתחה-בטקס-חגיגי"]</t>
+        </is>
+      </c>
+      <c r="AD32" t="n">
+        <v>228770277888540</v>
+      </c>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>12</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>משרות שוות בארגונים רפואיים</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1369923046517008/</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:41:54.906833+00:00</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>6</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>["https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fgroups%2F1369923046517008%2F", "https://www.facebook.com/groups/1369923046517008/media/", "https://www.facebook.com/groups/1369923046517008/posts/3505924476250177/", "https://www.facebook.com/groups/1369923046517008/posts/2447184298790872/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fgroups%2F1369923046517008%2Finfo%2F"]</t>
+        </is>
+      </c>
+      <c r="AD33" t="n">
+        <v>228770277888540</v>
+      </c>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>12</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>נחנך המיון החדש בביה"ח השרון</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://publichealth.doctorsonly.co.il/2022/03/256468/</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:45:15.265608+00:00</t>
+        </is>
+      </c>
+      <c r="W34" t="n">
+        <v>6</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>["https://publichealth.doctorsonly.co.il/2022/03/256468/"]</t>
+        </is>
+      </c>
+      <c r="AD34" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>12</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>נתניה לב העיר</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.leumit.co.il/medicalcenterssearch/medicalcenterssearchresults/medicalcenter/</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:42:03.011116+00:00</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>6</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>["https://www.leumit.co.il/medicalcenterssearch/medicalcenterssearchresults/medicalcenter/", "https://www.xn----8hcbjj5cq0blc.co.il/%D7%A7%D7%95%D7%A4%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%9C%D7%90%D7%95%D7%9E%D7%99%D7%AA/opening_hours.asp?eid=14649", "https://easy.co.il/page/27322363", "https://openinghours.co.il/מרכז-רפואי-לב-העיר-יהושע-שטמפפר-17-נתניה", "https://www.xn----8hcbjj5cq0blc.co.il/mobile_opening_hours_city.asp?cid=81&amp;city=%D7%A0%D7%AA%D7%A0%D7%99%D7%94", "https://www.leumit.co.il/medicalcenterssearch/medicalcenterssearchresults/medicalcenter/?medicalCenterTypeId=1&amp;branchNum=6&amp;subBranchNum=1"]</t>
+        </is>
+      </c>
+      <c r="AD35" t="n">
+        <v>228770277888540</v>
+      </c>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>12</v>
+      </c>
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>נתניה- סמילנסקי</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.meuhedet.co.il/poi/Pharmacy/044001_0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:45:20.773265+00:00</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>6</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>["https://www.meuhedet.co.il/poi/Pharmacy/044001_0", "https://www.alljobs.co.il/m/p/jobs/8307594", "https://jobify360.co.il/jobs/2590236-jk", "https://jobify360.co.il/about", "https://jobify360.co.il/contactus", "https://jobify360.co.il/jobs/38348767-dr", "https://jobify360.co.il/jobs/2756854-jk", "https://jobify360.co.il/jobs/38342858-dr", "https://fr.cybo.com/IL-biz/בנק-מזרחי-סניף-נתניה", "https://www.familyfinance.co.il/%D7%A1%D7%A0%D7%99%D7%A4%D7%99-%D7%9E%D7%A1-%D7%94%D7%9B%D7%A0%D7%A1%D7%94-%D7%90%D7%96%D7%95%D7%A8-%D7%94%D7%A9%D7%A8%D7%95%D7%9F/%D7%A1%D7%A0%D7%99%D7%A3-%D7%9E%D7%A1-%D7%94%D7%9B%D7%A0%D7%A1%D7%94-%D7%A0%D7%AA%D7%A0%D7%99%D7%94/", "https://patuah.co.il/he/b/%D7%A8%D7%A9%D7%95%D7%AA-%D7%94%D7%9E%D7%99%D7%A1%D7%99%D7%9D-%D7%9E%D7%A7%D7%A8%D7%A7%D7%A2%D7%99%D7%9F-%D7%A1%D7%9E%D7%99%D7%9C%D7%A0%D7%A1%D7%A7%D7%99-6-%D7%A0%D7%AA%D7%A0%D7%99%D7%94--u4445", "https://www.chabad.org.il/IsraeliBranchs/Item.asp?ArticleID=67522&amp;CategoryID=60&amp;CityID=-1", "https://jobify360.co.il/jobs/4460494263-in", "https://jobify360.co.il/jobs/274f51e57b03d17a-id", "https://jobify360.co.il/jobs/38318443-dr", "https://openinghours.co.il/מאוחדת-סמילנסקי-20-נתניה", "https://easy.co.il/page/27352466", "https://il.near-place.com/mwhdt-smylnsqy-20-ntnyh", "https://www.meuhedet.co.il/poi/MeuhedetClinic/044001_0", "https://www.meuhedet.co.il/poi/MeuhedetClinic/044006_0"]</t>
+        </is>
+      </c>
+      <c r="AD36" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>12</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>עיריית פתח תקווה</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.petah-tikva.muni.il/health/kupatholiim</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-09-08T08:08:51.054289+00:00</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>6</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>["https://www.petah-tikva.muni.il/health/kupatholiim", "https://www.petah-tikva.muni.il/city-and-municipality/bids", "https://www.govojobs.co.il/govjobs/more/עיריית-פתח-תקווה-דרושים?page=8181", "https://www.alljobs.co.il/Employer/HP/Default.aspx?cid=180065", "https://www.davar1.co.il/topic/פתח-תקווה/", "https://www.be106.net/207/157035", "https://www.petah-tikva.muni.il/", "https://petachtikva.co.il/%D7%90%D7%AA%D7%A8-%D7%A2%D7%99%D7%A8%D7%99%D7%99%D7%AA-%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-%D7%94%D7%97%D7%93%D7%A9-%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99%D7%9D-%D7%93%D7%99%D7%92%D7%99/", "https://www.facebook.com/Petah.Tikva.Muni/about_contact_and_basic_info/", "https://sherut.org.il/שירות-לקוחות-עיריית-פתח-תקווה/", "https://sherut-kal.co.il/org/iriyat-petah-tikva", "https://xn----9hcbajix2gfiog.org.il/%D7%A2%D7%99%D7%A8%D7%99%D7%99%D7%AA-%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA/", "https://customer-service.co.il/שירות-לקוחות-עיריית-פתח-תקווה/", "https://serviced.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA-%D7%A2%D7%99%D7%A8%D7%99%D7%99%D7%AA-%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-%D7%98/", "https://www.sherut.net/PetahTikva", "https://www.petah-tikva.muni.il/city-and-municipality/departments", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2F%40Petah.Tikva.Muni%2F", "https://www.govserv.org/IL/Petah-Tikva/116563891775107/עיריית-פתח-תקווה"]</t>
+        </is>
+      </c>
+      <c r="AD37" t="n">
+        <v>228770277770448</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>12</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>קופת חולים בנתניה</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/h-c43950-e0-p0-l0-city7400/</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:45:35.156165+00:00</t>
+        </is>
+      </c>
+      <c r="W38" t="n">
+        <v>6</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>["https://www.d.co.il/h-c43950-e0-p0-l0-city7400/", "https://openinghours.co.il/כללית-קופת-חולים-דרך-רזיאל-8-נתניה", "https://www.meuhedet.co.il/poi/Pharmacy/044001_0", "https://www.laniado.org.il/contact-us/"]</t>
+        </is>
+      </c>
+      <c r="AD38" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>12</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>קופת חולים ושירותי בריאות</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.meuhedet.co.il/</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:42:17.183055+00:00</t>
+        </is>
+      </c>
+      <c r="W39" t="n">
+        <v>6</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>["https://www.meuhedet.co.il/", "https://www.police.gov.il/join/hmo-info", "https://www.kamaze.co.il/Health/Companies/82008/meuhedet"]</t>
+        </is>
+      </c>
+      <c r="AD39" t="n">
+        <v>228770277888540</v>
+      </c>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>12</v>
+      </c>
+      <c r="B40" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>קופת חולים מאוחדת</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.aguda.co.il/services/מרפאות-לייעוץ-וגמילה-ממשככי-כאבים-ותר/קופת-חולים-מאוחדת-באר-שבע/</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:42:32.489567+00:00</t>
+        </is>
+      </c>
+      <c r="W40" t="n">
+        <v>6</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>["https://www.aguda.co.il/services/%D7%9E%D7%A8%D7%A4%D7%90%D7%95%D7%AA-%D7%9C%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%95%D7%92%D7%9E%D7%99%D7%9C%D7%94-%D7%9E%D7%9E%D7%A9%D7%9B%D7%9B%D7%99-%D7%9B%D7%90%D7%91%D7%99%D7%9D-%D7%95%D7%AA%D7%A8/%D7%A7%D7%95%D7%A4%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%9E%D7%90%D7%95%D7%97%D7%93%D7%AA-%D7%91%D7%90%D7%A8-%D7%A9%D7%91%D7%A2/", "https://www.meuhedet.co.il/", "https://www.meuhedet.co.il/%D7%9E%D7%99%D7%93%D7%A2-%D7%9C%D7%9C%D7%A7%D7%95%D7%97/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%9E%D7%90%D7%95%D7%97%D7%93%D7%AA/", "https://www.meuhedet.co.il/%D7%9E%D7%99%D7%93%D7%A2-%D7%9C%D7%9C%D7%A7%D7%95%D7%97/%D7%9B%D7%AA%D7%91%D7%95-%D7%9C%D7%A0%D7%95/", "https://civilsociety.co.il/%D7%9E%D7%A8%D7%A4%D7%90%D7%95%D7%AA-%D7%9E%D7%90%D7%95%D7%97%D7%93%D7%AA/", "https://www.xn----8hcbjj5cq0blc.co.il/%D7%A7%D7%95%D7%A4%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%9E%D7%90%D7%95%D7%97%D7%93%D7%AA/opening_hours_city.asp?cid=515&amp;city=%D7%97%D7%99%D7%A4%D7%94", "https://online.meuhedet.co.il/shaban/Hospitals/1704000", "https://www.meuhedet.co.il/poi/Pharmacy/020006_0", "https://www.meuhedet.co.il/%D7%96%D7%9B%D7%95%D7%99%D7%95%D7%AA-%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99%D7%9D-%D7%95%D7%91%D7%99%D7%98%D7%95%D7%97%D7%99%D7%9D/%D7%96%D7%9B%D7%95%D7%99%D7%95%D7%AA-%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99%D7%9D-%D7%95%D7%91%D7%99%D7%98%D7%95%D7%97%D7%99%D7%9D/%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%A0%D7%A4%D7%A9/", "https://www.meuhedet.co.il/poi/MedicalInstitution/006923400000000000000000000000_0", "https://www.meuhedet.co.il/poi/NurseryClinic/057002_0", "https://www.leumit.co.il/", "https://www.leumit.co.il/media/kc2ir3w5/מרפאות-אחודות-לשעת-חירום-מעודכן-ל-24924.xlsx", "https://www.leumit.co.il/jobs/work-in-leumit/", "https://sherut-il.com/%D7%A7%D7%95%D7%A4%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%9E%D7%90%D7%95%D7%97%D7%93%D7%AA/", "https://sherut.org.il/שירות-לקוחות-קופת-חולים-מאוחדת/", "https://www.sherut-lakohot.co.il/מאוחדת/", "https://customer-service.co.il/שירות-לקוחות-קופת-חולים-מאוחדת/", "https://xn----9hcbajix2gfiog.org.il/%D7%9E%D7%90%D7%95%D7%97%D7%93%D7%AA-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA/"]</t>
+        </is>
+      </c>
+      <c r="AD40" t="n">
+        <v>228770277888540</v>
+      </c>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>12</v>
+      </c>
+      <c r="B41" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>קריירה בתפקידי מנהל ומטה בכללית</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.clalit.co.il/he/info/career/Pages/jobs_admin_hq.aspx</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:45:28.305999+00:00</t>
+        </is>
+      </c>
+      <c r="W41" t="n">
+        <v>6</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>["https://www.clalit.co.il/he/info/career/Pages/jobs_admin_hq.aspx"]</t>
+        </is>
+      </c>
+      <c r="AD41" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>12</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ראשון לציון</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.bbalev.co.il/rishon-lezion-rehabilitation-center/</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:42:37.004969+00:00</t>
+        </is>
+      </c>
+      <c r="W42" t="n">
+        <v>6</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>["https://www.bbalev.co.il/rishon-lezion-rehabilitation-center/", "https://www.hironit.org.il/", "https://rishonlezion.datacity.org.il/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%90%D7%99%D7%9C%D7%99%D7%94-%D7%9C%D7%99%D7%98%D7%95%D7%91%D7%A6%D7%99%D7%A7/", "https://cardioisrael.co.il/", "https://www.bikurofe.co.il/rashlatz/", "https://maccabi-dent.com/מרפאה/?id=34", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=Km6CypIruiLU5ds9xCtoroVaxsl83kkvU1bvzM3DHYD/vm3uabFa00GTZExDtQMX8aE22J8J81QUwn7wjxMUXQ==", "https://my.rishonlezion.muni.il/", "https://sherut.org.il/שירות-לקוחות-עיריית-ראשון-לציון/", "https://rishonlezion.complot.co.il/", "https://rishonlezion.complot.co.il/generalinfo/contact/", "https://www.drushim.co.il/jobs/search/%D7%A8%D7%90%D7%A9%D7%95%D7%9F+%D7%9C%D7%A6%D7%99%D7%95%D7%9F,/", "http://www.rishonim-md.co.il/"]</t>
+        </is>
+      </c>
+      <c r="AD42" t="n">
+        <v>228770277888540</v>
+      </c>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>12</v>
+      </c>
+      <c r="B43" t="n">
+        <v>5</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ראשון לציון נרקיסים</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://go.serguide.maccabi4u.co.il/heb/medicalcentres/medicalcentressearchresults/medicalcentresinfopage/?ItemKeyIndex=565BCDA945B48CF6B40D9C90A8FCCBA5&amp;RequestId=00000000-0000-0000-0005-000000000008</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:45:41.553345+00:00</t>
+        </is>
+      </c>
+      <c r="W43" t="n">
+        <v>6</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>["https://go.serguide.maccabi4u.co.il/heb/medicalcentres/medicalcentressearchresults/medicalcentresinfopage/?ItemKeyIndex=565BCDA945B48CF6B40D9C90A8FCCBA5&amp;RequestId=00000000-0000-0000-0005-000000000008", "https://optica-halperin.com/branch/%D7%A8%D7%90%D7%A9%D7%95%D7%9F-%D7%9C%D7%A6%D7%99%D7%95%D7%9F-%D7%A0%D7%A8%D7%A7%D7%99%D7%A1%D7%99%D7%9D/", "https://www.be106.net/realestate/show/129379", "https://www.zooeretz.co.il/pages/52682-StoresRishonLezionNarkisim", "https://www.komo.co.il/code/nadlan/apartments-for-sale.asp?nehes=1&amp;cityName=%D7%A8%D7%90%D7%A9%D7%95%D7%9F+%D7%9C%D7%A6%D7%99%D7%95%D7%9F&amp;neighborhoodNum=4555&amp;privateOnly=1", "https://www.yad2.co.il/realestate/forsale/center-and-sharon?area=9&amp;city=8300&amp;neighborhood=991420", "https://www.yad2.co.il/realestate/rent/center-and-sharon?area=9&amp;city=8300&amp;neighborhood=991420", "https://www.yad2.co.il/realestate/forsale/center-and-sharon?area=9&amp;city=8300&amp;neighborhood=991420&amp;property=1&amp;minRooms=5&amp;maxRooms=5", "https://go.serguide.maccabi4u.co.il/heb/labsandtherapists/labsandtherapistssearchresults/labsandtherapistsinfopage/?ItemKeyIndex=88D350AE4E4DC9ADE801C16BF38D6996&amp;RequestId=00000000-0000-0000-0003-000000000025", "https://mekomonrishon.co.il/2026/01/21/%D7%9E%D7%9E%D7%A9%D7%99%D7%9B%D7%94-%D7%91%D7%AA%D7%A0%D7%95%D7%A4%D7%AA-%D7%94%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%9C%D7%90%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%99%D7%A8%D7%95/", "https://www.maccabitivi.co.il/clinics/rishon-lezion_narkisim/"]</t>
+        </is>
+      </c>
+      <c r="AD43" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>12</v>
+      </c>
+      <c r="B44" t="n">
+        <v>5</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>שירותי בריאות כללית , מרפאת אשדוד י"ג</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.b144.co.il/b144_sip/401C04134675625C41100413/</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:45:52.064143+00:00</t>
+        </is>
+      </c>
+      <c r="W44" t="n">
+        <v>6</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>["https://www.b144.co.il/b144_sip/401C04134675625C41100413/", "https://www.b144.co.il/b144_sip/401C04134175655A4D170C12/"]</t>
+        </is>
+      </c>
+      <c r="AD44" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>12</v>
+      </c>
+      <c r="B45" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>שירותי בריאות כללית , מרפאת נתניה דרום</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.b144.co.il/b144_sip/401C04134675625C4F160014/</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:46:07.453308+00:00</t>
+        </is>
+      </c>
+      <c r="W45" t="n">
+        <v>6</v>
+      </c>
+      <c r="X45" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>["https://www.b144.co.il/b144_sip/401C04134675625C4F160014/", "https://srch.co.il/מרפאה-נתניה-דרום"]</t>
+        </is>
+      </c>
+      <c r="AD45" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>12</v>
+      </c>
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>שירותי בריאות כללית באשדוד</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.t.co.il/Business/Network_192_1_0_s127.html</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:46:07.454651+00:00</t>
+        </is>
+      </c>
+      <c r="W46" t="n">
+        <v>6</v>
+      </c>
+      <c r="X46" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>["https://www.t.co.il/Business/Network_192_1_0_s127.html", "https://www.t.co.il/Business/Card-233846.html", "https://easy.co.il/list/Clalit-Health?region=303", "https://easy.co.il/list/Clalit-Health?c2=2024&amp;region=303"]</t>
+        </is>
+      </c>
+      <c r="AD46" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>12</v>
+      </c>
+      <c r="B47" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>שירותי בריאות כללית בראשון לציון</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.t.co.il/Business/Network_192_1_0_s1199.html</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:42:49.757888+00:00</t>
+        </is>
+      </c>
+      <c r="W47" t="n">
+        <v>6</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>["https://www.t.co.il/Business/Network_192_1_0_s1199.html", "https://openinghours.co.il/פינסקר-מרכז-מקצועי-שירותי-בריאות-כללית-יהודה-לייב-31-35-ראשון-לציון", "https://www.d.co.il/34237380/43950/", "https://easy.co.il/list/Clalit-Health?region=1783", "https://www.t.co.il/Business/Card-757542.html", "https://www.d.co.il/64200610/43950/", "https://patuah.co.il/he/b/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%96%D7%91%D7%95%D7%98%D7%99%D7%A0%D7%A1%D7%A7%D7%99-18-%D7%A8%D7%90%D7%A9%D7%95%D7%9F-%D7%9C%D7%A6%D7%99%D7%95%D7%9F--u6169"]</t>
+        </is>
+      </c>
+      <c r="AD47" t="n">
+        <v>228770277888540</v>
+      </c>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>12</v>
+      </c>
+      <c r="B48" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>תל אביב מדיקל קליניק</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>clinic_manager</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://tamc.co.il/</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>REVIEW_INVALID_TARGET_NAME</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:46:13.416395+00:00</t>
+        </is>
+      </c>
+      <c r="W48" t="n">
+        <v>6</v>
+      </c>
+      <c r="X48" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>["https://tamc.co.il/", "https://tamc.co.il/uncategorized-he/medical-directors-remarks/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTAmedicalclinic%2Fphotos%2F%25D7%259E%25D7%25A8%25D7%25A4%25D7%2590%25D7%25AA-%25D7%2594%25D7%2590%25D7%2595%25D7%25A0%25D7%25A7%25D7%2595%25D7%259C%25D7%2595%25D7%2592%25D7%2599%25D7%2594-%25D7%2594%25D7%25A4%25D7%25A8%25D7%2598%25D7%2599%25D7%25AA-%25D7%2591%25D7%25AA%25D7%259C-%25D7%2590%25D7%2591%25D7%2599%25D7%2591-%25D7%25A6%25D7%2595%25D7%2595%25D7%25AA-%25D7%259E%25D7%2595%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259E%25D7%2595%25D7%2591%25D7%2599%25D7%259C-%25D7%2596%25D7%259E%25D7%2599%25D7%25A0%25D7%2595%25D7%25AA-%25D7%259E%25D7%2594%25D7%2599%25D7%25A8%25D7%2594-%25D7%2595%25D7%2598%25D7%2599%25D7%25A4%25D7%2595%25D7%259C-%25D7%259E%25D7%2595%25D7%25AA%25D7%2590%25D7%259D-%25D7%2590%25D7%2599%2F797350246146727%2F", "https://www.infomed.co.il/experts/153623/", "https://tlvmed.co.il/"]</t>
+        </is>
+      </c>
+      <c r="AD48" t="n">
+        <v>228958564246194</v>
+      </c>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -706,9 +706,11 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>183079455104316</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>549238365312948</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
@@ -809,7 +811,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>228770277888546</v>
+        <v>686310833665638</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -914,7 +916,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>228770277888546</v>
+        <v>686310833665638</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1019,7 +1021,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>228770277888546</v>
+        <v>686310833665638</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1124,7 +1126,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>228770277888546</v>
+        <v>686310833665638</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1229,9 +1231,11 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE7" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
       <c r="AF7" t="n">
         <v>0</v>
       </c>
@@ -1332,7 +1336,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>228770277888546</v>
+        <v>686310833665638</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1437,9 +1441,11 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>228770277888540</v>
-      </c>
-      <c r="AE9" t="inlineStr"/>
+        <v>686310833665620</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
       <c r="AF9" t="n">
         <v>0</v>
       </c>
@@ -1540,9 +1546,11 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE10" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
       <c r="AF10" t="n">
         <v>0</v>
       </c>
@@ -1643,7 +1651,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>228770277888546</v>
+        <v>686310833665638</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -1748,9 +1756,11 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>228770277888540</v>
-      </c>
-      <c r="AE12" t="inlineStr"/>
+        <v>686310833665620</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
       <c r="AF12" t="n">
         <v>0</v>
       </c>
@@ -1851,7 +1861,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>152513518592367</v>
+        <v>457540555777101</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -1956,9 +1966,11 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE14" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
       <c r="AF14" t="n">
         <v>0</v>
       </c>
@@ -2059,9 +2071,11 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE15" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
       <c r="AF15" t="n">
         <v>0</v>
       </c>
@@ -2162,9 +2176,11 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>228770277888540</v>
-      </c>
-      <c r="AE16" t="inlineStr"/>
+        <v>686310833665620</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
       <c r="AF16" t="n">
         <v>0</v>
       </c>
@@ -2265,9 +2281,11 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>228770277888540</v>
-      </c>
-      <c r="AE17" t="inlineStr"/>
+        <v>686310833665620</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
       <c r="AF17" t="n">
         <v>0</v>
       </c>
@@ -2368,9 +2386,11 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE18" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
       <c r="AF18" t="n">
         <v>0</v>
       </c>
@@ -2471,9 +2491,11 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE19" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
       <c r="AF19" t="n">
         <v>0</v>
       </c>
@@ -2574,9 +2596,11 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>228770277888540</v>
-      </c>
-      <c r="AE20" t="inlineStr"/>
+        <v>686310833665620</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
       <c r="AF20" t="n">
         <v>0</v>
       </c>
@@ -2677,9 +2701,11 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE21" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
       <c r="AF21" t="n">
         <v>0</v>
       </c>
@@ -2780,9 +2806,11 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE22" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
       <c r="AF22" t="n">
         <v>0</v>
       </c>
@@ -2883,9 +2911,11 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE23" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
       <c r="AF23" t="n">
         <v>0</v>
       </c>
@@ -2986,9 +3016,11 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE24" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
       <c r="AF24" t="n">
         <v>0</v>
       </c>
@@ -3089,9 +3121,11 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>228770277888540</v>
-      </c>
-      <c r="AE25" t="inlineStr"/>
+        <v>686310833665620</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
       <c r="AF25" t="n">
         <v>0</v>
       </c>
@@ -3192,9 +3226,11 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>228770277888540</v>
-      </c>
-      <c r="AE26" t="inlineStr"/>
+        <v>686310833665620</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
       <c r="AF26" t="n">
         <v>0</v>
       </c>
@@ -3295,9 +3331,11 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE27" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
       <c r="AF27" t="n">
         <v>0</v>
       </c>
@@ -3398,9 +3436,11 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE28" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
       <c r="AF28" t="n">
         <v>0</v>
       </c>
@@ -3501,9 +3541,11 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE29" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
       <c r="AF29" t="n">
         <v>0</v>
       </c>
@@ -3604,9 +3646,11 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>228770277888540</v>
-      </c>
-      <c r="AE30" t="inlineStr"/>
+        <v>686310833665620</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
       <c r="AF30" t="n">
         <v>0</v>
       </c>
@@ -3707,9 +3751,11 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>228770277888540</v>
-      </c>
-      <c r="AE31" t="inlineStr"/>
+        <v>686310833665620</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
       <c r="AF31" t="n">
         <v>0</v>
       </c>
@@ -3810,9 +3856,11 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>228770277888540</v>
-      </c>
-      <c r="AE32" t="inlineStr"/>
+        <v>686310833665620</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
       <c r="AF32" t="n">
         <v>0</v>
       </c>
@@ -3913,9 +3961,11 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>228770277888540</v>
-      </c>
-      <c r="AE33" t="inlineStr"/>
+        <v>686310833665620</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
       <c r="AF33" t="n">
         <v>0</v>
       </c>
@@ -4016,9 +4066,11 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE34" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
       <c r="AF34" t="n">
         <v>0</v>
       </c>
@@ -4119,9 +4171,11 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>228770277888540</v>
-      </c>
-      <c r="AE35" t="inlineStr"/>
+        <v>686310833665620</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
       <c r="AF35" t="n">
         <v>0</v>
       </c>
@@ -4222,9 +4276,11 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE36" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
       <c r="AF36" t="n">
         <v>0</v>
       </c>
@@ -4325,7 +4381,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>228770277770448</v>
+        <v>686310833311344</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -4430,9 +4486,11 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE38" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
       <c r="AF38" t="n">
         <v>0</v>
       </c>
@@ -4533,9 +4591,11 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>228770277888540</v>
-      </c>
-      <c r="AE39" t="inlineStr"/>
+        <v>686310833665620</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
       <c r="AF39" t="n">
         <v>0</v>
       </c>
@@ -4636,9 +4696,11 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>228770277888540</v>
-      </c>
-      <c r="AE40" t="inlineStr"/>
+        <v>686310833665620</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
       <c r="AF40" t="n">
         <v>0</v>
       </c>
@@ -4739,9 +4801,11 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE41" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
       <c r="AF41" t="n">
         <v>0</v>
       </c>
@@ -4842,9 +4906,11 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>228770277888540</v>
-      </c>
-      <c r="AE42" t="inlineStr"/>
+        <v>686310833665620</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1</v>
+      </c>
       <c r="AF42" t="n">
         <v>0</v>
       </c>
@@ -4945,9 +5011,11 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE43" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
       <c r="AF43" t="n">
         <v>0</v>
       </c>
@@ -5048,9 +5116,11 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE44" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
       <c r="AF44" t="n">
         <v>0</v>
       </c>
@@ -5151,9 +5221,11 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE45" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
       <c r="AF45" t="n">
         <v>0</v>
       </c>
@@ -5254,9 +5326,11 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE46" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
       <c r="AF46" t="n">
         <v>0</v>
       </c>
@@ -5357,9 +5431,11 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>228770277888540</v>
-      </c>
-      <c r="AE47" t="inlineStr"/>
+        <v>686310833665620</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
       <c r="AF47" t="n">
         <v>0</v>
       </c>
@@ -5460,9 +5536,11 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>228958564246194</v>
-      </c>
-      <c r="AE48" t="inlineStr"/>
+        <v>686875692738582</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
       <c r="AF48" t="n">
         <v>0</v>
       </c>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>549238365312948</v>
+        <v>1647715095938844</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>686310833665638</v>
+        <v>2058932500996914</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>686310833665638</v>
+        <v>2058932500996914</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>686310833665638</v>
+        <v>2058932500996914</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>686310833665638</v>
+        <v>2058932500996914</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>686310833665638</v>
+        <v>2058932500996914</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>686310833665620</v>
+        <v>2058932500996860</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>686310833665638</v>
+        <v>2058932500996914</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>686310833665620</v>
+        <v>2058932500996860</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>457540555777101</v>
+        <v>1372621667331303</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>686310833665620</v>
+        <v>2058932500996860</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>686310833665620</v>
+        <v>2058932500996860</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>686310833665620</v>
+        <v>2058932500996860</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>686310833665620</v>
+        <v>2058932500996860</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>686310833665620</v>
+        <v>2058932500996860</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>686310833665620</v>
+        <v>2058932500996860</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>686310833665620</v>
+        <v>2058932500996860</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>686310833665620</v>
+        <v>2058932500996860</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>686310833665620</v>
+        <v>2058932500996860</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>686310833665620</v>
+        <v>2058932500996860</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>686310833311344</v>
+        <v>2058932499934032</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>686310833665620</v>
+        <v>2058932500996860</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>686310833665620</v>
+        <v>2058932500996860</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>686310833665620</v>
+        <v>2058932500996860</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -5326,7 +5326,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>686310833665620</v>
+        <v>2058932500996860</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>686875692738582</v>
+        <v>2060627078215746</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1647715095938844</v>
+        <v>4943145287816532</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>2058932500996914</v>
+        <v>6176797502990742</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>2058932500996914</v>
+        <v>6176797502990742</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>2058932500996914</v>
+        <v>6176797502990742</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>2058932500996914</v>
+        <v>6176797502990742</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>2058932500996914</v>
+        <v>6176797502990742</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>2058932500996860</v>
+        <v>6176797502990580</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>2058932500996914</v>
+        <v>6176797502990742</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>2058932500996860</v>
+        <v>6176797502990580</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1372621667331303</v>
+        <v>4117865001993909</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>2058932500996860</v>
+        <v>6176797502990580</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>2058932500996860</v>
+        <v>6176797502990580</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>2058932500996860</v>
+        <v>6176797502990580</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>2058932500996860</v>
+        <v>6176797502990580</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>2058932500996860</v>
+        <v>6176797502990580</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>2058932500996860</v>
+        <v>6176797502990580</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>2058932500996860</v>
+        <v>6176797502990580</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>2058932500996860</v>
+        <v>6176797502990580</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>2058932500996860</v>
+        <v>6176797502990580</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>2058932500996860</v>
+        <v>6176797502990580</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>2058932499934032</v>
+        <v>6176797499802096</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>2058932500996860</v>
+        <v>6176797502990580</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>2058932500996860</v>
+        <v>6176797502990580</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>2058932500996860</v>
+        <v>6176797502990580</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -5326,7 +5326,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>2058932500996860</v>
+        <v>6176797502990580</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>2060627078215746</v>
+        <v>6181881234647238</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM1"/>
+  <dimension ref="A1:AQ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,19 +601,19 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>role_evidence</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>resolution_reason</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>search_fingerprint</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>role_evidence</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>verification_review_required</t>
@@ -622,6 +622,26 @@
       <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>previous_candidate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>verification_schema_version</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>identity_name_verified</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>identity_specialty_verified</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>identity_evidence</t>
         </is>
       </c>
     </row>

--- a/output/review.xlsx
+++ b/output/review.xlsx
@@ -616,32 +616,32 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>verification_schema_version</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>identity_name_verified</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>identity_specialty_verified</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>identity_evidence</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>verification_review_required</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>previous_candidate</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>verification_schema_version</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>identity_name_verified</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>identity_specialty_verified</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>identity_evidence</t>
         </is>
       </c>
     </row>
